--- a/financial_models/Res_Property_Monitor.xlsx
+++ b/financial_models/Res_Property_Monitor.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE8D6D20-4DEB-4F8A-8323-63C690C1F456}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7636D8D4-EF0E-4C9A-87B7-C89B182EF50A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="6150" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="6150" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Assumptions" sheetId="13" r:id="rId1"/>
@@ -20,10 +20,10 @@
   <definedNames>
     <definedName name="AuraStyleDefaultsReset" hidden="1">#N/A</definedName>
     <definedName name="Cap_Rate">Assumptions!$C$5</definedName>
-    <definedName name="HKDCNY">Assumptions!$C$30</definedName>
-    <definedName name="HKDUSD">Assumptions!$C$29</definedName>
+    <definedName name="HKDCNY">Assumptions!$C$29</definedName>
+    <definedName name="HKDUSD">Assumptions!$C$28</definedName>
     <definedName name="Holding_Period">Assumptions!$C$6</definedName>
-    <definedName name="Other_Annual_Expense_Percent">Assumptions!$C$26</definedName>
+    <definedName name="Other_Annual_Expense_Percent">Assumptions!$C$25</definedName>
     <definedName name="WW3f877d8e32714ec8a8180854ed7f8276_634328481945590045" hidden="1">#REF!</definedName>
     <definedName name="WW3f877d8e32714ec8a8180854ed7f8276_634328482352282765" hidden="1">#REF!</definedName>
   </definedNames>
@@ -58,9 +58,6 @@
     <t>Apt.</t>
   </si>
   <si>
-    <t>Interest Rate</t>
-  </si>
-  <si>
     <t>Monthly Management Fee</t>
   </si>
   <si>
@@ -184,9 +181,6 @@
     <t>Asking Price</t>
   </si>
   <si>
-    <t>Optimal Price</t>
-  </si>
-  <si>
     <t>Annual NOI</t>
   </si>
   <si>
@@ -287,32 +281,6 @@
   </si>
   <si>
     <t>How to Analyze a Property Investment Using IRR</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">This guide explains a simple way to evaluate if buying a rental property is a good investment. It uses a method called </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Internal Rate of Return (IRR)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>, which shows your average annual return over the holding period.</t>
-    </r>
   </si>
   <si>
     <t>Saleable Area (Sqft)</t>
@@ -507,9 +475,6 @@
   </si>
   <si>
     <t>如何使用 IRR 分析物業投資</t>
-  </si>
-  <si>
-    <t>本指南介紹一種簡單方法，幫助你評估購買出租物業是否為好投資。它使用一種叫做「內部回報率」（Internal Rate of Return，簡稱 IRR）的方法，顯示你在持有期間的平均年化回報率。</t>
   </si>
   <si>
     <r>
@@ -674,6 +639,102 @@
 IRR = 目標回報率 → 中性
 IRR &lt; 目標回報率 → 不值得投資</t>
     </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Core logic: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">The return comes from two main parts: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>stable rental income + capital appreciation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> during the holding period.
+The lower the purchase price, the higher the rental growth, or the greater the price appreciation, the higher the IRR will be.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>核心邏輯：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>回報來自兩部分——</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>穩定租金收入+持有期資本增值</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>。
+購入價越低、租金增長或價格升幅越大，IRR 越高。</t>
+    </r>
+  </si>
+  <si>
+    <t>IRR Netural Price</t>
+  </si>
+  <si>
+    <t>typical unlevered hurdle rates range from 4.0%–5.0%</t>
   </si>
 </sst>
 </file>
@@ -820,164 +881,136 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="10" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="10" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -988,6 +1021,21 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1317,7 +1365,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:D59"/>
+  <dimension ref="B2:D58"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="2.59765625" customWidth="1"/>
@@ -1327,259 +1375,250 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B4" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" s="12">
+        <v>0.05</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" s="13">
+        <v>15</v>
+      </c>
+      <c r="D6" s="4"/>
+    </row>
+    <row r="8" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B8" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="12">
+        <v>2.3E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C10" s="12">
+        <v>0.01</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B11" t="s">
+        <v>73</v>
+      </c>
+      <c r="C11" s="42">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C12" s="27">
+        <f>(1+C11)^(1/Holding_Period)-1</f>
+        <v>1.7644813405053306E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="C13" s="3"/>
+    </row>
+    <row r="14" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B14" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-    </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B4" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4" s="16" t="s">
+      <c r="C14" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D14" s="14" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B5" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="C5" s="14">
-        <f>C9+1%</f>
-        <v>0.04</v>
-      </c>
-      <c r="D5" s="11"/>
-    </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B6" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="C6" s="15">
-        <v>15</v>
-      </c>
-      <c r="D6" s="11"/>
-    </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B8" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="C8" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="D8" s="16" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B9" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="14">
-        <v>0.03</v>
-      </c>
-      <c r="D9" s="11"/>
-    </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B10" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="C10" s="14">
-        <v>2.3E-2</v>
-      </c>
-      <c r="D10" s="11"/>
-    </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B11" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="C11" s="14">
+    <row r="15" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B15" t="s">
+        <v>58</v>
+      </c>
+      <c r="C15" s="12">
         <v>0.01</v>
       </c>
-      <c r="D11" s="4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B12" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="C12" s="52">
-        <v>0.3</v>
-      </c>
-      <c r="D12" s="11"/>
-    </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B13" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="C13" s="46">
-        <f>(1+C12)^(1/Holding_Period)-1</f>
-        <v>1.7644813405053306E-2</v>
-      </c>
-      <c r="D13" s="11"/>
-    </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="C14" s="3"/>
-    </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B15" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="C15" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="D15" s="16" t="s">
-        <v>1</v>
+      <c r="D15" s="4" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="16" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C16" s="18">
+        <v>20000</v>
+      </c>
+      <c r="D16" s="4" t="s">
         <v>60</v>
-      </c>
-      <c r="C16" s="22">
-        <v>0.01</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B17" t="s">
-        <v>59</v>
-      </c>
-      <c r="C17" s="23">
-        <v>20000</v>
+        <v>61</v>
+      </c>
+      <c r="C17" s="18">
+        <v>5000</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B18" t="s">
+        <v>62</v>
+      </c>
+      <c r="C18" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="D18" s="4"/>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="C19" s="3"/>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B20" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="C18" s="23">
-        <v>5000</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B19" t="s">
-        <v>64</v>
-      </c>
-      <c r="C19" s="22">
-        <v>1E-3</v>
-      </c>
-      <c r="D19" s="4"/>
-    </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="C20" s="3"/>
+      <c r="C20" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="D20" s="14" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B21" s="17" t="s">
-        <v>65</v>
-      </c>
-      <c r="C21" s="16" t="s">
+      <c r="B21" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21" s="12">
+        <v>5.5E-2</v>
+      </c>
+      <c r="D21" s="4"/>
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B22" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" s="12">
+        <v>0.03</v>
+      </c>
+      <c r="D22" s="4"/>
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B23" t="s">
+        <v>14</v>
+      </c>
+      <c r="C23" s="12">
+        <v>0.08</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B24" t="s">
+        <v>17</v>
+      </c>
+      <c r="C24" s="12">
+        <v>0.02</v>
+      </c>
+      <c r="D24" s="4"/>
+    </row>
+    <row r="25" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B25" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C25" s="17">
+        <f>SUM(C21:C24)</f>
+        <v>0.18499999999999997</v>
+      </c>
+      <c r="D25" s="4"/>
+    </row>
+    <row r="27" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B27" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="C27" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="D21" s="16" t="s">
+      <c r="D27" s="14" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B22" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="C22" s="20">
-        <v>5.5E-2</v>
-      </c>
-      <c r="D22" s="6"/>
-    </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B23" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="C23" s="20">
-        <v>0.03</v>
-      </c>
-      <c r="D23" s="6"/>
-    </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B24" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="C24" s="20">
-        <v>0.08</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B25" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="C25" s="20">
-        <v>0.02</v>
-      </c>
-      <c r="D25" s="6"/>
-    </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B26" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="C26" s="21">
-        <f>SUM(C22:C25)</f>
-        <v>0.18499999999999997</v>
-      </c>
-      <c r="D26" s="6"/>
-    </row>
     <row r="28" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B28" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="C28" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="D28" s="16" t="s">
-        <v>1</v>
+      <c r="B28" t="s">
+        <v>3</v>
+      </c>
+      <c r="C28" s="45">
+        <v>7.8</v>
       </c>
     </row>
     <row r="29" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B29" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="C29" s="56">
-        <v>7.8</v>
-      </c>
-      <c r="D29" s="11"/>
+      <c r="B29" t="s">
+        <v>4</v>
+      </c>
+      <c r="C29" s="45">
+        <v>0.89</v>
+      </c>
     </row>
     <row r="30" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B30" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="C30" s="56">
-        <v>0.89</v>
-      </c>
-      <c r="D30" s="11"/>
-    </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B31" s="18" t="s">
+      <c r="B30" t="s">
         <v>5</v>
       </c>
-      <c r="C31" s="57">
+      <c r="C30" s="46">
         <v>1000</v>
       </c>
-      <c r="D31" s="11"/>
+    </row>
+    <row r="32" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B32" s="1" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B33" s="1" t="s">
+      <c r="B33" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1588,27 +1627,30 @@
         <v>31</v>
       </c>
     </row>
-    <row r="35" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B35" t="s">
-        <v>32</v>
+    <row r="36" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B36" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="37" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B37" s="1" t="s">
-        <v>22</v>
+      <c r="B37" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B38" t="s">
         <v>10</v>
       </c>
+      <c r="C38" s="2">
+        <v>0.05</v>
+      </c>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B39" t="s">
         <v>11</v>
       </c>
       <c r="C39" s="2">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="40" spans="2:3" x14ac:dyDescent="0.45">
@@ -1616,41 +1658,38 @@
         <v>12</v>
       </c>
       <c r="C40" s="2">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B41" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41" s="2"/>
+    </row>
+    <row r="43" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B43" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="44" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B44" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="46" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B46" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="47" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B47" t="s">
         <v>13</v>
-      </c>
-      <c r="C41" s="2">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="42" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B42" t="s">
-        <v>23</v>
-      </c>
-      <c r="C42" s="2"/>
-    </row>
-    <row r="44" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B44" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="45" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B45" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="47" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B47" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="48" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B48" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="49" spans="2:2" x14ac:dyDescent="0.45">
@@ -1658,13 +1697,13 @@
         <v>16</v>
       </c>
     </row>
-    <row r="50" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B50" t="s">
+    <row r="51" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B51" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="52" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B52" s="1" t="s">
+      <c r="B52" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1678,24 +1717,19 @@
         <v>20</v>
       </c>
     </row>
-    <row r="55" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B55" t="s">
-        <v>21</v>
+    <row r="56" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B56" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="57" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B57" s="1" t="s">
+      <c r="B57" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="58" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B58" t="s">
         <v>26</v>
-      </c>
-    </row>
-    <row r="59" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B59" t="s">
-        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1712,366 +1746,365 @@
   <dimension ref="B2:E52"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="18" customWidth="1"/>
-    <col min="2" max="2" width="28.53125" style="18" customWidth="1"/>
-    <col min="3" max="9" width="16.59765625" style="18" customWidth="1"/>
-    <col min="10" max="16384" width="8.796875" style="18"/>
+    <col min="1" max="1" width="2.6640625" customWidth="1"/>
+    <col min="2" max="2" width="28.53125" customWidth="1"/>
+    <col min="3" max="9" width="16.59765625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B2" s="48" t="s">
-        <v>91</v>
+      <c r="B2" s="38" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B4" s="50" t="s">
-        <v>42</v>
-      </c>
-      <c r="C4" s="25" t="s">
-        <v>45</v>
+      <c r="B4" s="40" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B5" s="50" t="s">
+      <c r="B5" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="25" t="s">
+      <c r="C5" s="20" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B6" s="50" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" s="26">
+      <c r="B6" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="21">
         <v>2000</v>
       </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B7" s="50" t="s">
-        <v>34</v>
-      </c>
-      <c r="C7" s="27">
+      <c r="B7" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="22">
         <f ca="1">YEAR(TODAY())-C6</f>
         <v>26</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B8" s="50" t="s">
-        <v>86</v>
-      </c>
-      <c r="C8" s="28">
+      <c r="B8" s="40" t="s">
+        <v>83</v>
+      </c>
+      <c r="C8" s="23">
         <v>1000</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B9" s="50" t="s">
-        <v>87</v>
-      </c>
-      <c r="C9" s="29">
+      <c r="B9" s="40" t="s">
+        <v>84</v>
+      </c>
+      <c r="C9" s="24">
         <v>2</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B10" s="50" t="s">
-        <v>39</v>
-      </c>
-      <c r="C10" s="30">
+      <c r="B10" s="40" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="25">
         <f>Holding_Period</f>
         <v>15</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B12" s="47" t="s">
-        <v>93</v>
+      <c r="B12" s="37" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B14" s="50" t="s">
+      <c r="B14" s="40" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D14" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="C14" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>50</v>
+      <c r="E14" s="6" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B15" s="51" t="s">
-        <v>88</v>
-      </c>
-      <c r="C15" s="42">
+      <c r="B15" s="41" t="s">
+        <v>85</v>
+      </c>
+      <c r="C15" s="34">
         <f>C16/C8</f>
         <v>15000</v>
       </c>
-      <c r="D15" s="43">
+      <c r="D15" s="35">
         <v>14000</v>
       </c>
-      <c r="E15" s="43">
-        <v>10000</v>
+      <c r="E15" s="34">
+        <f>E16/C8</f>
+        <v>12300</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B16" s="50" t="s">
-        <v>54</v>
-      </c>
-      <c r="C16" s="32">
+      <c r="B16" s="40" t="s">
+        <v>52</v>
+      </c>
+      <c r="C16" s="18">
         <v>15000000</v>
       </c>
-      <c r="D16" s="31">
+      <c r="D16" s="26">
         <f>D15*C$8</f>
         <v>14000000</v>
       </c>
-      <c r="E16" s="31">
-        <f>E15*C$8</f>
-        <v>10000000</v>
+      <c r="E16" s="56">
+        <v>12300000</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B17" s="50" t="s">
+      <c r="B17" s="40" t="s">
+        <v>67</v>
+      </c>
+      <c r="C17" s="54">
+        <f>Assumptions!C15</f>
+        <v>0.01</v>
+      </c>
+      <c r="D17" s="54"/>
+      <c r="E17" s="54"/>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B18" s="40" t="s">
+        <v>64</v>
+      </c>
+      <c r="C18" s="12">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="D18" s="12">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="E18" s="12">
+        <v>3.7499999999999999E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B19" s="40" t="s">
+        <v>66</v>
+      </c>
+      <c r="C19" s="54">
+        <f>Assumptions!C18</f>
+        <v>1E-3</v>
+      </c>
+      <c r="D19" s="54"/>
+      <c r="E19" s="54"/>
+    </row>
+    <row r="20" spans="2:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B20" s="43" t="s">
+        <v>68</v>
+      </c>
+      <c r="C20" s="55">
+        <f>Assumptions!C16+Assumptions!C17</f>
+        <v>25000</v>
+      </c>
+      <c r="D20" s="55"/>
+      <c r="E20" s="55"/>
+    </row>
+    <row r="21" spans="2:5" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="B21" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="C17" s="33">
-        <f>Assumptions!C16</f>
-        <v>0.01</v>
-      </c>
-      <c r="D17" s="33"/>
-      <c r="E17" s="33"/>
-    </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B18" s="50" t="s">
-        <v>66</v>
-      </c>
-      <c r="C18" s="14">
-        <v>3.7499999999999999E-2</v>
-      </c>
-      <c r="D18" s="14">
-        <v>3.7499999999999999E-2</v>
-      </c>
-      <c r="E18" s="14">
-        <v>3.7499999999999999E-2</v>
-      </c>
-    </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B19" s="50" t="s">
-        <v>68</v>
-      </c>
-      <c r="C19" s="33">
-        <f>Assumptions!C19</f>
-        <v>1E-3</v>
-      </c>
-      <c r="D19" s="33"/>
-      <c r="E19" s="33"/>
-    </row>
-    <row r="20" spans="2:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B20" s="54" t="s">
-        <v>70</v>
-      </c>
-      <c r="C20" s="45">
-        <f>Assumptions!C17+Assumptions!C18</f>
-        <v>25000</v>
-      </c>
-      <c r="D20" s="45"/>
-      <c r="E20" s="45"/>
-    </row>
-    <row r="21" spans="2:5" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="B21" s="34" t="s">
-        <v>71</v>
-      </c>
-      <c r="C21" s="35">
+      <c r="C21" s="29">
         <f>C16+C16*($C$17+C18+$C$19)+$C$20</f>
         <v>15752500</v>
       </c>
-      <c r="D21" s="35">
+      <c r="D21" s="29">
         <f t="shared" ref="D21:E21" si="0">D16+D16*($C$17+D18+$C$19)+$C$20</f>
         <v>14704000</v>
       </c>
-      <c r="E21" s="35">
+      <c r="E21" s="29">
         <f t="shared" si="0"/>
-        <v>10510000</v>
+        <v>12921550</v>
       </c>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B23" s="47" t="s">
-        <v>92</v>
+      <c r="B23" s="37" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="24" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C24" s="5"/>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B25" s="50" t="s">
-        <v>72</v>
-      </c>
-      <c r="C25" s="36">
-        <f>Assumptions!$C$10</f>
+      <c r="B25" s="40" t="s">
+        <v>70</v>
+      </c>
+      <c r="C25" s="30">
+        <f>Assumptions!$C$9</f>
         <v>2.3E-2</v>
       </c>
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B26" s="51" t="s">
-        <v>46</v>
-      </c>
-      <c r="C26" s="49">
+      <c r="B26" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="C26" s="39">
         <f>D16</f>
         <v>14000000</v>
       </c>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B27" s="34" t="s">
-        <v>73</v>
-      </c>
-      <c r="C27" s="38">
+      <c r="B27" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="C27" s="32">
         <f>C26*C$25/12</f>
         <v>26833.333333333332</v>
       </c>
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B28" s="8"/>
-      <c r="C28" s="38"/>
+      <c r="B28" s="7"/>
+      <c r="C28" s="32"/>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B29" s="50" t="s">
-        <v>9</v>
-      </c>
-      <c r="C29" s="38">
+      <c r="B29" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" s="32">
         <f>C$9*C$8</f>
         <v>2000</v>
       </c>
     </row>
     <row r="30" spans="2:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B30" s="54" t="s">
-        <v>47</v>
-      </c>
-      <c r="C30" s="55">
+      <c r="B30" s="43" t="s">
+        <v>46</v>
+      </c>
+      <c r="C30" s="44">
         <f ca="1">(C27*(Other_Annual_Expense_Percent-IF(C$7&gt;=30,4%,0)))</f>
         <v>4964.1666666666661</v>
       </c>
     </row>
     <row r="31" spans="2:5" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="B31" s="34" t="s">
-        <v>74</v>
-      </c>
-      <c r="C31" s="38">
+      <c r="B31" s="28" t="s">
+        <v>72</v>
+      </c>
+      <c r="C31" s="32">
         <f ca="1">C27-C29-C30</f>
         <v>19869.166666666664</v>
       </c>
     </row>
     <row r="32" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B32" s="34" t="s">
-        <v>53</v>
-      </c>
-      <c r="C32" s="36">
+      <c r="B32" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="C32" s="30">
+        <f>Assumptions!C10</f>
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="34" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B34" s="37" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="36" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B36" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="C36" s="33">
         <f>Assumptions!C11</f>
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B34" s="47" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B36" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="C36" s="40">
-        <f>Assumptions!C12</f>
         <v>0.3</v>
       </c>
     </row>
     <row r="37" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B37" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="C37" s="36">
+      <c r="B37" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="C37" s="30">
         <f>(1+C36)^(1/C10)-1</f>
         <v>1.7644813405053306E-2</v>
       </c>
     </row>
     <row r="38" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B38" s="24" t="s">
-        <v>44</v>
-      </c>
-      <c r="C38" s="9">
+      <c r="B38" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="C38" s="8">
         <f>D16*(1+C$36)</f>
         <v>18200000</v>
       </c>
     </row>
     <row r="40" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B40" s="47" t="s">
-        <v>98</v>
+      <c r="B40" s="37" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="42" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B42" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="C42" s="58" t="str">
+      <c r="B42" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="C42" s="47" t="str">
         <f>C14</f>
         <v>Asking Price</v>
       </c>
-      <c r="D42" s="58" t="str">
+      <c r="D42" s="47" t="str">
         <f>D14</f>
         <v>Comparable</v>
       </c>
-      <c r="E42" s="58" t="str">
+      <c r="E42" s="47" t="str">
         <f>E14</f>
-        <v>Optimal Price</v>
+        <v>IRR Netural Price</v>
       </c>
     </row>
     <row r="43" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B43" s="24" t="s">
-        <v>78</v>
-      </c>
-      <c r="C43" s="31">
+      <c r="B43" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="C43" s="26">
         <f>C16</f>
         <v>15000000</v>
       </c>
-      <c r="D43" s="31">
+      <c r="D43" s="26">
         <f t="shared" ref="D43:E43" si="1">D16</f>
         <v>14000000</v>
       </c>
-      <c r="E43" s="31">
+      <c r="E43" s="26">
         <f t="shared" si="1"/>
-        <v>10000000</v>
+        <v>12300000</v>
       </c>
     </row>
     <row r="44" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B44" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="C44" s="37">
+      <c r="B44" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="C44" s="31">
         <f>C21</f>
         <v>15752500</v>
       </c>
-      <c r="D44" s="37">
+      <c r="D44" s="31">
         <f>D21</f>
         <v>14704000</v>
       </c>
-      <c r="E44" s="37">
+      <c r="E44" s="31">
         <f>E21</f>
-        <v>10510000</v>
+        <v>12921550</v>
       </c>
     </row>
     <row r="45" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B45" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="C45" s="41">
+      <c r="B45" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="C45" s="52">
         <f ca="1">C$31*12</f>
         <v>238429.99999999997</v>
       </c>
-      <c r="D45" s="41"/>
-      <c r="E45" s="41"/>
+      <c r="D45" s="52"/>
+      <c r="E45" s="52"/>
     </row>
     <row r="46" spans="2:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B46" s="44" t="s">
-        <v>52</v>
+      <c r="B46" s="36" t="s">
+        <v>50</v>
       </c>
       <c r="C46" s="53">
         <f>C$38</f>
@@ -2081,43 +2114,40 @@
       <c r="E46" s="53"/>
     </row>
     <row r="47" spans="2:5" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="B47" s="34" t="s">
-        <v>79</v>
-      </c>
-      <c r="C47" s="39">
+      <c r="B47" s="28" t="s">
+        <v>77</v>
+      </c>
+      <c r="C47" s="27">
         <f ca="1">RATE(15, $C45*(1+$C$32), -C44, $C46 / (1+$C$32)^15) + $C$32</f>
         <v>2.4998387525081909E-2</v>
       </c>
-      <c r="D47" s="39">
+      <c r="D47" s="27">
         <f t="shared" ref="D47:E47" ca="1" si="2">RATE(15, $C45*(1+$C$32), -D44, $C46 / (1+$C$32)^15) + $C$32</f>
         <v>3.0196760572581638E-2</v>
       </c>
-      <c r="E47" s="39">
+      <c r="E47" s="27">
         <f t="shared" ca="1" si="2"/>
-        <v>5.6330514463608899E-2</v>
-      </c>
-    </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B49" s="60" t="s">
+        <v>4.009247428661733E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B49" s="48" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="50" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B50" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="51" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B51" t="s">
         <v>80</v>
       </c>
-      <c r="C49" s="59"/>
-      <c r="D49" s="59"/>
-      <c r="E49" s="59"/>
-    </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B50" s="18" t="s">
+    </row>
+    <row r="52" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B52" t="s">
         <v>81</v>
-      </c>
-    </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B51" s="18" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B52" s="18" t="s">
-        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -2149,115 +2179,115 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B2" s="61" t="s">
-        <v>84</v>
-      </c>
-      <c r="C2" s="62"/>
-      <c r="D2" s="61" t="s">
+      <c r="B2" s="49" t="s">
+        <v>82</v>
+      </c>
+      <c r="C2" s="50"/>
+      <c r="D2" s="49" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B3" s="50"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="50"/>
+    </row>
+    <row r="4" spans="2:4" ht="57" x14ac:dyDescent="0.45">
+      <c r="B4" s="51" t="s">
+        <v>105</v>
+      </c>
+      <c r="C4" s="50"/>
+      <c r="D4" s="51" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B5" s="50"/>
+      <c r="C5" s="50"/>
+      <c r="D5" s="50"/>
+    </row>
+    <row r="6" spans="2:4" ht="128.25" x14ac:dyDescent="0.45">
+      <c r="B6" s="51" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6" s="50"/>
+      <c r="D6" s="51" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B7" s="50"/>
+      <c r="C7" s="50"/>
+      <c r="D7" s="50"/>
+    </row>
+    <row r="8" spans="2:4" ht="85.5" x14ac:dyDescent="0.45">
+      <c r="B8" s="51" t="s">
+        <v>93</v>
+      </c>
+      <c r="C8" s="50"/>
+      <c r="D8" s="51" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B9" s="50"/>
+      <c r="C9" s="50"/>
+      <c r="D9" s="50"/>
+    </row>
+    <row r="10" spans="2:4" ht="85.5" x14ac:dyDescent="0.45">
+      <c r="B10" s="51" t="s">
+        <v>92</v>
+      </c>
+      <c r="C10" s="50"/>
+      <c r="D10" s="51" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B3" s="62"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
-    </row>
-    <row r="4" spans="2:4" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="B4" s="63" t="s">
-        <v>85</v>
-      </c>
-      <c r="C4" s="62"/>
-      <c r="D4" s="63" t="s">
+    <row r="11" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B11" s="50"/>
+      <c r="C11" s="50"/>
+      <c r="D11" s="50"/>
+    </row>
+    <row r="12" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B12" s="50"/>
+      <c r="C12" s="50"/>
+      <c r="D12" s="50"/>
+    </row>
+    <row r="13" spans="2:4" ht="71.25" x14ac:dyDescent="0.45">
+      <c r="B13" s="51" t="s">
+        <v>86</v>
+      </c>
+      <c r="C13" s="50"/>
+      <c r="D13" s="51" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B5" s="62"/>
-      <c r="C5" s="62"/>
-      <c r="D5" s="62"/>
-    </row>
-    <row r="6" spans="2:4" ht="128.25" x14ac:dyDescent="0.45">
-      <c r="B6" s="63" t="s">
-        <v>94</v>
-      </c>
-      <c r="C6" s="62"/>
-      <c r="D6" s="63" t="s">
+    <row r="14" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B14" s="50"/>
+      <c r="C14" s="50"/>
+      <c r="D14" s="50"/>
+    </row>
+    <row r="15" spans="2:4" ht="128.25" x14ac:dyDescent="0.45">
+      <c r="B15" s="51" t="s">
+        <v>96</v>
+      </c>
+      <c r="C15" s="50"/>
+      <c r="D15" s="51" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B7" s="62"/>
-      <c r="C7" s="62"/>
-      <c r="D7" s="62"/>
-    </row>
-    <row r="8" spans="2:4" ht="85.5" x14ac:dyDescent="0.45">
-      <c r="B8" s="63" t="s">
-        <v>96</v>
-      </c>
-      <c r="C8" s="62"/>
-      <c r="D8" s="63" t="s">
+    <row r="16" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B16" s="50"/>
+      <c r="C16" s="50"/>
+      <c r="D16" s="50"/>
+    </row>
+    <row r="17" spans="2:4" ht="85.5" x14ac:dyDescent="0.45">
+      <c r="B17" s="51" t="s">
+        <v>97</v>
+      </c>
+      <c r="C17" s="50"/>
+      <c r="D17" s="51" t="s">
         <v>104</v>
-      </c>
-    </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B9" s="62"/>
-      <c r="C9" s="62"/>
-      <c r="D9" s="62"/>
-    </row>
-    <row r="10" spans="2:4" ht="85.5" x14ac:dyDescent="0.45">
-      <c r="B10" s="63" t="s">
-        <v>95</v>
-      </c>
-      <c r="C10" s="62"/>
-      <c r="D10" s="63" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B11" s="62"/>
-      <c r="C11" s="62"/>
-      <c r="D11" s="62"/>
-    </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B12" s="62"/>
-      <c r="C12" s="62"/>
-      <c r="D12" s="62"/>
-    </row>
-    <row r="13" spans="2:4" ht="71.25" x14ac:dyDescent="0.45">
-      <c r="B13" s="63" t="s">
-        <v>89</v>
-      </c>
-      <c r="C13" s="62"/>
-      <c r="D13" s="63" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B14" s="62"/>
-      <c r="C14" s="62"/>
-      <c r="D14" s="62"/>
-    </row>
-    <row r="15" spans="2:4" ht="128.25" x14ac:dyDescent="0.45">
-      <c r="B15" s="63" t="s">
-        <v>99</v>
-      </c>
-      <c r="C15" s="62"/>
-      <c r="D15" s="63" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B16" s="62"/>
-      <c r="C16" s="62"/>
-      <c r="D16" s="62"/>
-    </row>
-    <row r="17" spans="2:4" ht="85.5" x14ac:dyDescent="0.45">
-      <c r="B17" s="63" t="s">
-        <v>100</v>
-      </c>
-      <c r="C17" s="62"/>
-      <c r="D17" s="63" t="s">
-        <v>108</v>
       </c>
     </row>
   </sheetData>

--- a/financial_models/Res_Property_Monitor.xlsx
+++ b/financial_models/Res_Property_Monitor.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7636D8D4-EF0E-4C9A-87B7-C89B182EF50A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8FC238E-F37D-4782-8DCE-FC4A537B4663}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="6150" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -881,7 +881,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -896,12 +896,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="10" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -925,9 +919,6 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="4" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -975,9 +966,6 @@
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1022,6 +1010,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1034,8 +1025,29 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1375,20 +1387,20 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="D4" s="12" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1396,7 +1408,7 @@
       <c r="B5" t="s">
         <v>35</v>
       </c>
-      <c r="C5" s="12">
+      <c r="C5" s="10">
         <v>0.05</v>
       </c>
       <c r="D5" s="4" t="s">
@@ -1407,19 +1419,19 @@
       <c r="B6" t="s">
         <v>38</v>
       </c>
-      <c r="C6" s="13">
+      <c r="C6" s="11">
         <v>15</v>
       </c>
       <c r="D6" s="4"/>
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="C8" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="D8" s="12" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1427,7 +1439,7 @@
       <c r="B9" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="12">
+      <c r="C9" s="10">
         <v>2.3E-2</v>
       </c>
     </row>
@@ -1435,7 +1447,7 @@
       <c r="B10" t="s">
         <v>75</v>
       </c>
-      <c r="C10" s="12">
+      <c r="C10" s="10">
         <v>0.01</v>
       </c>
       <c r="D10" s="4" t="s">
@@ -1446,7 +1458,7 @@
       <c r="B11" t="s">
         <v>73</v>
       </c>
-      <c r="C11" s="42">
+      <c r="C11" s="38">
         <v>0.3</v>
       </c>
     </row>
@@ -1454,7 +1466,7 @@
       <c r="B12" t="s">
         <v>74</v>
       </c>
-      <c r="C12" s="27">
+      <c r="C12" s="24">
         <f>(1+C11)^(1/Holding_Period)-1</f>
         <v>1.7644813405053306E-2</v>
       </c>
@@ -1463,13 +1475,13 @@
       <c r="C13" s="3"/>
     </row>
     <row r="14" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="C14" s="14" t="s">
+      <c r="C14" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="D14" s="14" t="s">
+      <c r="D14" s="12" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1477,7 +1489,7 @@
       <c r="B15" t="s">
         <v>58</v>
       </c>
-      <c r="C15" s="12">
+      <c r="C15" s="10">
         <v>0.01</v>
       </c>
       <c r="D15" s="4" t="s">
@@ -1488,7 +1500,7 @@
       <c r="B16" t="s">
         <v>57</v>
       </c>
-      <c r="C16" s="18">
+      <c r="C16" s="16">
         <v>20000</v>
       </c>
       <c r="D16" s="4" t="s">
@@ -1499,7 +1511,7 @@
       <c r="B17" t="s">
         <v>61</v>
       </c>
-      <c r="C17" s="18">
+      <c r="C17" s="16">
         <v>5000</v>
       </c>
       <c r="D17" s="4" t="s">
@@ -1510,7 +1522,7 @@
       <c r="B18" t="s">
         <v>62</v>
       </c>
-      <c r="C18" s="12">
+      <c r="C18" s="10">
         <v>1E-3</v>
       </c>
       <c r="D18" s="4"/>
@@ -1519,13 +1531,13 @@
       <c r="C19" s="3"/>
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B20" s="15" t="s">
+      <c r="B20" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="C20" s="14" t="s">
+      <c r="C20" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="D20" s="14" t="s">
+      <c r="D20" s="12" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1533,7 +1545,7 @@
       <c r="B21" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="12">
+      <c r="C21" s="10">
         <v>5.5E-2</v>
       </c>
       <c r="D21" s="4"/>
@@ -1542,7 +1554,7 @@
       <c r="B22" t="s">
         <v>27</v>
       </c>
-      <c r="C22" s="12">
+      <c r="C22" s="10">
         <v>0.03</v>
       </c>
       <c r="D22" s="4"/>
@@ -1551,7 +1563,7 @@
       <c r="B23" t="s">
         <v>14</v>
       </c>
-      <c r="C23" s="12">
+      <c r="C23" s="10">
         <v>0.08</v>
       </c>
       <c r="D23" s="4" t="s">
@@ -1562,29 +1574,29 @@
       <c r="B24" t="s">
         <v>17</v>
       </c>
-      <c r="C24" s="12">
+      <c r="C24" s="10">
         <v>0.02</v>
       </c>
       <c r="D24" s="4"/>
     </row>
     <row r="25" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B25" s="16" t="s">
+      <c r="B25" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="C25" s="17">
+      <c r="C25" s="15">
         <f>SUM(C21:C24)</f>
         <v>0.18499999999999997</v>
       </c>
       <c r="D25" s="4"/>
     </row>
     <row r="27" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B27" s="15" t="s">
+      <c r="B27" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="C27" s="14" t="s">
+      <c r="C27" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="D27" s="14" t="s">
+      <c r="D27" s="12" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1592,7 +1604,7 @@
       <c r="B28" t="s">
         <v>3</v>
       </c>
-      <c r="C28" s="45">
+      <c r="C28" s="41">
         <v>7.8</v>
       </c>
     </row>
@@ -1600,7 +1612,7 @@
       <c r="B29" t="s">
         <v>4</v>
       </c>
-      <c r="C29" s="45">
+      <c r="C29" s="41">
         <v>0.89</v>
       </c>
     </row>
@@ -1608,7 +1620,7 @@
       <c r="B30" t="s">
         <v>5</v>
       </c>
-      <c r="C30" s="46">
+      <c r="C30" s="42">
         <v>1000</v>
       </c>
     </row>
@@ -1752,75 +1764,75 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B2" s="38" t="s">
+      <c r="B2" s="34" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B4" s="40" t="s">
+      <c r="B4" s="36" t="s">
         <v>41</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="17" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B5" s="40" t="s">
+      <c r="B5" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="20" t="s">
+      <c r="C5" s="17" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B6" s="40" t="s">
+      <c r="B6" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="21">
+      <c r="C6" s="18">
         <v>2000</v>
       </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B7" s="40" t="s">
+      <c r="B7" s="36" t="s">
         <v>33</v>
       </c>
-      <c r="C7" s="22">
+      <c r="C7" s="19">
         <f ca="1">YEAR(TODAY())-C6</f>
         <v>26</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B8" s="40" t="s">
+      <c r="B8" s="36" t="s">
         <v>83</v>
       </c>
-      <c r="C8" s="23">
+      <c r="C8" s="20">
         <v>1000</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B9" s="40" t="s">
+      <c r="B9" s="36" t="s">
         <v>84</v>
       </c>
-      <c r="C9" s="24">
+      <c r="C9" s="21">
         <v>2</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B10" s="40" t="s">
+      <c r="B10" s="36" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="25">
+      <c r="C10" s="22">
         <f>Holding_Period</f>
         <v>15</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B12" s="37" t="s">
+      <c r="B12" s="33" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B14" s="40" t="s">
+      <c r="B14" s="36" t="s">
         <v>39</v>
       </c>
       <c r="C14" s="6" t="s">
@@ -1834,102 +1846,102 @@
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B15" s="41" t="s">
+      <c r="B15" s="37" t="s">
         <v>85</v>
       </c>
-      <c r="C15" s="34">
+      <c r="C15" s="31">
         <f>C16/C8</f>
         <v>15000</v>
       </c>
-      <c r="D15" s="35">
+      <c r="D15" s="32">
         <v>14000</v>
       </c>
-      <c r="E15" s="34">
+      <c r="E15" s="31">
         <f>E16/C8</f>
         <v>12300</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B16" s="40" t="s">
+      <c r="B16" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="C16" s="18">
+      <c r="C16" s="16">
         <v>15000000</v>
       </c>
-      <c r="D16" s="26">
+      <c r="D16" s="23">
         <f>D15*C$8</f>
         <v>14000000</v>
       </c>
-      <c r="E16" s="56">
+      <c r="E16" s="48">
         <v>12300000</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B17" s="40" t="s">
+      <c r="B17" s="36" t="s">
         <v>67</v>
       </c>
-      <c r="C17" s="54">
+      <c r="C17" s="51">
         <f>Assumptions!C15</f>
         <v>0.01</v>
       </c>
-      <c r="D17" s="54"/>
-      <c r="E17" s="54"/>
+      <c r="D17" s="51"/>
+      <c r="E17" s="51"/>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B18" s="40" t="s">
+      <c r="B18" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="C18" s="12">
+      <c r="C18" s="10">
         <v>3.7499999999999999E-2</v>
       </c>
-      <c r="D18" s="12">
+      <c r="D18" s="10">
         <v>3.7499999999999999E-2</v>
       </c>
-      <c r="E18" s="12">
+      <c r="E18" s="10">
         <v>3.7499999999999999E-2</v>
       </c>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B19" s="40" t="s">
+      <c r="B19" s="36" t="s">
         <v>66</v>
       </c>
-      <c r="C19" s="54">
+      <c r="C19" s="51">
         <f>Assumptions!C18</f>
         <v>1E-3</v>
       </c>
-      <c r="D19" s="54"/>
-      <c r="E19" s="54"/>
+      <c r="D19" s="51"/>
+      <c r="E19" s="51"/>
     </row>
     <row r="20" spans="2:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B20" s="43" t="s">
+      <c r="B20" s="39" t="s">
         <v>68</v>
       </c>
-      <c r="C20" s="55">
+      <c r="C20" s="52">
         <f>Assumptions!C16+Assumptions!C17</f>
         <v>25000</v>
       </c>
-      <c r="D20" s="55"/>
-      <c r="E20" s="55"/>
+      <c r="D20" s="52"/>
+      <c r="E20" s="52"/>
     </row>
     <row r="21" spans="2:5" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="B21" s="28" t="s">
+      <c r="B21" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="C21" s="29">
+      <c r="C21" s="26">
         <f>C16+C16*($C$17+C18+$C$19)+$C$20</f>
         <v>15752500</v>
       </c>
-      <c r="D21" s="29">
+      <c r="D21" s="26">
         <f t="shared" ref="D21:E21" si="0">D16+D16*($C$17+D18+$C$19)+$C$20</f>
         <v>14704000</v>
       </c>
-      <c r="E21" s="29">
+      <c r="E21" s="26">
         <f t="shared" si="0"/>
         <v>12921550</v>
       </c>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B23" s="37" t="s">
+      <c r="B23" s="33" t="s">
         <v>89</v>
       </c>
     </row>
@@ -1937,201 +1949,201 @@
       <c r="C24" s="5"/>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B25" s="40" t="s">
+      <c r="B25" s="36" t="s">
         <v>70</v>
       </c>
-      <c r="C25" s="30">
+      <c r="C25" s="27">
         <f>Assumptions!$C$9</f>
         <v>2.3E-2</v>
       </c>
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B26" s="41" t="s">
+      <c r="B26" s="37" t="s">
         <v>45</v>
       </c>
-      <c r="C26" s="39">
+      <c r="C26" s="35">
         <f>D16</f>
         <v>14000000</v>
       </c>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B27" s="28" t="s">
+      <c r="B27" s="25" t="s">
         <v>71</v>
       </c>
-      <c r="C27" s="32">
+      <c r="C27" s="59">
         <f>C26*C$25/12</f>
         <v>26833.333333333332</v>
       </c>
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B28" s="7"/>
-      <c r="C28" s="32"/>
+      <c r="C28" s="29"/>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B29" s="40" t="s">
+      <c r="B29" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="C29" s="32">
+      <c r="C29" s="29">
         <f>C$9*C$8</f>
         <v>2000</v>
       </c>
     </row>
     <row r="30" spans="2:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B30" s="43" t="s">
+      <c r="B30" s="39" t="s">
         <v>46</v>
       </c>
-      <c r="C30" s="44">
+      <c r="C30" s="40">
         <f ca="1">(C27*(Other_Annual_Expense_Percent-IF(C$7&gt;=30,4%,0)))</f>
         <v>4964.1666666666661</v>
       </c>
     </row>
     <row r="31" spans="2:5" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="B31" s="28" t="s">
+      <c r="B31" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="C31" s="32">
+      <c r="C31" s="59">
         <f ca="1">C27-C29-C30</f>
         <v>19869.166666666664</v>
       </c>
     </row>
     <row r="32" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B32" s="28" t="s">
+      <c r="B32" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="C32" s="30">
+      <c r="C32" s="60">
         <f>Assumptions!C10</f>
         <v>0.01</v>
       </c>
     </row>
     <row r="34" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B34" s="37" t="s">
+      <c r="B34" s="33" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="36" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B36" s="19" t="s">
+      <c r="B36" s="53" t="s">
         <v>42</v>
       </c>
-      <c r="C36" s="33">
+      <c r="C36" s="30">
         <f>Assumptions!C11</f>
         <v>0.3</v>
       </c>
     </row>
     <row r="37" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B37" s="19" t="s">
+      <c r="B37" s="55" t="s">
         <v>47</v>
       </c>
-      <c r="C37" s="30">
+      <c r="C37" s="56">
         <f>(1+C36)^(1/C10)-1</f>
         <v>1.7644813405053306E-2</v>
       </c>
     </row>
     <row r="38" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B38" s="19" t="s">
+      <c r="B38" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="C38" s="8">
+      <c r="C38" s="57">
         <f>D16*(1+C$36)</f>
         <v>18200000</v>
       </c>
     </row>
     <row r="40" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B40" s="37" t="s">
+      <c r="B40" s="33" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="42" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B42" s="9" t="s">
+      <c r="B42" s="53" t="s">
         <v>39</v>
       </c>
-      <c r="C42" s="47" t="str">
+      <c r="C42" s="43" t="str">
         <f>C14</f>
         <v>Asking Price</v>
       </c>
-      <c r="D42" s="47" t="str">
+      <c r="D42" s="43" t="str">
         <f>D14</f>
         <v>Comparable</v>
       </c>
-      <c r="E42" s="47" t="str">
+      <c r="E42" s="43" t="str">
         <f>E14</f>
         <v>IRR Netural Price</v>
       </c>
     </row>
     <row r="43" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B43" s="19" t="s">
+      <c r="B43" s="53" t="s">
         <v>76</v>
       </c>
-      <c r="C43" s="26">
+      <c r="C43" s="23">
         <f>C16</f>
         <v>15000000</v>
       </c>
-      <c r="D43" s="26">
+      <c r="D43" s="23">
         <f t="shared" ref="D43:E43" si="1">D16</f>
         <v>14000000</v>
       </c>
-      <c r="E43" s="26">
+      <c r="E43" s="23">
         <f t="shared" si="1"/>
         <v>12300000</v>
       </c>
     </row>
     <row r="44" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B44" s="19" t="s">
+      <c r="B44" s="53" t="s">
         <v>69</v>
       </c>
-      <c r="C44" s="31">
+      <c r="C44" s="28">
         <f>C21</f>
         <v>15752500</v>
       </c>
-      <c r="D44" s="31">
+      <c r="D44" s="28">
         <f>D21</f>
         <v>14704000</v>
       </c>
-      <c r="E44" s="31">
+      <c r="E44" s="28">
         <f>E21</f>
         <v>12921550</v>
       </c>
     </row>
     <row r="45" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B45" s="19" t="s">
+      <c r="B45" s="53" t="s">
         <v>49</v>
       </c>
-      <c r="C45" s="52">
+      <c r="C45" s="49">
         <f ca="1">C$31*12</f>
         <v>238429.99999999997</v>
       </c>
-      <c r="D45" s="52"/>
-      <c r="E45" s="52"/>
+      <c r="D45" s="49"/>
+      <c r="E45" s="49"/>
     </row>
     <row r="46" spans="2:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B46" s="36" t="s">
+      <c r="B46" s="54" t="s">
         <v>50</v>
       </c>
-      <c r="C46" s="53">
+      <c r="C46" s="50">
         <f>C$38</f>
         <v>18200000</v>
       </c>
-      <c r="D46" s="53"/>
-      <c r="E46" s="53"/>
+      <c r="D46" s="50"/>
+      <c r="E46" s="50"/>
     </row>
     <row r="47" spans="2:5" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="B47" s="28" t="s">
+      <c r="B47" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="C47" s="27">
+      <c r="C47" s="58">
         <f ca="1">RATE(15, $C45*(1+$C$32), -C44, $C46 / (1+$C$32)^15) + $C$32</f>
         <v>2.4998387525081909E-2</v>
       </c>
-      <c r="D47" s="27">
+      <c r="D47" s="58">
         <f t="shared" ref="D47:E47" ca="1" si="2">RATE(15, $C45*(1+$C$32), -D44, $C46 / (1+$C$32)^15) + $C$32</f>
         <v>3.0196760572581638E-2</v>
       </c>
-      <c r="E47" s="27">
+      <c r="E47" s="58">
         <f t="shared" ca="1" si="2"/>
         <v>4.009247428661733E-2</v>
       </c>
     </row>
     <row r="49" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B49" s="48" t="s">
+      <c r="B49" s="44" t="s">
         <v>78</v>
       </c>
     </row>
@@ -2179,114 +2191,114 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B2" s="49" t="s">
+      <c r="B2" s="45" t="s">
         <v>82</v>
       </c>
-      <c r="C2" s="50"/>
-      <c r="D2" s="49" t="s">
+      <c r="C2" s="46"/>
+      <c r="D2" s="45" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B3" s="50"/>
-      <c r="C3" s="50"/>
-      <c r="D3" s="50"/>
+      <c r="B3" s="46"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
     </row>
     <row r="4" spans="2:4" ht="57" x14ac:dyDescent="0.45">
-      <c r="B4" s="51" t="s">
+      <c r="B4" s="47" t="s">
         <v>105</v>
       </c>
-      <c r="C4" s="50"/>
-      <c r="D4" s="51" t="s">
+      <c r="C4" s="46"/>
+      <c r="D4" s="47" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B5" s="50"/>
-      <c r="C5" s="50"/>
-      <c r="D5" s="50"/>
+      <c r="B5" s="46"/>
+      <c r="C5" s="46"/>
+      <c r="D5" s="46"/>
     </row>
     <row r="6" spans="2:4" ht="128.25" x14ac:dyDescent="0.45">
-      <c r="B6" s="51" t="s">
+      <c r="B6" s="47" t="s">
         <v>91</v>
       </c>
-      <c r="C6" s="50"/>
-      <c r="D6" s="51" t="s">
+      <c r="C6" s="46"/>
+      <c r="D6" s="47" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B7" s="50"/>
-      <c r="C7" s="50"/>
-      <c r="D7" s="50"/>
+      <c r="B7" s="46"/>
+      <c r="C7" s="46"/>
+      <c r="D7" s="46"/>
     </row>
     <row r="8" spans="2:4" ht="85.5" x14ac:dyDescent="0.45">
-      <c r="B8" s="51" t="s">
+      <c r="B8" s="47" t="s">
         <v>93</v>
       </c>
-      <c r="C8" s="50"/>
-      <c r="D8" s="51" t="s">
+      <c r="C8" s="46"/>
+      <c r="D8" s="47" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="9" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B9" s="50"/>
-      <c r="C9" s="50"/>
-      <c r="D9" s="50"/>
+      <c r="B9" s="46"/>
+      <c r="C9" s="46"/>
+      <c r="D9" s="46"/>
     </row>
     <row r="10" spans="2:4" ht="85.5" x14ac:dyDescent="0.45">
-      <c r="B10" s="51" t="s">
+      <c r="B10" s="47" t="s">
         <v>92</v>
       </c>
-      <c r="C10" s="50"/>
-      <c r="D10" s="51" t="s">
+      <c r="C10" s="46"/>
+      <c r="D10" s="47" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="11" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B11" s="50"/>
-      <c r="C11" s="50"/>
-      <c r="D11" s="50"/>
+      <c r="B11" s="46"/>
+      <c r="C11" s="46"/>
+      <c r="D11" s="46"/>
     </row>
     <row r="12" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B12" s="50"/>
-      <c r="C12" s="50"/>
-      <c r="D12" s="50"/>
+      <c r="B12" s="46"/>
+      <c r="C12" s="46"/>
+      <c r="D12" s="46"/>
     </row>
     <row r="13" spans="2:4" ht="71.25" x14ac:dyDescent="0.45">
-      <c r="B13" s="51" t="s">
+      <c r="B13" s="47" t="s">
         <v>86</v>
       </c>
-      <c r="C13" s="50"/>
-      <c r="D13" s="51" t="s">
+      <c r="C13" s="46"/>
+      <c r="D13" s="47" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="14" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B14" s="50"/>
-      <c r="C14" s="50"/>
-      <c r="D14" s="50"/>
+      <c r="B14" s="46"/>
+      <c r="C14" s="46"/>
+      <c r="D14" s="46"/>
     </row>
     <row r="15" spans="2:4" ht="128.25" x14ac:dyDescent="0.45">
-      <c r="B15" s="51" t="s">
+      <c r="B15" s="47" t="s">
         <v>96</v>
       </c>
-      <c r="C15" s="50"/>
-      <c r="D15" s="51" t="s">
+      <c r="C15" s="46"/>
+      <c r="D15" s="47" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="16" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B16" s="50"/>
-      <c r="C16" s="50"/>
-      <c r="D16" s="50"/>
+      <c r="B16" s="46"/>
+      <c r="C16" s="46"/>
+      <c r="D16" s="46"/>
     </row>
     <row r="17" spans="2:4" ht="85.5" x14ac:dyDescent="0.45">
-      <c r="B17" s="51" t="s">
+      <c r="B17" s="47" t="s">
         <v>97</v>
       </c>
-      <c r="C17" s="50"/>
-      <c r="D17" s="51" t="s">
+      <c r="C17" s="46"/>
+      <c r="D17" s="47" t="s">
         <v>104</v>
       </c>
     </row>

--- a/financial_models/Res_Property_Monitor.xlsx
+++ b/financial_models/Res_Property_Monitor.xlsx
@@ -8,14 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8FC238E-F37D-4782-8DCE-FC4A537B4663}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A20BDA1-F1CC-4022-9F7A-1DBDC960EE95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="6150" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Assumptions" sheetId="13" r:id="rId1"/>
-    <sheet name="Model" sheetId="14" r:id="rId2"/>
-    <sheet name="Logic_Summary" sheetId="15" r:id="rId3"/>
+    <sheet name="銀海山莊" sheetId="14" r:id="rId2"/>
+    <sheet name="Quarry bay" sheetId="17" r:id="rId3"/>
+    <sheet name="翠荷苑" sheetId="18" r:id="rId4"/>
+    <sheet name="Logic_Summary" sheetId="15" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="AuraStyleDefaultsReset" hidden="1">#N/A</definedName>
@@ -32,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="115">
   <si>
     <t>Value</t>
   </si>
@@ -164,9 +166,6 @@
   </si>
   <si>
     <t>Sale price after appreciation</t>
-  </si>
-  <si>
-    <t>Test Property</t>
   </si>
   <si>
     <t>Reference market value</t>
@@ -735,6 +734,27 @@
   </si>
   <si>
     <t>typical unlevered hurdle rates range from 4.0%–5.0%</t>
+  </si>
+  <si>
+    <t>銀海山莊</t>
+  </si>
+  <si>
+    <t>差餉</t>
+  </si>
+  <si>
+    <t>Quarry bay</t>
+  </si>
+  <si>
+    <t>翠荷苑</t>
+  </si>
+  <si>
+    <t>Other Costs</t>
+  </si>
+  <si>
+    <t>Maintenance/Repairs/Sinking Fund</t>
+  </si>
+  <si>
+    <t>Old Building Premium Cost</t>
   </si>
 </sst>
 </file>
@@ -881,7 +901,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -934,9 +954,6 @@
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -949,16 +966,10 @@
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1013,6 +1024,38 @@
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="10" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1022,32 +1065,8 @@
     <xf numFmtId="10" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1388,14 +1407,14 @@
   <sheetData>
     <row r="2" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B2" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8"/>
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B4" s="13" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C4" s="12" t="s">
         <v>0</v>
@@ -1409,10 +1428,10 @@
         <v>35</v>
       </c>
       <c r="C5" s="10">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.45">
@@ -1426,7 +1445,7 @@
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B8" s="13" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C8" s="12" t="s">
         <v>0</v>
@@ -1445,28 +1464,28 @@
     </row>
     <row r="10" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C10" s="10">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
-        <v>73</v>
-      </c>
-      <c r="C11" s="38">
+        <v>72</v>
+      </c>
+      <c r="C11" s="35">
         <v>0.3</v>
       </c>
     </row>
     <row r="12" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
-        <v>74</v>
-      </c>
-      <c r="C12" s="24">
+        <v>73</v>
+      </c>
+      <c r="C12" s="23">
         <f>(1+C11)^(1/Holding_Period)-1</f>
         <v>1.7644813405053306E-2</v>
       </c>
@@ -1476,7 +1495,7 @@
     </row>
     <row r="14" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B14" s="13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C14" s="12" t="s">
         <v>0</v>
@@ -1487,40 +1506,40 @@
     </row>
     <row r="15" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C15" s="10">
         <v>0.01</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="16" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C16" s="16">
         <v>20000</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C17" s="16">
         <v>5000</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B18" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C18" s="10">
         <v>1E-3</v>
@@ -1532,7 +1551,7 @@
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B20" s="13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C20" s="12" t="s">
         <v>0</v>
@@ -1548,7 +1567,9 @@
       <c r="C21" s="10">
         <v>5.5E-2</v>
       </c>
-      <c r="D21" s="4"/>
+      <c r="D21" s="4" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="22" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B22" t="s">
@@ -1604,7 +1625,7 @@
       <c r="B28" t="s">
         <v>3</v>
       </c>
-      <c r="C28" s="41">
+      <c r="C28" s="38">
         <v>7.8</v>
       </c>
     </row>
@@ -1612,7 +1633,7 @@
       <c r="B29" t="s">
         <v>4</v>
       </c>
-      <c r="C29" s="41">
+      <c r="C29" s="38">
         <v>0.89</v>
       </c>
     </row>
@@ -1620,7 +1641,7 @@
       <c r="B30" t="s">
         <v>5</v>
       </c>
-      <c r="C30" s="42">
+      <c r="C30" s="39">
         <v>1000</v>
       </c>
     </row>
@@ -1755,29 +1776,29 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:E52"/>
+  <dimension ref="B2:E58"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
-    <col min="2" max="2" width="28.53125" customWidth="1"/>
+    <col min="2" max="2" width="29.86328125" customWidth="1"/>
     <col min="3" max="9" width="16.59765625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B2" s="34" t="s">
-        <v>88</v>
+      <c r="B2" s="31" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B4" s="36" t="s">
+      <c r="B4" s="33" t="s">
         <v>41</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>44</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B5" s="36" t="s">
+      <c r="B5" s="33" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="17" t="s">
@@ -1785,388 +1806,476 @@
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B6" s="36" t="s">
+      <c r="B6" s="33" t="s">
         <v>23</v>
       </c>
       <c r="C6" s="18">
-        <v>2000</v>
+        <v>1997</v>
       </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B7" s="36" t="s">
+      <c r="B7" s="33" t="s">
         <v>33</v>
       </c>
       <c r="C7" s="19">
         <f ca="1">YEAR(TODAY())-C6</f>
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B8" s="36" t="s">
+      <c r="B8" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="C8" s="20">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B9" s="33" t="s">
         <v>83</v>
       </c>
-      <c r="C8" s="20">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B9" s="36" t="s">
-        <v>84</v>
-      </c>
       <c r="C9" s="21">
-        <v>2</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B10" s="36" t="s">
+      <c r="B10" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="22">
+      <c r="C10" s="51">
         <f>Holding_Period</f>
         <v>15</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B12" s="33" t="s">
-        <v>90</v>
+      <c r="B12" s="30" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B14" s="36" t="s">
+      <c r="B14" s="33" t="s">
         <v>39</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>40</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B15" s="37" t="s">
-        <v>85</v>
-      </c>
-      <c r="C15" s="31">
+      <c r="B15" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="C15" s="28">
         <f>C16/C8</f>
-        <v>15000</v>
-      </c>
-      <c r="D15" s="32">
+        <v>18115.942028985508</v>
+      </c>
+      <c r="D15" s="29">
         <v>14000</v>
       </c>
-      <c r="E15" s="31">
+      <c r="E15" s="28">
         <f>E16/C8</f>
-        <v>12300</v>
+        <v>12318.840579710144</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B16" s="36" t="s">
-        <v>52</v>
+      <c r="B16" s="33" t="s">
+        <v>51</v>
       </c>
       <c r="C16" s="16">
-        <v>15000000</v>
-      </c>
-      <c r="D16" s="23">
+        <v>12500000</v>
+      </c>
+      <c r="D16" s="22">
         <f>D15*C$8</f>
-        <v>14000000</v>
-      </c>
-      <c r="E16" s="48">
-        <v>12300000</v>
+        <v>9660000</v>
+      </c>
+      <c r="E16" s="45">
+        <v>8500000</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B17" s="36" t="s">
-        <v>67</v>
-      </c>
-      <c r="C17" s="51">
+      <c r="B17" s="33" t="s">
+        <v>66</v>
+      </c>
+      <c r="C17" s="60">
         <f>Assumptions!C15</f>
         <v>0.01</v>
       </c>
-      <c r="D17" s="51"/>
-      <c r="E17" s="51"/>
+      <c r="D17" s="60"/>
+      <c r="E17" s="60"/>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B18" s="36" t="s">
-        <v>64</v>
+      <c r="B18" s="33" t="s">
+        <v>63</v>
       </c>
       <c r="C18" s="10">
         <v>3.7499999999999999E-2</v>
       </c>
       <c r="D18" s="10">
-        <v>3.7499999999999999E-2</v>
+        <v>3.4500000000000003E-2</v>
       </c>
       <c r="E18" s="10">
-        <v>3.7499999999999999E-2</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B19" s="36" t="s">
-        <v>66</v>
-      </c>
-      <c r="C19" s="51">
+      <c r="B19" s="33" t="s">
+        <v>65</v>
+      </c>
+      <c r="C19" s="60">
         <f>Assumptions!C18</f>
         <v>1E-3</v>
       </c>
-      <c r="D19" s="51"/>
-      <c r="E19" s="51"/>
-    </row>
-    <row r="20" spans="2:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B20" s="39" t="s">
-        <v>68</v>
-      </c>
-      <c r="C20" s="52">
+      <c r="D19" s="60"/>
+      <c r="E19" s="60"/>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B20" s="33" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" s="61">
         <f>Assumptions!C16+Assumptions!C17</f>
         <v>25000</v>
       </c>
-      <c r="D20" s="52"/>
-      <c r="E20" s="52"/>
-    </row>
-    <row r="21" spans="2:5" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="B21" s="25" t="s">
+      <c r="D20" s="61"/>
+      <c r="E20" s="61"/>
+    </row>
+    <row r="21" spans="2:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B21" s="36" t="s">
+        <v>112</v>
+      </c>
+      <c r="C21" s="54">
+        <v>150000</v>
+      </c>
+      <c r="D21" s="54">
+        <v>150000</v>
+      </c>
+      <c r="E21" s="54">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="B22" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="C22" s="25">
+        <f>C16+C16*($C$17+C18+$C$19)+$C$20+C21</f>
+        <v>13281250</v>
+      </c>
+      <c r="D22" s="25">
+        <f t="shared" ref="D22:E22" si="0">D16+D16*($C$17+D18+$C$19)+$C$20+D21</f>
+        <v>10274530</v>
+      </c>
+      <c r="E22" s="25">
+        <f t="shared" si="0"/>
+        <v>9023500</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B24" s="30" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C25" s="5"/>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B26" s="33" t="s">
         <v>69</v>
       </c>
-      <c r="C21" s="26">
-        <f>C16+C16*($C$17+C18+$C$19)+$C$20</f>
-        <v>15752500</v>
-      </c>
-      <c r="D21" s="26">
-        <f t="shared" ref="D21:E21" si="0">D16+D16*($C$17+D18+$C$19)+$C$20</f>
-        <v>14704000</v>
-      </c>
-      <c r="E21" s="26">
-        <f t="shared" si="0"/>
-        <v>12921550</v>
-      </c>
-    </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B23" s="33" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="24" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="C24" s="5"/>
-    </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B25" s="36" t="s">
+      <c r="C26" s="52">
+        <v>2.8000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B27" s="34" t="s">
+        <v>44</v>
+      </c>
+      <c r="C27" s="32">
+        <f>D16</f>
+        <v>9660000</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B28" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="C25" s="27">
-        <f>Assumptions!$C$9</f>
-        <v>2.3E-2</v>
-      </c>
-    </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B26" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="C26" s="35">
-        <f>D16</f>
-        <v>14000000</v>
-      </c>
-    </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B27" s="25" t="s">
-        <v>71</v>
-      </c>
-      <c r="C27" s="59">
-        <f>C26*C$25/12</f>
-        <v>26833.333333333332</v>
-      </c>
-    </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B28" s="7"/>
-      <c r="C28" s="29"/>
+      <c r="C28" s="49">
+        <f>C27*C$26/12</f>
+        <v>22540</v>
+      </c>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B29" s="36" t="s">
+      <c r="B29" s="7"/>
+      <c r="C29" s="27"/>
+    </row>
+    <row r="30" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B30" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="C29" s="29">
+      <c r="C30" s="27">
         <f>C$9*C$8</f>
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="30" spans="2:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B30" s="39" t="s">
-        <v>46</v>
-      </c>
-      <c r="C30" s="40">
-        <f ca="1">(C27*(Other_Annual_Expense_Percent-IF(C$7&gt;=30,4%,0)))</f>
-        <v>4964.1666666666661</v>
-      </c>
-    </row>
-    <row r="31" spans="2:5" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="B31" s="25" t="s">
-        <v>72</v>
-      </c>
-      <c r="C31" s="59">
-        <f ca="1">C27-C29-C30</f>
-        <v>19869.166666666664</v>
+        <v>1725</v>
+      </c>
+      <c r="D30" s="55">
+        <f>C30/C28</f>
+        <v>7.6530612244897961E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B31" s="33" t="s">
+        <v>21</v>
+      </c>
+      <c r="C31" s="27">
+        <f>$C$28*D31</f>
+        <v>1239.7</v>
+      </c>
+      <c r="D31" s="55">
+        <f>Assumptions!C21</f>
+        <v>5.5E-2</v>
       </c>
     </row>
     <row r="32" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B32" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="C32" s="60">
-        <f>Assumptions!C10</f>
-        <v>0.01</v>
+      <c r="B32" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="C32" s="27">
+        <f t="shared" ref="C32:C35" si="1">$C$28*D32</f>
+        <v>676.19999999999993</v>
+      </c>
+      <c r="D32" s="55">
+        <f>Assumptions!C22</f>
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B33" s="33" t="s">
+        <v>113</v>
+      </c>
+      <c r="C33" s="27">
+        <f t="shared" si="1"/>
+        <v>1803.2</v>
+      </c>
+      <c r="D33" s="3">
+        <f>Assumptions!C23</f>
+        <v>0.08</v>
       </c>
     </row>
     <row r="34" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B34" s="33" t="s">
+        <v>114</v>
+      </c>
+      <c r="C34" s="27">
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D34" s="3">
+        <f ca="1">IF(C$7&gt;=30,4%,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B35" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="C35" s="27">
+        <f t="shared" si="1"/>
+        <v>450.8</v>
+      </c>
+      <c r="D35" s="3">
+        <f>Assumptions!C24</f>
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="36" spans="2:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B36" s="36" t="s">
+        <v>45</v>
+      </c>
+      <c r="C36" s="56">
+        <v>0</v>
+      </c>
+      <c r="D36" s="57">
+        <f>C36/C28</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:5" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="B37" s="24" t="s">
+        <v>71</v>
+      </c>
+      <c r="C37" s="49">
+        <f ca="1">C28-SUM(C30:C36)</f>
+        <v>16645.099999999999</v>
+      </c>
+      <c r="D37" s="55">
+        <f ca="1">C37/C28</f>
+        <v>0.73846938775510196</v>
+      </c>
+    </row>
+    <row r="38" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B38" s="24" t="s">
+        <v>50</v>
+      </c>
+      <c r="C38" s="50">
+        <f>Assumptions!C10</f>
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="40" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B40" s="30" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="42" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B42" s="33" t="s">
+        <v>42</v>
+      </c>
+      <c r="C42" s="53">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="43" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B43" s="34" t="s">
+        <v>46</v>
+      </c>
+      <c r="C43" s="46">
+        <f>(1+C42)^(1/C10)-1</f>
+        <v>2.268495988716035E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B44" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="C44" s="47">
+        <f>D16*(1+C$42)</f>
+        <v>13524000</v>
+      </c>
+    </row>
+    <row r="46" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B46" s="30" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B36" s="53" t="s">
-        <v>42</v>
-      </c>
-      <c r="C36" s="30">
-        <f>Assumptions!C11</f>
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B37" s="55" t="s">
-        <v>47</v>
-      </c>
-      <c r="C37" s="56">
-        <f>(1+C36)^(1/C10)-1</f>
-        <v>1.7644813405053306E-2</v>
-      </c>
-    </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B38" s="25" t="s">
-        <v>43</v>
-      </c>
-      <c r="C38" s="57">
-        <f>D16*(1+C$36)</f>
-        <v>18200000</v>
-      </c>
-    </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B40" s="33" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B42" s="53" t="s">
+    <row r="48" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B48" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="C42" s="43" t="str">
+      <c r="C48" s="40" t="str">
         <f>C14</f>
         <v>Asking Price</v>
       </c>
-      <c r="D42" s="43" t="str">
+      <c r="D48" s="40" t="str">
         <f>D14</f>
         <v>Comparable</v>
       </c>
-      <c r="E42" s="43" t="str">
+      <c r="E48" s="40" t="str">
         <f>E14</f>
         <v>IRR Netural Price</v>
       </c>
     </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B43" s="53" t="s">
+    <row r="49" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B49" s="33" t="s">
+        <v>75</v>
+      </c>
+      <c r="C49" s="22">
+        <f>C16</f>
+        <v>12500000</v>
+      </c>
+      <c r="D49" s="22">
+        <f t="shared" ref="D49:E49" si="2">D16</f>
+        <v>9660000</v>
+      </c>
+      <c r="E49" s="22">
+        <f t="shared" si="2"/>
+        <v>8500000</v>
+      </c>
+    </row>
+    <row r="50" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B50" s="33" t="s">
+        <v>68</v>
+      </c>
+      <c r="C50" s="26">
+        <f>C22</f>
+        <v>13281250</v>
+      </c>
+      <c r="D50" s="26">
+        <f>D22</f>
+        <v>10274530</v>
+      </c>
+      <c r="E50" s="26">
+        <f>E22</f>
+        <v>9023500</v>
+      </c>
+    </row>
+    <row r="51" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B51" s="33" t="s">
+        <v>48</v>
+      </c>
+      <c r="C51" s="58">
+        <f ca="1">C$37*12</f>
+        <v>199741.19999999998</v>
+      </c>
+      <c r="D51" s="58"/>
+      <c r="E51" s="58"/>
+    </row>
+    <row r="52" spans="2:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B52" s="36" t="s">
+        <v>49</v>
+      </c>
+      <c r="C52" s="59">
+        <f>C$44</f>
+        <v>13524000</v>
+      </c>
+      <c r="D52" s="59"/>
+      <c r="E52" s="59"/>
+    </row>
+    <row r="53" spans="2:5" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="B53" s="24" t="s">
         <v>76</v>
       </c>
-      <c r="C43" s="23">
-        <f>C16</f>
-        <v>15000000</v>
-      </c>
-      <c r="D43" s="23">
-        <f t="shared" ref="D43:E43" si="1">D16</f>
-        <v>14000000</v>
-      </c>
-      <c r="E43" s="23">
-        <f t="shared" si="1"/>
-        <v>12300000</v>
-      </c>
-    </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B44" s="53" t="s">
-        <v>69</v>
-      </c>
-      <c r="C44" s="28">
-        <f>C21</f>
-        <v>15752500</v>
-      </c>
-      <c r="D44" s="28">
-        <f>D21</f>
-        <v>14704000</v>
-      </c>
-      <c r="E44" s="28">
-        <f>E21</f>
-        <v>12921550</v>
-      </c>
-    </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B45" s="53" t="s">
-        <v>49</v>
-      </c>
-      <c r="C45" s="49">
-        <f ca="1">C$31*12</f>
-        <v>238429.99999999997</v>
-      </c>
-      <c r="D45" s="49"/>
-      <c r="E45" s="49"/>
-    </row>
-    <row r="46" spans="2:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B46" s="54" t="s">
-        <v>50</v>
-      </c>
-      <c r="C46" s="50">
-        <f>C$38</f>
-        <v>18200000</v>
-      </c>
-      <c r="D46" s="50"/>
-      <c r="E46" s="50"/>
-    </row>
-    <row r="47" spans="2:5" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="B47" s="25" t="s">
+      <c r="C53" s="48">
+        <f ca="1">RATE(15, $C51*(1+$C$38), -C50, $C52 / (1+$C$38)^15) + $C$38</f>
+        <v>1.8999155164258121E-2</v>
+      </c>
+      <c r="D53" s="48">
+        <f t="shared" ref="D53:E53" ca="1" si="3">RATE(15, $C51*(1+$C$38), -D50, $C52 / (1+$C$38)^15) + $C$38</f>
+        <v>3.8543863508982534E-2</v>
+      </c>
+      <c r="E53" s="48">
+        <f t="shared" ca="1" si="3"/>
+        <v>4.8742541751567378E-2</v>
+      </c>
+    </row>
+    <row r="55" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B55" s="41" t="s">
         <v>77</v>
       </c>
-      <c r="C47" s="58">
-        <f ca="1">RATE(15, $C45*(1+$C$32), -C44, $C46 / (1+$C$32)^15) + $C$32</f>
-        <v>2.4998387525081909E-2</v>
-      </c>
-      <c r="D47" s="58">
-        <f t="shared" ref="D47:E47" ca="1" si="2">RATE(15, $C45*(1+$C$32), -D44, $C46 / (1+$C$32)^15) + $C$32</f>
-        <v>3.0196760572581638E-2</v>
-      </c>
-      <c r="E47" s="58">
-        <f t="shared" ca="1" si="2"/>
-        <v>4.009247428661733E-2</v>
-      </c>
-    </row>
-    <row r="49" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B49" s="44" t="s">
+    </row>
+    <row r="56" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B56" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="50" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B50" t="s">
+    <row r="57" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B57" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="51" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B51" t="s">
+    <row r="58" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B58" t="s">
         <v>80</v>
-      </c>
-    </row>
-    <row r="52" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B52" t="s">
-        <v>81</v>
       </c>
     </row>
   </sheetData>
   <dataConsolidate/>
   <mergeCells count="5">
-    <mergeCell ref="C45:E45"/>
-    <mergeCell ref="C46:E46"/>
+    <mergeCell ref="C51:E51"/>
+    <mergeCell ref="C52:E52"/>
     <mergeCell ref="C17:E17"/>
     <mergeCell ref="C19:E19"/>
     <mergeCell ref="C20:E20"/>
@@ -2177,6 +2286,885 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{443574DC-9638-4865-B3ED-3B836FA95BE0}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B2:E53"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="2.6640625" customWidth="1"/>
+    <col min="2" max="2" width="28.53125" customWidth="1"/>
+    <col min="3" max="9" width="16.59765625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B2" s="31" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B4" s="33" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B5" s="33" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B6" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="18">
+        <v>2002</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B7" s="33" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="19">
+        <f ca="1">YEAR(TODAY())-C6</f>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B8" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="C8" s="20">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B9" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="C9" s="21">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B10" s="33" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="51">
+        <f>Holding_Period</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B12" s="30" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B14" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B15" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="C15" s="28">
+        <f>C16/C8</f>
+        <v>16082.474226804125</v>
+      </c>
+      <c r="D15" s="29">
+        <v>15500</v>
+      </c>
+      <c r="E15" s="28">
+        <f>E16/C8</f>
+        <v>14538.53385789773</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B16" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16" s="16">
+        <v>7800000</v>
+      </c>
+      <c r="D16" s="22">
+        <f>D15*C$8</f>
+        <v>7517500</v>
+      </c>
+      <c r="E16" s="45">
+        <v>7051188.9210803993</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B17" s="33" t="s">
+        <v>66</v>
+      </c>
+      <c r="C17" s="60">
+        <f>Assumptions!C15</f>
+        <v>0.01</v>
+      </c>
+      <c r="D17" s="60"/>
+      <c r="E17" s="60"/>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B18" s="33" t="s">
+        <v>63</v>
+      </c>
+      <c r="C18" s="10">
+        <v>0.03</v>
+      </c>
+      <c r="D18" s="10">
+        <v>0.03</v>
+      </c>
+      <c r="E18" s="10">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B19" s="33" t="s">
+        <v>65</v>
+      </c>
+      <c r="C19" s="60">
+        <f>Assumptions!C18</f>
+        <v>1E-3</v>
+      </c>
+      <c r="D19" s="60"/>
+      <c r="E19" s="60"/>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B20" s="33" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" s="61">
+        <f>Assumptions!C16+Assumptions!C17</f>
+        <v>25000</v>
+      </c>
+      <c r="D20" s="61"/>
+      <c r="E20" s="61"/>
+    </row>
+    <row r="21" spans="2:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B21" s="36" t="s">
+        <v>112</v>
+      </c>
+      <c r="C21" s="54">
+        <v>0</v>
+      </c>
+      <c r="D21" s="54">
+        <v>0</v>
+      </c>
+      <c r="E21" s="54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="B22" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="C22" s="25">
+        <f>C16+C16*($C$17+C18+$C$19)+$C$20+C21</f>
+        <v>8144800</v>
+      </c>
+      <c r="D22" s="25">
+        <f t="shared" ref="D22:E22" si="0">D16+D16*($C$17+D18+$C$19)+$C$20+D21</f>
+        <v>7850717.5</v>
+      </c>
+      <c r="E22" s="25">
+        <f t="shared" si="0"/>
+        <v>7365287.6668446958</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B24" s="30" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C25" s="5"/>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B26" s="33" t="s">
+        <v>69</v>
+      </c>
+      <c r="C26" s="52">
+        <v>3.1E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B27" s="34" t="s">
+        <v>44</v>
+      </c>
+      <c r="C27" s="32">
+        <f>D16</f>
+        <v>7517500</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B28" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="C28" s="49">
+        <f>C27*C$26/12</f>
+        <v>19420.208333333332</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B29" s="7"/>
+      <c r="C29" s="27"/>
+    </row>
+    <row r="30" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B30" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" s="27">
+        <f>C$9*C$8</f>
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="31" spans="2:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B31" s="36" t="s">
+        <v>45</v>
+      </c>
+      <c r="C31" s="37">
+        <f ca="1">(C28*(Other_Annual_Expense_Percent-IF(C$7&gt;=30,4%,0)))</f>
+        <v>3592.7385416666657</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="B32" s="24" t="s">
+        <v>71</v>
+      </c>
+      <c r="C32" s="49">
+        <f ca="1">C28-C30-C31</f>
+        <v>14760.469791666666</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B33" s="24" t="s">
+        <v>50</v>
+      </c>
+      <c r="C33" s="50">
+        <f>Assumptions!C10</f>
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B35" s="30" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="37" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B37" s="33" t="s">
+        <v>42</v>
+      </c>
+      <c r="C37" s="53">
+        <f>Assumptions!C11</f>
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="38" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B38" s="34" t="s">
+        <v>46</v>
+      </c>
+      <c r="C38" s="46">
+        <f>(1+C37)^(1/C10)-1</f>
+        <v>1.7644813405053306E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B39" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="C39" s="47">
+        <f>D16*(1+C$37)</f>
+        <v>9772750</v>
+      </c>
+    </row>
+    <row r="41" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B41" s="30" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="43" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B43" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="C43" s="40" t="str">
+        <f>C14</f>
+        <v>Asking Price</v>
+      </c>
+      <c r="D43" s="40" t="str">
+        <f>D14</f>
+        <v>Comparable</v>
+      </c>
+      <c r="E43" s="40" t="str">
+        <f>E14</f>
+        <v>IRR Netural Price</v>
+      </c>
+    </row>
+    <row r="44" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B44" s="33" t="s">
+        <v>75</v>
+      </c>
+      <c r="C44" s="22">
+        <f>C16</f>
+        <v>7800000</v>
+      </c>
+      <c r="D44" s="22">
+        <f t="shared" ref="D44:E44" si="1">D16</f>
+        <v>7517500</v>
+      </c>
+      <c r="E44" s="22">
+        <f t="shared" si="1"/>
+        <v>7051188.9210803993</v>
+      </c>
+    </row>
+    <row r="45" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B45" s="33" t="s">
+        <v>68</v>
+      </c>
+      <c r="C45" s="26">
+        <f>C22</f>
+        <v>8144800</v>
+      </c>
+      <c r="D45" s="26">
+        <f>D22</f>
+        <v>7850717.5</v>
+      </c>
+      <c r="E45" s="26">
+        <f>E22</f>
+        <v>7365287.6668446958</v>
+      </c>
+    </row>
+    <row r="46" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B46" s="33" t="s">
+        <v>48</v>
+      </c>
+      <c r="C46" s="58">
+        <f ca="1">C$32*12</f>
+        <v>177125.63750000001</v>
+      </c>
+      <c r="D46" s="58"/>
+      <c r="E46" s="58"/>
+    </row>
+    <row r="47" spans="2:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B47" s="36" t="s">
+        <v>49</v>
+      </c>
+      <c r="C47" s="59">
+        <f>C$39</f>
+        <v>9772750</v>
+      </c>
+      <c r="D47" s="59"/>
+      <c r="E47" s="59"/>
+    </row>
+    <row r="48" spans="2:5" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="B48" s="24" t="s">
+        <v>76</v>
+      </c>
+      <c r="C48" s="48">
+        <f ca="1">RATE(15, $C46*(1+$C$33), -C45, $C47 / (1+$C$33)^15) + $C$33</f>
+        <v>3.5712756815729746E-2</v>
+      </c>
+      <c r="D48" s="48">
+        <f t="shared" ref="D48:E48" ca="1" si="2">RATE(15, $C46*(1+$C$33), -D45, $C47 / (1+$C$33)^15) + $C$33</f>
+        <v>3.8628303343988556E-2</v>
+      </c>
+      <c r="E48" s="48">
+        <f t="shared" ca="1" si="2"/>
+        <v>4.3735038261089168E-2</v>
+      </c>
+    </row>
+    <row r="50" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B50" s="41" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="51" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B51" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="52" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B52" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="53" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B53" t="s">
+        <v>80</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataConsolidate/>
+  <mergeCells count="5">
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="C46:E46"/>
+    <mergeCell ref="C47:E47"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="97" fitToWidth="0" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D09B748-33FA-4405-BB75-AAF1632A9069}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B2:E53"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="2.6640625" customWidth="1"/>
+    <col min="2" max="2" width="28.53125" customWidth="1"/>
+    <col min="3" max="9" width="16.59765625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B2" s="31" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B4" s="33" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B5" s="33" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B6" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="18">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B7" s="33" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="19">
+        <f ca="1">YEAR(TODAY())-C6</f>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B8" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="C8" s="20">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B9" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="C9" s="21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B10" s="33" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="51">
+        <f>Holding_Period</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B12" s="30" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B14" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B15" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="C15" s="28">
+        <f>C16/C8</f>
+        <v>13587.301587301587</v>
+      </c>
+      <c r="D15" s="29">
+        <v>13587</v>
+      </c>
+      <c r="E15" s="28">
+        <f>E16/C8</f>
+        <v>12262.119150039165</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B16" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16" s="16">
+        <v>4280000</v>
+      </c>
+      <c r="D16" s="22">
+        <f>D15*C$8</f>
+        <v>4279905</v>
+      </c>
+      <c r="E16" s="45">
+        <v>3862567.5322623369</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B17" s="33" t="s">
+        <v>66</v>
+      </c>
+      <c r="C17" s="60">
+        <f>Assumptions!C15</f>
+        <v>0.01</v>
+      </c>
+      <c r="D17" s="60"/>
+      <c r="E17" s="60"/>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B18" s="33" t="s">
+        <v>63</v>
+      </c>
+      <c r="C18" s="10">
+        <v>5.5E-2</v>
+      </c>
+      <c r="D18" s="10">
+        <f>C18</f>
+        <v>5.5E-2</v>
+      </c>
+      <c r="E18" s="10">
+        <f>D18</f>
+        <v>5.5E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B19" s="33" t="s">
+        <v>65</v>
+      </c>
+      <c r="C19" s="60">
+        <f>Assumptions!C18</f>
+        <v>1E-3</v>
+      </c>
+      <c r="D19" s="60"/>
+      <c r="E19" s="60"/>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B20" s="33" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" s="61">
+        <f>Assumptions!C16+Assumptions!C17</f>
+        <v>25000</v>
+      </c>
+      <c r="D20" s="61"/>
+      <c r="E20" s="61"/>
+    </row>
+    <row r="21" spans="2:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B21" s="36" t="s">
+        <v>112</v>
+      </c>
+      <c r="C21" s="54">
+        <v>135000</v>
+      </c>
+      <c r="D21" s="54">
+        <v>135000</v>
+      </c>
+      <c r="E21" s="54">
+        <v>135000</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="B22" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="C22" s="25">
+        <f>C16+C16*($C$17+C18+$C$19)+$C$20+C21</f>
+        <v>4722480</v>
+      </c>
+      <c r="D22" s="25">
+        <f t="shared" ref="D22:E22" si="0">D16+D16*($C$17+D18+$C$19)+$C$20+D21</f>
+        <v>4722378.7300000004</v>
+      </c>
+      <c r="E22" s="25">
+        <f t="shared" si="0"/>
+        <v>4277496.989391651</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B24" s="30" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C25" s="5"/>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B26" s="33" t="s">
+        <v>69</v>
+      </c>
+      <c r="C26" s="52">
+        <v>4.2057008274716381E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B27" s="34" t="s">
+        <v>44</v>
+      </c>
+      <c r="C27" s="32">
+        <f>D16</f>
+        <v>4279905</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B28" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="C28" s="49">
+        <f>C27*C$26/12</f>
+        <v>15000.000000000002</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B29" s="7"/>
+      <c r="C29" s="27"/>
+    </row>
+    <row r="30" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B30" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" s="27">
+        <f>C$9*C$8</f>
+        <v>630</v>
+      </c>
+    </row>
+    <row r="31" spans="2:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B31" s="36" t="s">
+        <v>45</v>
+      </c>
+      <c r="C31" s="37">
+        <f ca="1">(C28*(Other_Annual_Expense_Percent-IF(C$7&gt;=30,4%,0)))</f>
+        <v>2174.9999999999995</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="B32" s="24" t="s">
+        <v>71</v>
+      </c>
+      <c r="C32" s="49">
+        <f ca="1">C28-C30-C31</f>
+        <v>12195.000000000002</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B33" s="24" t="s">
+        <v>50</v>
+      </c>
+      <c r="C33" s="50">
+        <f>Assumptions!C10</f>
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B35" s="30" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="37" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B37" s="33" t="s">
+        <v>42</v>
+      </c>
+      <c r="C37" s="53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B38" s="34" t="s">
+        <v>46</v>
+      </c>
+      <c r="C38" s="46">
+        <f>(1+C37)^(1/C10)-1</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B39" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="C39" s="47">
+        <f>D16*(1+C$37)</f>
+        <v>4279905</v>
+      </c>
+    </row>
+    <row r="41" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B41" s="30" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="43" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B43" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="C43" s="40" t="str">
+        <f>C14</f>
+        <v>Asking Price</v>
+      </c>
+      <c r="D43" s="40" t="str">
+        <f>D14</f>
+        <v>Comparable</v>
+      </c>
+      <c r="E43" s="40" t="str">
+        <f>E14</f>
+        <v>IRR Netural Price</v>
+      </c>
+    </row>
+    <row r="44" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B44" s="33" t="s">
+        <v>75</v>
+      </c>
+      <c r="C44" s="22">
+        <f>C16</f>
+        <v>4280000</v>
+      </c>
+      <c r="D44" s="22">
+        <f t="shared" ref="D44:E44" si="1">D16</f>
+        <v>4279905</v>
+      </c>
+      <c r="E44" s="22">
+        <f t="shared" si="1"/>
+        <v>3862567.5322623369</v>
+      </c>
+    </row>
+    <row r="45" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B45" s="33" t="s">
+        <v>68</v>
+      </c>
+      <c r="C45" s="26">
+        <f>C22</f>
+        <v>4722480</v>
+      </c>
+      <c r="D45" s="26">
+        <f>D22</f>
+        <v>4722378.7300000004</v>
+      </c>
+      <c r="E45" s="26">
+        <f>E22</f>
+        <v>4277496.989391651</v>
+      </c>
+    </row>
+    <row r="46" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B46" s="33" t="s">
+        <v>48</v>
+      </c>
+      <c r="C46" s="58">
+        <f ca="1">C$32*12</f>
+        <v>146340.00000000003</v>
+      </c>
+      <c r="D46" s="58"/>
+      <c r="E46" s="58"/>
+    </row>
+    <row r="47" spans="2:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B47" s="36" t="s">
+        <v>49</v>
+      </c>
+      <c r="C47" s="59">
+        <f>C$39</f>
+        <v>4279905</v>
+      </c>
+      <c r="D47" s="59"/>
+      <c r="E47" s="59"/>
+    </row>
+    <row r="48" spans="2:5" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="B48" s="24" t="s">
+        <v>76</v>
+      </c>
+      <c r="C48" s="48">
+        <f ca="1">RATE(15, $C46*(1+$C$33), -C45, $C47 / (1+$C$33)^15) + $C$33</f>
+        <v>3.1538049414762341E-2</v>
+      </c>
+      <c r="D48" s="48">
+        <f t="shared" ref="D48:E48" ca="1" si="2">RATE(15, $C46*(1+$C$33), -D45, $C47 / (1+$C$33)^15) + $C$33</f>
+        <v>3.153987598185972E-2</v>
+      </c>
+      <c r="E48" s="48">
+        <f t="shared" ca="1" si="2"/>
+        <v>4.006688888639906E-2</v>
+      </c>
+    </row>
+    <row r="50" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B50" s="41" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="51" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B51" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="52" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B52" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="53" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B53" t="s">
+        <v>80</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataConsolidate/>
+  <mergeCells count="5">
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="C46:E46"/>
+    <mergeCell ref="C47:E47"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="94" fitToWidth="0" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45BF1B36-25FE-4F70-8854-2FC395D8FBE5}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -2191,115 +3179,115 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B2" s="45" t="s">
-        <v>82</v>
-      </c>
-      <c r="C2" s="46"/>
-      <c r="D2" s="45" t="s">
+      <c r="B2" s="42" t="s">
+        <v>81</v>
+      </c>
+      <c r="C2" s="43"/>
+      <c r="D2" s="42" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B3" s="43"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
+    </row>
+    <row r="4" spans="2:4" ht="57" x14ac:dyDescent="0.45">
+      <c r="B4" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="C4" s="43"/>
+      <c r="D4" s="44" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B5" s="43"/>
+      <c r="C5" s="43"/>
+      <c r="D5" s="43"/>
+    </row>
+    <row r="6" spans="2:4" ht="128.25" x14ac:dyDescent="0.45">
+      <c r="B6" s="44" t="s">
+        <v>90</v>
+      </c>
+      <c r="C6" s="43"/>
+      <c r="D6" s="44" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B3" s="46"/>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
-    </row>
-    <row r="4" spans="2:4" ht="57" x14ac:dyDescent="0.45">
-      <c r="B4" s="47" t="s">
-        <v>105</v>
-      </c>
-      <c r="C4" s="46"/>
-      <c r="D4" s="47" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B5" s="46"/>
-      <c r="C5" s="46"/>
-      <c r="D5" s="46"/>
-    </row>
-    <row r="6" spans="2:4" ht="128.25" x14ac:dyDescent="0.45">
-      <c r="B6" s="47" t="s">
+    <row r="7" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B7" s="43"/>
+      <c r="C7" s="43"/>
+      <c r="D7" s="43"/>
+    </row>
+    <row r="8" spans="2:4" ht="85.5" x14ac:dyDescent="0.45">
+      <c r="B8" s="44" t="s">
+        <v>92</v>
+      </c>
+      <c r="C8" s="43"/>
+      <c r="D8" s="44" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B9" s="43"/>
+      <c r="C9" s="43"/>
+      <c r="D9" s="43"/>
+    </row>
+    <row r="10" spans="2:4" ht="85.5" x14ac:dyDescent="0.45">
+      <c r="B10" s="44" t="s">
         <v>91</v>
       </c>
-      <c r="C6" s="46"/>
-      <c r="D6" s="47" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B7" s="46"/>
-      <c r="C7" s="46"/>
-      <c r="D7" s="46"/>
-    </row>
-    <row r="8" spans="2:4" ht="85.5" x14ac:dyDescent="0.45">
-      <c r="B8" s="47" t="s">
-        <v>93</v>
-      </c>
-      <c r="C8" s="46"/>
-      <c r="D8" s="47" t="s">
+      <c r="C10" s="43"/>
+      <c r="D10" s="44" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B9" s="46"/>
-      <c r="C9" s="46"/>
-      <c r="D9" s="46"/>
-    </row>
-    <row r="10" spans="2:4" ht="85.5" x14ac:dyDescent="0.45">
-      <c r="B10" s="47" t="s">
-        <v>92</v>
-      </c>
-      <c r="C10" s="46"/>
-      <c r="D10" s="47" t="s">
+    <row r="11" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B11" s="43"/>
+      <c r="C11" s="43"/>
+      <c r="D11" s="43"/>
+    </row>
+    <row r="12" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B12" s="43"/>
+      <c r="C12" s="43"/>
+      <c r="D12" s="43"/>
+    </row>
+    <row r="13" spans="2:4" ht="71.25" x14ac:dyDescent="0.45">
+      <c r="B13" s="44" t="s">
+        <v>85</v>
+      </c>
+      <c r="C13" s="43"/>
+      <c r="D13" s="44" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B11" s="46"/>
-      <c r="C11" s="46"/>
-      <c r="D11" s="46"/>
-    </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B12" s="46"/>
-      <c r="C12" s="46"/>
-      <c r="D12" s="46"/>
-    </row>
-    <row r="13" spans="2:4" ht="71.25" x14ac:dyDescent="0.45">
-      <c r="B13" s="47" t="s">
-        <v>86</v>
-      </c>
-      <c r="C13" s="46"/>
-      <c r="D13" s="47" t="s">
+    <row r="14" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B14" s="43"/>
+      <c r="C14" s="43"/>
+      <c r="D14" s="43"/>
+    </row>
+    <row r="15" spans="2:4" ht="128.25" x14ac:dyDescent="0.45">
+      <c r="B15" s="44" t="s">
+        <v>95</v>
+      </c>
+      <c r="C15" s="43"/>
+      <c r="D15" s="44" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B14" s="46"/>
-      <c r="C14" s="46"/>
-      <c r="D14" s="46"/>
-    </row>
-    <row r="15" spans="2:4" ht="128.25" x14ac:dyDescent="0.45">
-      <c r="B15" s="47" t="s">
+    <row r="16" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B16" s="43"/>
+      <c r="C16" s="43"/>
+      <c r="D16" s="43"/>
+    </row>
+    <row r="17" spans="2:4" ht="85.5" x14ac:dyDescent="0.45">
+      <c r="B17" s="44" t="s">
         <v>96</v>
       </c>
-      <c r="C15" s="46"/>
-      <c r="D15" s="47" t="s">
+      <c r="C17" s="43"/>
+      <c r="D17" s="44" t="s">
         <v>103</v>
-      </c>
-    </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B16" s="46"/>
-      <c r="C16" s="46"/>
-      <c r="D16" s="46"/>
-    </row>
-    <row r="17" spans="2:4" ht="85.5" x14ac:dyDescent="0.45">
-      <c r="B17" s="47" t="s">
-        <v>97</v>
-      </c>
-      <c r="C17" s="46"/>
-      <c r="D17" s="47" t="s">
-        <v>104</v>
       </c>
     </row>
   </sheetData>

--- a/financial_models/Res_Property_Monitor.xlsx
+++ b/financial_models/Res_Property_Monitor.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A20BDA1-F1CC-4022-9F7A-1DBDC960EE95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB076F1C-585D-4606-BF52-BDEB9E366D62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="6150" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,10 +22,10 @@
   <definedNames>
     <definedName name="AuraStyleDefaultsReset" hidden="1">#N/A</definedName>
     <definedName name="Cap_Rate">Assumptions!$C$5</definedName>
-    <definedName name="HKDCNY">Assumptions!$C$29</definedName>
-    <definedName name="HKDUSD">Assumptions!$C$28</definedName>
+    <definedName name="HKDCNY">Assumptions!$C$21</definedName>
+    <definedName name="HKDUSD">Assumptions!$C$20</definedName>
     <definedName name="Holding_Period">Assumptions!$C$6</definedName>
-    <definedName name="Other_Annual_Expense_Percent">Assumptions!$C$25</definedName>
+    <definedName name="Other_Annual_Expense_Percent">Assumptions!#REF!</definedName>
     <definedName name="WW3f877d8e32714ec8a8180854ed7f8276_634328481945590045" hidden="1">#REF!</definedName>
     <definedName name="WW3f877d8e32714ec8a8180854ed7f8276_634328482352282765" hidden="1">#REF!</definedName>
   </definedNames>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="109">
   <si>
     <t>Value</t>
   </si>
@@ -51,9 +51,6 @@
     <t>HKDCNY</t>
   </si>
   <si>
-    <t>Scaling Factor</t>
-  </si>
-  <si>
     <t>Type</t>
   </si>
   <si>
@@ -138,18 +135,9 @@
     <t>Age</t>
   </si>
   <si>
-    <t>If house is built over 30 yrs, then increase to 12%</t>
-  </si>
-  <si>
     <t>Hurdle Cap Rate</t>
   </si>
   <si>
-    <t>Other Annual Expense %</t>
-  </si>
-  <si>
-    <t>Gross Rental Yield Reference</t>
-  </si>
-  <si>
     <t>Holding Period</t>
   </si>
   <si>
@@ -192,18 +180,12 @@
     <t>Price (HKD)</t>
   </si>
   <si>
-    <t>Market Specific Parameters</t>
-  </si>
-  <si>
     <t>Assumptions</t>
   </si>
   <si>
     <t>Investor Preference</t>
   </si>
   <si>
-    <t>Transaction Cost Breakdown</t>
-  </si>
-  <si>
     <t>Legal Fee</t>
   </si>
   <si>
@@ -237,9 +219,6 @@
     <t>Agency Commissions %</t>
   </si>
   <si>
-    <t>Legal + Inspection Fees</t>
-  </si>
-  <si>
     <t>Total Consideration</t>
   </si>
   <si>
@@ -250,12 +229,6 @@
   </si>
   <si>
     <t>Monthly NOI (HKD)</t>
-  </si>
-  <si>
-    <t>Expected Appreciation after holding period</t>
-  </si>
-  <si>
-    <t>Expected Price CAGR</t>
   </si>
   <si>
     <t>Exp. Annual Rental Growth rate</t>
@@ -756,6 +729,15 @@
   <si>
     <t>Old Building Premium Cost</t>
   </si>
+  <si>
+    <t>Legal</t>
+  </si>
+  <si>
+    <t>Inspection Fees</t>
+  </si>
+  <si>
+    <t>Default Transaction Cost</t>
+  </si>
 </sst>
 </file>
 
@@ -766,7 +748,7 @@
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="166" formatCode="#,##0&quot;yrs&quot;"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -838,14 +820,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -901,7 +875,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -930,12 +904,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -955,9 +923,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -991,9 +956,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1001,9 +963,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1065,7 +1024,13 @@
     <xf numFmtId="10" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1396,7 +1361,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:D58"/>
+  <dimension ref="B2:D49"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="2.59765625" customWidth="1"/>
@@ -1407,14 +1372,14 @@
   <sheetData>
     <row r="2" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B2" s="9" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8"/>
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B4" s="13" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C4" s="12" t="s">
         <v>0</v>
@@ -1425,344 +1390,270 @@
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C5" s="10">
         <v>0.04</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B6" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C6" s="11">
         <v>15</v>
       </c>
       <c r="D6" s="4"/>
     </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C7" s="10">
+        <v>0.02</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>77</v>
+      </c>
+    </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B8" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="3"/>
+    </row>
+    <row r="9" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B9" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="C9" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D9" s="12" t="s">
         <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B9" t="s">
-        <v>37</v>
-      </c>
-      <c r="C9" s="10">
-        <v>2.3E-2</v>
       </c>
     </row>
     <row r="10" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="C10" s="10">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>86</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
-        <v>72</v>
-      </c>
-      <c r="C11" s="35">
-        <v>0.3</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="C11" s="10">
+        <v>1E-3</v>
+      </c>
+      <c r="D11" s="4"/>
     </row>
     <row r="12" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
-        <v>73</v>
-      </c>
-      <c r="C12" s="23">
-        <f>(1+C11)^(1/Holding_Period)-1</f>
-        <v>1.7644813405053306E-2</v>
+        <v>50</v>
+      </c>
+      <c r="C12" s="14">
+        <v>20000</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="13" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="C13" s="3"/>
+      <c r="B13" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" s="14">
+        <v>5000</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="14" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B14" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="3"/>
+    </row>
+    <row r="15" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B15" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D15" s="12" t="s">
         <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B15" t="s">
-        <v>57</v>
-      </c>
-      <c r="C15" s="10">
-        <v>0.01</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="16" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
-        <v>56</v>
-      </c>
-      <c r="C16" s="16">
-        <v>20000</v>
+        <v>20</v>
+      </c>
+      <c r="C16" s="10">
+        <v>5.5E-2</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>59</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B17" t="s">
-        <v>60</v>
-      </c>
-      <c r="C17" s="16">
-        <v>5000</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B18" t="s">
-        <v>61</v>
-      </c>
-      <c r="C18" s="10">
-        <v>1E-3</v>
-      </c>
-      <c r="D18" s="4"/>
+        <v>26</v>
+      </c>
+      <c r="C17" s="10">
+        <v>0.03</v>
+      </c>
+      <c r="D17" s="4"/>
     </row>
     <row r="19" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="C19" s="3"/>
+      <c r="B19" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B20" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="C20" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D20" s="12" t="s">
-        <v>1</v>
+      <c r="B20" t="s">
+        <v>3</v>
+      </c>
+      <c r="C20" s="34">
+        <v>7.8</v>
       </c>
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C21" s="10">
-        <v>5.5E-2</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B22" t="s">
-        <v>27</v>
-      </c>
-      <c r="C22" s="10">
-        <v>0.03</v>
-      </c>
-      <c r="D22" s="4"/>
+        <v>4</v>
+      </c>
+      <c r="C21" s="34">
+        <v>0.89</v>
+      </c>
     </row>
     <row r="23" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B23" t="s">
-        <v>14</v>
-      </c>
-      <c r="C23" s="10">
-        <v>0.08</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>34</v>
+      <c r="B23" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="24" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B24" t="s">
-        <v>17</v>
-      </c>
-      <c r="C24" s="10">
-        <v>0.02</v>
-      </c>
-      <c r="D24" s="4"/>
+        <v>29</v>
+      </c>
     </row>
     <row r="25" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B25" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="C25" s="15">
-        <f>SUM(C21:C24)</f>
-        <v>0.18499999999999997</v>
-      </c>
-      <c r="D25" s="4"/>
+      <c r="B25" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="27" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B27" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="C27" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D27" s="12" t="s">
-        <v>1</v>
+      <c r="B27" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="28" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B28" t="s">
-        <v>3</v>
-      </c>
-      <c r="C28" s="38">
-        <v>7.8</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B29" t="s">
-        <v>4</v>
-      </c>
-      <c r="C29" s="38">
-        <v>0.89</v>
+        <v>9</v>
+      </c>
+      <c r="C29" s="2">
+        <v>0.05</v>
       </c>
     </row>
     <row r="30" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B30" t="s">
-        <v>5</v>
-      </c>
-      <c r="C30" s="39">
-        <v>1000</v>
+        <v>10</v>
+      </c>
+      <c r="C30" s="2">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="31" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B31" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="2">
+        <v>0.12</v>
       </c>
     </row>
     <row r="32" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B32" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B33" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="34" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B34" t="s">
+      <c r="B32" t="s">
+        <v>21</v>
+      </c>
+      <c r="C32" s="2"/>
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B34" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B35" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="36" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B36" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="37" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B37" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="38" spans="2:3" x14ac:dyDescent="0.45">
+    <row r="37" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B37" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="38" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B38" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="2">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="39" spans="2:3" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="39" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B39" t="s">
-        <v>11</v>
-      </c>
-      <c r="C39" s="2">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="40" spans="2:3" x14ac:dyDescent="0.45">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="40" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B40" t="s">
-        <v>12</v>
-      </c>
-      <c r="C40" s="2">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="41" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B41" t="s">
-        <v>22</v>
-      </c>
-      <c r="C41" s="2"/>
-    </row>
-    <row r="43" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B43" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="44" spans="2:3" x14ac:dyDescent="0.45">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B42" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="43" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B43" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="44" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B44" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="46" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B46" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="47" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B47" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="48" spans="2:3" x14ac:dyDescent="0.45">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="45" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B45" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="47" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B47" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="48" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B48" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
     </row>
     <row r="49" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B49" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="51" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B51" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="52" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B52" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="53" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B53" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="54" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B54" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="56" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B56" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="57" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B57" t="s">
         <v>25</v>
-      </c>
-    </row>
-    <row r="58" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B58" t="s">
-        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -1776,7 +1667,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:E58"/>
+  <dimension ref="B2:E59"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
@@ -1785,500 +1676,510 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B2" s="31" t="s">
-        <v>87</v>
+      <c r="B2" s="28" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B4" s="33" t="s">
-        <v>41</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>108</v>
+      <c r="B4" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B5" s="33" t="s">
+      <c r="B5" s="30" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="17" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B6" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="18">
+      <c r="B6" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="16">
         <v>1997</v>
       </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B7" s="33" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7" s="19">
+      <c r="B7" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="17">
         <f ca="1">YEAR(TODAY())-C6</f>
         <v>29</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B8" s="33" t="s">
-        <v>82</v>
-      </c>
-      <c r="C8" s="20">
+      <c r="B8" s="30" t="s">
+        <v>73</v>
+      </c>
+      <c r="C8" s="18">
         <v>690</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B9" s="33" t="s">
-        <v>83</v>
-      </c>
-      <c r="C9" s="21">
+      <c r="B9" s="30" t="s">
+        <v>74</v>
+      </c>
+      <c r="C9" s="19">
         <v>2.5</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B10" s="33" t="s">
-        <v>38</v>
-      </c>
-      <c r="C10" s="51">
+      <c r="B10" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="46">
         <f>Holding_Period</f>
         <v>15</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B12" s="30" t="s">
-        <v>89</v>
+      <c r="B12" s="27" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B14" s="33" t="s">
-        <v>39</v>
+      <c r="B14" s="30" t="s">
+        <v>35</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B15" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="C15" s="28">
+      <c r="B15" s="31" t="s">
+        <v>75</v>
+      </c>
+      <c r="C15" s="25">
         <f>C16/C8</f>
         <v>18115.942028985508</v>
       </c>
-      <c r="D15" s="29">
+      <c r="D15" s="26">
         <v>14000</v>
       </c>
-      <c r="E15" s="28">
+      <c r="E15" s="25">
         <f>E16/C8</f>
         <v>12318.840579710144</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B16" s="33" t="s">
-        <v>51</v>
-      </c>
-      <c r="C16" s="16">
+      <c r="B16" s="30" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" s="14">
         <v>12500000</v>
       </c>
-      <c r="D16" s="22">
+      <c r="D16" s="20">
         <f>D15*C$8</f>
         <v>9660000</v>
       </c>
-      <c r="E16" s="45">
+      <c r="E16" s="40">
         <v>8500000</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B17" s="33" t="s">
-        <v>66</v>
-      </c>
-      <c r="C17" s="60">
-        <f>Assumptions!C15</f>
+      <c r="B17" s="30" t="s">
+        <v>60</v>
+      </c>
+      <c r="C17" s="58">
+        <f>Assumptions!C10</f>
         <v>0.01</v>
       </c>
-      <c r="D17" s="60"/>
-      <c r="E17" s="60"/>
+      <c r="D17" s="58"/>
+      <c r="E17" s="58"/>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B18" s="33" t="s">
-        <v>63</v>
-      </c>
-      <c r="C18" s="10">
+      <c r="B18" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="C18" s="57">
         <v>3.7499999999999999E-2</v>
       </c>
-      <c r="D18" s="10">
+      <c r="D18" s="57">
         <v>3.4500000000000003E-2</v>
       </c>
-      <c r="E18" s="10">
+      <c r="E18" s="57">
         <v>0.03</v>
       </c>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B19" s="33" t="s">
-        <v>65</v>
-      </c>
-      <c r="C19" s="60">
-        <f>Assumptions!C18</f>
+      <c r="B19" s="30" t="s">
+        <v>59</v>
+      </c>
+      <c r="C19" s="55">
+        <f>Assumptions!C11</f>
         <v>1E-3</v>
       </c>
-      <c r="D19" s="60"/>
-      <c r="E19" s="60"/>
+      <c r="D19" s="55"/>
+      <c r="E19" s="55"/>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B20" s="33" t="s">
-        <v>67</v>
-      </c>
-      <c r="C20" s="61">
-        <f>Assumptions!C16+Assumptions!C17</f>
-        <v>25000</v>
-      </c>
-      <c r="D20" s="61"/>
-      <c r="E20" s="61"/>
-    </row>
-    <row r="21" spans="2:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B21" s="36" t="s">
-        <v>112</v>
-      </c>
-      <c r="C21" s="54">
+      <c r="B20" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="C20" s="56">
+        <f>Assumptions!C12</f>
+        <v>20000</v>
+      </c>
+      <c r="D20" s="56"/>
+      <c r="E20" s="56"/>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B21" s="30" t="s">
+        <v>107</v>
+      </c>
+      <c r="C21" s="56">
+        <f>Assumptions!C13</f>
+        <v>5000</v>
+      </c>
+      <c r="D21" s="56"/>
+      <c r="E21" s="56"/>
+    </row>
+    <row r="22" spans="2:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B22" s="32" t="s">
+        <v>103</v>
+      </c>
+      <c r="C22" s="49">
         <v>150000</v>
       </c>
-      <c r="D21" s="54">
+      <c r="D22" s="49">
         <v>150000</v>
       </c>
-      <c r="E21" s="54">
+      <c r="E22" s="49">
         <v>150000</v>
       </c>
     </row>
-    <row r="22" spans="2:5" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="B22" s="24" t="s">
-        <v>68</v>
-      </c>
-      <c r="C22" s="25">
-        <f>C16+C16*($C$17+C18+$C$19)+$C$20+C21</f>
+    <row r="23" spans="2:5" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="B23" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="C23" s="22">
+        <f>C16+C16*($C$17+C18+$C$19)+$C$20+$C$21+C22</f>
         <v>13281250</v>
       </c>
-      <c r="D22" s="25">
-        <f t="shared" ref="D22:E22" si="0">D16+D16*($C$17+D18+$C$19)+$C$20+D21</f>
+      <c r="D23" s="22">
+        <f t="shared" ref="D23:E23" si="0">D16+D16*($C$17+D18+$C$19)+$C$20+$C$21+D22</f>
         <v>10274530</v>
       </c>
-      <c r="E22" s="25">
+      <c r="E23" s="22">
         <f t="shared" si="0"/>
         <v>9023500</v>
       </c>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B24" s="30" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="25" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="C25" s="5"/>
-    </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B26" s="33" t="s">
-        <v>69</v>
-      </c>
-      <c r="C26" s="52">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B25" s="27" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C26" s="5"/>
+    </row>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B27" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="C27" s="47">
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B27" s="34" t="s">
-        <v>44</v>
-      </c>
-      <c r="C27" s="32">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B28" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="C28" s="29">
         <f>D16</f>
         <v>9660000</v>
       </c>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B28" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="C28" s="49">
-        <f>C27*C$26/12</f>
+    <row r="29" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B29" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="C29" s="44">
+        <f>C28*C$27/12</f>
         <v>22540</v>
       </c>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B29" s="7"/>
-      <c r="C29" s="27"/>
-    </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B30" s="33" t="s">
-        <v>8</v>
-      </c>
-      <c r="C30" s="27">
+      <c r="B30" s="7"/>
+      <c r="C30" s="24"/>
+    </row>
+    <row r="31" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B31" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="24">
         <f>C$9*C$8</f>
         <v>1725</v>
       </c>
-      <c r="D30" s="55">
-        <f>C30/C28</f>
+      <c r="D31" s="50">
+        <f>C31/C29</f>
         <v>7.6530612244897961E-2</v>
       </c>
     </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B31" s="33" t="s">
-        <v>21</v>
-      </c>
-      <c r="C31" s="27">
-        <f>$C$28*D31</f>
+    <row r="32" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B32" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="C32" s="24">
+        <f>$C$29*D32</f>
         <v>1239.7</v>
       </c>
-      <c r="D31" s="55">
-        <f>Assumptions!C21</f>
+      <c r="D32" s="50">
+        <f>Assumptions!C16</f>
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B32" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="C32" s="27">
-        <f t="shared" ref="C32:C35" si="1">$C$28*D32</f>
+    <row r="33" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B33" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="C33" s="24">
+        <f t="shared" ref="C33:C36" si="1">$C$29*D33</f>
         <v>676.19999999999993</v>
       </c>
-      <c r="D32" s="55">
-        <f>Assumptions!C22</f>
+      <c r="D33" s="50">
+        <f>Assumptions!C17</f>
         <v>0.03</v>
       </c>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B33" s="33" t="s">
-        <v>113</v>
-      </c>
-      <c r="C33" s="27">
+    <row r="34" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B34" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="C34" s="24">
         <f t="shared" si="1"/>
         <v>1803.2</v>
       </c>
-      <c r="D33" s="3">
-        <f>Assumptions!C23</f>
+      <c r="D34" s="3">
         <v>0.08</v>
       </c>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B34" s="33" t="s">
-        <v>114</v>
-      </c>
-      <c r="C34" s="27">
+    <row r="35" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B35" s="30" t="s">
+        <v>105</v>
+      </c>
+      <c r="C35" s="24">
         <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
-      <c r="D34" s="3">
+      <c r="D35" s="3">
         <f ca="1">IF(C$7&gt;=30,4%,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B35" s="33" t="s">
-        <v>17</v>
-      </c>
-      <c r="C35" s="27">
+    <row r="36" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B36" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="C36" s="24">
         <f t="shared" si="1"/>
         <v>450.8</v>
       </c>
-      <c r="D35" s="3">
-        <f>Assumptions!C24</f>
+      <c r="D36" s="3">
         <v>0.02</v>
       </c>
     </row>
-    <row r="36" spans="2:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B36" s="36" t="s">
-        <v>45</v>
-      </c>
-      <c r="C36" s="56">
+    <row r="37" spans="2:4" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B37" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="C37" s="51">
         <v>0</v>
       </c>
-      <c r="D36" s="57">
-        <f>C36/C28</f>
+      <c r="D37" s="52">
+        <f>C37/C29</f>
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="2:5" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="B37" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="C37" s="49">
-        <f ca="1">C28-SUM(C30:C36)</f>
+    <row r="38" spans="2:4" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="B38" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="C38" s="44">
+        <f ca="1">C29-SUM(C31:C37)</f>
         <v>16645.099999999999</v>
       </c>
-      <c r="D37" s="55">
-        <f ca="1">C37/C28</f>
+      <c r="D38" s="50">
+        <f ca="1">C38/C29</f>
         <v>0.73846938775510196</v>
       </c>
     </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B38" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="C38" s="50">
-        <f>Assumptions!C10</f>
+    <row r="39" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B39" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="C39" s="45">
+        <f>Assumptions!C7</f>
         <v>0.02</v>
       </c>
     </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B40" s="30" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B42" s="33" t="s">
+    <row r="41" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B41" s="27" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="43" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B43" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="C43" s="48">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B44" s="31" t="s">
         <v>42</v>
       </c>
-      <c r="C42" s="53">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B43" s="34" t="s">
-        <v>46</v>
-      </c>
-      <c r="C43" s="46">
-        <f>(1+C42)^(1/C10)-1</f>
+      <c r="C44" s="41">
+        <f>(1+C43)^(1/C10)-1</f>
         <v>2.268495988716035E-2</v>
       </c>
     </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B44" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="C44" s="47">
-        <f>D16*(1+C$42)</f>
+    <row r="45" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B45" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="C45" s="42">
+        <f>D16*(1+C$43)</f>
         <v>13524000</v>
       </c>
     </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B46" s="30" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B48" s="33" t="s">
-        <v>39</v>
-      </c>
-      <c r="C48" s="40" t="str">
+    <row r="47" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B47" s="27" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="49" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B49" s="30" t="s">
+        <v>35</v>
+      </c>
+      <c r="C49" s="35" t="str">
         <f>C14</f>
         <v>Asking Price</v>
       </c>
-      <c r="D48" s="40" t="str">
+      <c r="D49" s="35" t="str">
         <f>D14</f>
         <v>Comparable</v>
       </c>
-      <c r="E48" s="40" t="str">
+      <c r="E49" s="35" t="str">
         <f>E14</f>
         <v>IRR Netural Price</v>
       </c>
     </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B49" s="33" t="s">
-        <v>75</v>
-      </c>
-      <c r="C49" s="22">
+    <row r="50" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B50" s="30" t="s">
+        <v>66</v>
+      </c>
+      <c r="C50" s="20">
         <f>C16</f>
         <v>12500000</v>
       </c>
-      <c r="D49" s="22">
-        <f t="shared" ref="D49:E49" si="2">D16</f>
+      <c r="D50" s="20">
+        <f t="shared" ref="D50:E50" si="2">D16</f>
         <v>9660000</v>
       </c>
-      <c r="E49" s="22">
+      <c r="E50" s="20">
         <f t="shared" si="2"/>
         <v>8500000</v>
       </c>
     </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B50" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="C50" s="26">
-        <f>C22</f>
+    <row r="51" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B51" s="30" t="s">
+        <v>61</v>
+      </c>
+      <c r="C51" s="23">
+        <f>C23</f>
         <v>13281250</v>
       </c>
-      <c r="D50" s="26">
-        <f>D22</f>
+      <c r="D51" s="23">
+        <f>D23</f>
         <v>10274530</v>
       </c>
-      <c r="E50" s="26">
-        <f>E22</f>
+      <c r="E51" s="23">
+        <f>E23</f>
         <v>9023500</v>
       </c>
     </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B51" s="33" t="s">
-        <v>48</v>
-      </c>
-      <c r="C51" s="58">
-        <f ca="1">C$37*12</f>
+    <row r="52" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B52" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="C52" s="53">
+        <f ca="1">C$38*12</f>
         <v>199741.19999999998</v>
       </c>
-      <c r="D51" s="58"/>
-      <c r="E51" s="58"/>
-    </row>
-    <row r="52" spans="2:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B52" s="36" t="s">
-        <v>49</v>
-      </c>
-      <c r="C52" s="59">
-        <f>C$44</f>
+      <c r="D52" s="53"/>
+      <c r="E52" s="53"/>
+    </row>
+    <row r="53" spans="2:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B53" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C53" s="54">
+        <f>C$45</f>
         <v>13524000</v>
       </c>
-      <c r="D52" s="59"/>
-      <c r="E52" s="59"/>
-    </row>
-    <row r="53" spans="2:5" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="B53" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="C53" s="48">
-        <f ca="1">RATE(15, $C51*(1+$C$38), -C50, $C52 / (1+$C$38)^15) + $C$38</f>
+      <c r="D53" s="54"/>
+      <c r="E53" s="54"/>
+    </row>
+    <row r="54" spans="2:5" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="B54" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="C54" s="43">
+        <f ca="1">RATE(15, $C52*(1+$C$39), -C51, $C53 / (1+$C$39)^15) + $C$39</f>
         <v>1.8999155164258121E-2</v>
       </c>
-      <c r="D53" s="48">
-        <f t="shared" ref="D53:E53" ca="1" si="3">RATE(15, $C51*(1+$C$38), -D50, $C52 / (1+$C$38)^15) + $C$38</f>
+      <c r="D54" s="43">
+        <f t="shared" ref="D54:E54" ca="1" si="3">RATE(15, $C52*(1+$C$39), -D51, $C53 / (1+$C$39)^15) + $C$39</f>
         <v>3.8543863508982534E-2</v>
       </c>
-      <c r="E53" s="48">
+      <c r="E54" s="43">
         <f t="shared" ca="1" si="3"/>
         <v>4.8742541751567378E-2</v>
       </c>
     </row>
-    <row r="55" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B55" s="41" t="s">
-        <v>77</v>
-      </c>
-    </row>
     <row r="56" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B56" t="s">
-        <v>78</v>
+      <c r="B56" s="36" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="57" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B57" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
     </row>
     <row r="58" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B58" t="s">
-        <v>80</v>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="59" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B59" t="s">
+        <v>71</v>
       </c>
     </row>
   </sheetData>
   <dataConsolidate/>
-  <mergeCells count="5">
-    <mergeCell ref="C51:E51"/>
+  <mergeCells count="6">
     <mergeCell ref="C52:E52"/>
+    <mergeCell ref="C53:E53"/>
     <mergeCell ref="C17:E17"/>
     <mergeCell ref="C19:E19"/>
     <mergeCell ref="C20:E20"/>
+    <mergeCell ref="C21:E21"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="97" fitToWidth="0" orientation="portrait" verticalDpi="0" r:id="rId1"/>
@@ -2290,141 +2191,141 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:E53"/>
+  <dimension ref="B2:E59"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
-    <col min="2" max="2" width="28.53125" customWidth="1"/>
+    <col min="2" max="2" width="29.86328125" customWidth="1"/>
     <col min="3" max="9" width="16.59765625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B2" s="31" t="s">
-        <v>87</v>
+      <c r="B2" s="28" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B4" s="33" t="s">
-        <v>41</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>110</v>
+      <c r="B4" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B5" s="33" t="s">
+      <c r="B5" s="30" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="17" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B6" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="18">
+      <c r="B6" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="16">
         <v>2002</v>
       </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B7" s="33" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7" s="19">
+      <c r="B7" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="17">
         <f ca="1">YEAR(TODAY())-C6</f>
         <v>24</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B8" s="33" t="s">
-        <v>82</v>
-      </c>
-      <c r="C8" s="20">
+      <c r="B8" s="30" t="s">
+        <v>73</v>
+      </c>
+      <c r="C8" s="18">
         <v>485</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B9" s="33" t="s">
-        <v>83</v>
-      </c>
-      <c r="C9" s="21">
+      <c r="B9" s="30" t="s">
+        <v>74</v>
+      </c>
+      <c r="C9" s="19">
         <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B10" s="33" t="s">
-        <v>38</v>
-      </c>
-      <c r="C10" s="51">
+      <c r="B10" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="46">
         <f>Holding_Period</f>
         <v>15</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B12" s="30" t="s">
-        <v>89</v>
+      <c r="B12" s="27" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B14" s="33" t="s">
-        <v>39</v>
+      <c r="B14" s="30" t="s">
+        <v>35</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B15" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="C15" s="28">
+      <c r="B15" s="31" t="s">
+        <v>75</v>
+      </c>
+      <c r="C15" s="25">
         <f>C16/C8</f>
         <v>16082.474226804125</v>
       </c>
-      <c r="D15" s="29">
+      <c r="D15" s="26">
         <v>15500</v>
       </c>
-      <c r="E15" s="28">
+      <c r="E15" s="25">
         <f>E16/C8</f>
         <v>14538.53385789773</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B16" s="33" t="s">
-        <v>51</v>
-      </c>
-      <c r="C16" s="16">
+      <c r="B16" s="30" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" s="14">
         <v>7800000</v>
       </c>
-      <c r="D16" s="22">
+      <c r="D16" s="20">
         <f>D15*C$8</f>
         <v>7517500</v>
       </c>
-      <c r="E16" s="45">
+      <c r="E16" s="40">
         <v>7051188.9210803993</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B17" s="33" t="s">
-        <v>66</v>
-      </c>
-      <c r="C17" s="60">
-        <f>Assumptions!C15</f>
+      <c r="B17" s="30" t="s">
+        <v>60</v>
+      </c>
+      <c r="C17" s="58">
+        <f>Assumptions!C10</f>
         <v>0.01</v>
       </c>
-      <c r="D17" s="60"/>
-      <c r="E17" s="60"/>
+      <c r="D17" s="58"/>
+      <c r="E17" s="58"/>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B18" s="33" t="s">
-        <v>63</v>
+      <c r="B18" s="30" t="s">
+        <v>57</v>
       </c>
       <c r="C18" s="10">
         <v>0.03</v>
@@ -2437,287 +2338,372 @@
       </c>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B19" s="33" t="s">
-        <v>65</v>
-      </c>
-      <c r="C19" s="60">
-        <f>Assumptions!C18</f>
+      <c r="B19" s="30" t="s">
+        <v>59</v>
+      </c>
+      <c r="C19" s="55">
+        <f>Assumptions!C11</f>
         <v>1E-3</v>
       </c>
-      <c r="D19" s="60"/>
-      <c r="E19" s="60"/>
+      <c r="D19" s="55"/>
+      <c r="E19" s="55"/>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B20" s="33" t="s">
-        <v>67</v>
-      </c>
-      <c r="C20" s="61">
-        <f>Assumptions!C16+Assumptions!C17</f>
-        <v>25000</v>
-      </c>
-      <c r="D20" s="61"/>
-      <c r="E20" s="61"/>
-    </row>
-    <row r="21" spans="2:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B21" s="36" t="s">
-        <v>112</v>
-      </c>
-      <c r="C21" s="54">
+      <c r="B20" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="C20" s="56">
+        <f>Assumptions!C12</f>
+        <v>20000</v>
+      </c>
+      <c r="D20" s="56"/>
+      <c r="E20" s="56"/>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B21" s="30" t="s">
+        <v>107</v>
+      </c>
+      <c r="C21" s="56">
+        <f>Assumptions!C13</f>
+        <v>5000</v>
+      </c>
+      <c r="D21" s="56"/>
+      <c r="E21" s="56"/>
+    </row>
+    <row r="22" spans="2:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B22" s="32" t="s">
+        <v>103</v>
+      </c>
+      <c r="C22" s="49">
         <v>0</v>
       </c>
-      <c r="D21" s="54">
+      <c r="D22" s="49">
         <v>0</v>
       </c>
-      <c r="E21" s="54">
+      <c r="E22" s="49">
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:5" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="B22" s="24" t="s">
-        <v>68</v>
-      </c>
-      <c r="C22" s="25">
-        <f>C16+C16*($C$17+C18+$C$19)+$C$20+C21</f>
-        <v>8144800</v>
-      </c>
-      <c r="D22" s="25">
-        <f t="shared" ref="D22:E22" si="0">D16+D16*($C$17+D18+$C$19)+$C$20+D21</f>
-        <v>7850717.5</v>
-      </c>
-      <c r="E22" s="25">
+    <row r="23" spans="2:5" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="B23" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="C23" s="22">
+        <f>C16+C16*($C$17+C18+$C$19)+$C$20+C22</f>
+        <v>8139800</v>
+      </c>
+      <c r="D23" s="22">
+        <f t="shared" ref="D23:E23" si="0">D16+D16*($C$17+D18+$C$19)+$C$20+D22</f>
+        <v>7845717.5</v>
+      </c>
+      <c r="E23" s="22">
         <f t="shared" si="0"/>
-        <v>7365287.6668446958</v>
-      </c>
-    </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B24" s="30" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="25" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="C25" s="5"/>
-    </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B26" s="33" t="s">
-        <v>69</v>
-      </c>
-      <c r="C26" s="52">
+        <v>7360287.6668446958</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B25" s="27" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C26" s="5"/>
+    </row>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B27" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="C27" s="47">
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B27" s="34" t="s">
-        <v>44</v>
-      </c>
-      <c r="C27" s="32">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B28" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="C28" s="29">
         <f>D16</f>
         <v>7517500</v>
       </c>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B28" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="C28" s="49">
-        <f>C27*C$26/12</f>
+    <row r="29" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B29" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="C29" s="44">
+        <f>C28*C$27/12</f>
         <v>19420.208333333332</v>
       </c>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B29" s="7"/>
-      <c r="C29" s="27"/>
-    </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B30" s="33" t="s">
-        <v>8</v>
-      </c>
-      <c r="C30" s="27">
+      <c r="B30" s="7"/>
+      <c r="C30" s="24"/>
+    </row>
+    <row r="31" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B31" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="24">
         <f>C$9*C$8</f>
         <v>1067</v>
       </c>
-    </row>
-    <row r="31" spans="2:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B31" s="36" t="s">
-        <v>45</v>
-      </c>
-      <c r="C31" s="37">
-        <f ca="1">(C28*(Other_Annual_Expense_Percent-IF(C$7&gt;=30,4%,0)))</f>
-        <v>3592.7385416666657</v>
-      </c>
-    </row>
-    <row r="32" spans="2:5" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="B32" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="C32" s="49">
-        <f ca="1">C28-C30-C31</f>
+      <c r="D31" s="50">
+        <f>C31/C29</f>
+        <v>5.4942767950052034E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B32" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="C32" s="24">
+        <f>$C$29*D32</f>
+        <v>1068.1114583333333</v>
+      </c>
+      <c r="D32" s="50">
+        <f>Assumptions!C16</f>
+        <v>5.5E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B33" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="C33" s="24">
+        <f t="shared" ref="C33:C36" si="1">$C$29*D33</f>
+        <v>582.60624999999993</v>
+      </c>
+      <c r="D33" s="50">
+        <f>Assumptions!C17</f>
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B34" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="C34" s="24">
+        <f t="shared" si="1"/>
+        <v>1553.6166666666666</v>
+      </c>
+      <c r="D34" s="3">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B35" s="30" t="s">
+        <v>105</v>
+      </c>
+      <c r="C35" s="24">
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D35" s="3">
+        <f ca="1">IF(C$7&gt;=30,4%,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B36" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="C36" s="24">
+        <f t="shared" si="1"/>
+        <v>388.40416666666664</v>
+      </c>
+      <c r="D36" s="3">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="37" spans="2:4" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B37" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="C37" s="33">
+        <v>0</v>
+      </c>
+      <c r="D37" s="52">
+        <f>C37/C29</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="2:4" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="B38" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="C38" s="44">
+        <f ca="1">C29-SUM(C31:C37)</f>
         <v>14760.469791666666</v>
       </c>
-    </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B33" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="C33" s="50">
-        <f>Assumptions!C10</f>
+      <c r="D38" s="50">
+        <f ca="1">C38/C29</f>
+        <v>0.76005723204994802</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B39" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="C39" s="45">
+        <f>Assumptions!C7</f>
         <v>0.02</v>
       </c>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B35" s="30" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B37" s="33" t="s">
+    <row r="41" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B41" s="27" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="43" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B43" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="C43" s="48">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B44" s="31" t="s">
         <v>42</v>
       </c>
-      <c r="C37" s="53">
-        <f>Assumptions!C11</f>
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B38" s="34" t="s">
-        <v>46</v>
-      </c>
-      <c r="C38" s="46">
-        <f>(1+C37)^(1/C10)-1</f>
+      <c r="C44" s="41">
+        <f>(1+C43)^(1/C10)-1</f>
         <v>1.7644813405053306E-2</v>
       </c>
     </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B39" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="C39" s="47">
-        <f>D16*(1+C$37)</f>
+    <row r="45" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B45" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="C45" s="42">
+        <f>D16*(1+C$43)</f>
         <v>9772750</v>
       </c>
     </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B41" s="30" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B43" s="33" t="s">
-        <v>39</v>
-      </c>
-      <c r="C43" s="40" t="str">
+    <row r="47" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B47" s="27" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="49" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B49" s="30" t="s">
+        <v>35</v>
+      </c>
+      <c r="C49" s="35" t="str">
         <f>C14</f>
         <v>Asking Price</v>
       </c>
-      <c r="D43" s="40" t="str">
+      <c r="D49" s="35" t="str">
         <f>D14</f>
         <v>Comparable</v>
       </c>
-      <c r="E43" s="40" t="str">
+      <c r="E49" s="35" t="str">
         <f>E14</f>
         <v>IRR Netural Price</v>
       </c>
     </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B44" s="33" t="s">
-        <v>75</v>
-      </c>
-      <c r="C44" s="22">
+    <row r="50" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B50" s="30" t="s">
+        <v>66</v>
+      </c>
+      <c r="C50" s="20">
         <f>C16</f>
         <v>7800000</v>
       </c>
-      <c r="D44" s="22">
-        <f t="shared" ref="D44:E44" si="1">D16</f>
+      <c r="D50" s="20">
+        <f>D16</f>
         <v>7517500</v>
       </c>
-      <c r="E44" s="22">
-        <f t="shared" si="1"/>
+      <c r="E50" s="20">
+        <f>E16</f>
         <v>7051188.9210803993</v>
       </c>
     </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B45" s="33" t="s">
+    <row r="51" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B51" s="30" t="s">
+        <v>61</v>
+      </c>
+      <c r="C51" s="23">
+        <f>C23</f>
+        <v>8139800</v>
+      </c>
+      <c r="D51" s="23">
+        <f>D23</f>
+        <v>7845717.5</v>
+      </c>
+      <c r="E51" s="23">
+        <f>E23</f>
+        <v>7360287.6668446958</v>
+      </c>
+    </row>
+    <row r="52" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B52" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="C52" s="53">
+        <f ca="1">C$38*12</f>
+        <v>177125.63750000001</v>
+      </c>
+      <c r="D52" s="53"/>
+      <c r="E52" s="53"/>
+    </row>
+    <row r="53" spans="2:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B53" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C53" s="54">
+        <f>C$45</f>
+        <v>9772750</v>
+      </c>
+      <c r="D53" s="54"/>
+      <c r="E53" s="54"/>
+    </row>
+    <row r="54" spans="2:5" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="B54" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="C54" s="43">
+        <f ca="1">RATE(15, $C52*(1+$C$39), -C51, $C53 / (1+$C$39)^15) + $C$39</f>
+        <v>3.5761284334018234E-2</v>
+      </c>
+      <c r="D54" s="43">
+        <f t="shared" ref="D54:E54" ca="1" si="2">RATE(15, $C52*(1+$C$39), -D51, $C53 / (1+$C$39)^15) + $C$39</f>
+        <v>3.8678982511552037E-2</v>
+      </c>
+      <c r="E54" s="43">
+        <f t="shared" ca="1" si="2"/>
+        <v>4.37896958784229E-2</v>
+      </c>
+    </row>
+    <row r="56" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B56" s="36" t="s">
         <v>68</v>
       </c>
-      <c r="C45" s="26">
-        <f>C22</f>
-        <v>8144800</v>
-      </c>
-      <c r="D45" s="26">
-        <f>D22</f>
-        <v>7850717.5</v>
-      </c>
-      <c r="E45" s="26">
-        <f>E22</f>
-        <v>7365287.6668446958</v>
-      </c>
-    </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B46" s="33" t="s">
-        <v>48</v>
-      </c>
-      <c r="C46" s="58">
-        <f ca="1">C$32*12</f>
-        <v>177125.63750000001</v>
-      </c>
-      <c r="D46" s="58"/>
-      <c r="E46" s="58"/>
-    </row>
-    <row r="47" spans="2:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B47" s="36" t="s">
-        <v>49</v>
-      </c>
-      <c r="C47" s="59">
-        <f>C$39</f>
-        <v>9772750</v>
-      </c>
-      <c r="D47" s="59"/>
-      <c r="E47" s="59"/>
-    </row>
-    <row r="48" spans="2:5" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="B48" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="C48" s="48">
-        <f ca="1">RATE(15, $C46*(1+$C$33), -C45, $C47 / (1+$C$33)^15) + $C$33</f>
-        <v>3.5712756815729746E-2</v>
-      </c>
-      <c r="D48" s="48">
-        <f t="shared" ref="D48:E48" ca="1" si="2">RATE(15, $C46*(1+$C$33), -D45, $C47 / (1+$C$33)^15) + $C$33</f>
-        <v>3.8628303343988556E-2</v>
-      </c>
-      <c r="E48" s="48">
-        <f t="shared" ca="1" si="2"/>
-        <v>4.3735038261089168E-2</v>
-      </c>
-    </row>
-    <row r="50" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B50" s="41" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="51" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B51" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="52" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B52" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="53" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B53" t="s">
-        <v>80</v>
+    </row>
+    <row r="57" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B57" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="58" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B58" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="59" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B59" t="s">
+        <v>71</v>
       </c>
     </row>
   </sheetData>
   <dataConsolidate/>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="C17:E17"/>
     <mergeCell ref="C19:E19"/>
     <mergeCell ref="C20:E20"/>
-    <mergeCell ref="C46:E46"/>
-    <mergeCell ref="C47:E47"/>
+    <mergeCell ref="C52:E52"/>
+    <mergeCell ref="C53:E53"/>
+    <mergeCell ref="C21:E21"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="97" fitToWidth="0" orientation="portrait" verticalDpi="0" r:id="rId1"/>
@@ -2729,141 +2715,141 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:E53"/>
+  <dimension ref="B2:E59"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
-    <col min="2" max="2" width="28.53125" customWidth="1"/>
+    <col min="2" max="2" width="29.86328125" customWidth="1"/>
     <col min="3" max="9" width="16.59765625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B2" s="31" t="s">
-        <v>87</v>
+      <c r="B2" s="28" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B4" s="33" t="s">
-        <v>41</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>111</v>
+      <c r="B4" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B5" s="33" t="s">
+      <c r="B5" s="30" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="17" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B6" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="18">
+      <c r="B6" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="16">
         <v>1995</v>
       </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B7" s="33" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7" s="19">
+      <c r="B7" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="17">
         <f ca="1">YEAR(TODAY())-C6</f>
         <v>31</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B8" s="33" t="s">
-        <v>82</v>
-      </c>
-      <c r="C8" s="20">
+      <c r="B8" s="30" t="s">
+        <v>73</v>
+      </c>
+      <c r="C8" s="18">
         <v>315</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B9" s="33" t="s">
-        <v>83</v>
-      </c>
-      <c r="C9" s="21">
+      <c r="B9" s="30" t="s">
+        <v>74</v>
+      </c>
+      <c r="C9" s="19">
         <v>2</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B10" s="33" t="s">
-        <v>38</v>
-      </c>
-      <c r="C10" s="51">
+      <c r="B10" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="46">
         <f>Holding_Period</f>
         <v>15</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B12" s="30" t="s">
-        <v>89</v>
+      <c r="B12" s="27" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B14" s="33" t="s">
-        <v>39</v>
+      <c r="B14" s="30" t="s">
+        <v>35</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B15" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="C15" s="28">
+      <c r="B15" s="31" t="s">
+        <v>75</v>
+      </c>
+      <c r="C15" s="25">
         <f>C16/C8</f>
         <v>13587.301587301587</v>
       </c>
-      <c r="D15" s="29">
+      <c r="D15" s="26">
         <v>13587</v>
       </c>
-      <c r="E15" s="28">
+      <c r="E15" s="25">
         <f>E16/C8</f>
         <v>12262.119150039165</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B16" s="33" t="s">
-        <v>51</v>
-      </c>
-      <c r="C16" s="16">
+      <c r="B16" s="30" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" s="14">
         <v>4280000</v>
       </c>
-      <c r="D16" s="22">
+      <c r="D16" s="20">
         <f>D15*C$8</f>
         <v>4279905</v>
       </c>
-      <c r="E16" s="45">
+      <c r="E16" s="40">
         <v>3862567.5322623369</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B17" s="33" t="s">
-        <v>66</v>
-      </c>
-      <c r="C17" s="60">
-        <f>Assumptions!C15</f>
+      <c r="B17" s="30" t="s">
+        <v>60</v>
+      </c>
+      <c r="C17" s="58">
+        <f>Assumptions!C10</f>
         <v>0.01</v>
       </c>
-      <c r="D17" s="60"/>
-      <c r="E17" s="60"/>
+      <c r="D17" s="58"/>
+      <c r="E17" s="58"/>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B18" s="33" t="s">
-        <v>63</v>
+      <c r="B18" s="30" t="s">
+        <v>57</v>
       </c>
       <c r="C18" s="10">
         <v>5.5E-2</v>
@@ -2878,286 +2864,372 @@
       </c>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B19" s="33" t="s">
-        <v>65</v>
-      </c>
-      <c r="C19" s="60">
-        <f>Assumptions!C18</f>
+      <c r="B19" s="30" t="s">
+        <v>59</v>
+      </c>
+      <c r="C19" s="55">
+        <f>Assumptions!C11</f>
         <v>1E-3</v>
       </c>
-      <c r="D19" s="60"/>
-      <c r="E19" s="60"/>
+      <c r="D19" s="55"/>
+      <c r="E19" s="55"/>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B20" s="33" t="s">
-        <v>67</v>
-      </c>
-      <c r="C20" s="61">
-        <f>Assumptions!C16+Assumptions!C17</f>
-        <v>25000</v>
-      </c>
-      <c r="D20" s="61"/>
-      <c r="E20" s="61"/>
-    </row>
-    <row r="21" spans="2:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B21" s="36" t="s">
-        <v>112</v>
-      </c>
-      <c r="C21" s="54">
+      <c r="B20" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="C20" s="56">
+        <f>Assumptions!C12</f>
+        <v>20000</v>
+      </c>
+      <c r="D20" s="56"/>
+      <c r="E20" s="56"/>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B21" s="30" t="s">
+        <v>107</v>
+      </c>
+      <c r="C21" s="56">
+        <f>Assumptions!C13</f>
+        <v>5000</v>
+      </c>
+      <c r="D21" s="56"/>
+      <c r="E21" s="56"/>
+    </row>
+    <row r="22" spans="2:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B22" s="32" t="s">
+        <v>103</v>
+      </c>
+      <c r="C22" s="49">
         <v>135000</v>
       </c>
-      <c r="D21" s="54">
+      <c r="D22" s="49">
         <v>135000</v>
       </c>
-      <c r="E21" s="54">
+      <c r="E22" s="49">
         <v>135000</v>
       </c>
     </row>
-    <row r="22" spans="2:5" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="B22" s="24" t="s">
-        <v>68</v>
-      </c>
-      <c r="C22" s="25">
-        <f>C16+C16*($C$17+C18+$C$19)+$C$20+C21</f>
-        <v>4722480</v>
-      </c>
-      <c r="D22" s="25">
-        <f t="shared" ref="D22:E22" si="0">D16+D16*($C$17+D18+$C$19)+$C$20+D21</f>
-        <v>4722378.7300000004</v>
-      </c>
-      <c r="E22" s="25">
+    <row r="23" spans="2:5" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="B23" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="C23" s="22">
+        <f>C16+C16*($C$17+C18+$C$19)+$C$20+C22</f>
+        <v>4717480</v>
+      </c>
+      <c r="D23" s="22">
+        <f t="shared" ref="D23:E23" si="0">D16+D16*($C$17+D18+$C$19)+$C$20+D22</f>
+        <v>4717378.7300000004</v>
+      </c>
+      <c r="E23" s="22">
         <f t="shared" si="0"/>
-        <v>4277496.989391651</v>
-      </c>
-    </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B24" s="30" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="25" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="C25" s="5"/>
-    </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B26" s="33" t="s">
-        <v>69</v>
-      </c>
-      <c r="C26" s="52">
+        <v>4272496.989391651</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B25" s="27" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C26" s="5"/>
+    </row>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B27" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="C27" s="47">
         <v>4.2057008274716381E-2</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B27" s="34" t="s">
-        <v>44</v>
-      </c>
-      <c r="C27" s="32">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B28" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="C28" s="29">
         <f>D16</f>
         <v>4279905</v>
       </c>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B28" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="C28" s="49">
-        <f>C27*C$26/12</f>
+    <row r="29" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B29" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="C29" s="44">
+        <f>C28*C$27/12</f>
         <v>15000.000000000002</v>
       </c>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B29" s="7"/>
-      <c r="C29" s="27"/>
-    </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B30" s="33" t="s">
-        <v>8</v>
-      </c>
-      <c r="C30" s="27">
+      <c r="B30" s="7"/>
+      <c r="C30" s="24"/>
+    </row>
+    <row r="31" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B31" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="24">
         <f>C$9*C$8</f>
         <v>630</v>
       </c>
-    </row>
-    <row r="31" spans="2:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B31" s="36" t="s">
-        <v>45</v>
-      </c>
-      <c r="C31" s="37">
-        <f ca="1">(C28*(Other_Annual_Expense_Percent-IF(C$7&gt;=30,4%,0)))</f>
-        <v>2174.9999999999995</v>
-      </c>
-    </row>
-    <row r="32" spans="2:5" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="B32" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="C32" s="49">
-        <f ca="1">C28-C30-C31</f>
-        <v>12195.000000000002</v>
-      </c>
-    </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B33" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="C33" s="50">
-        <f>Assumptions!C10</f>
+      <c r="D31" s="50">
+        <f>C31/C29</f>
+        <v>4.1999999999999996E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B32" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="C32" s="24">
+        <f>$C$29*D32</f>
+        <v>825.00000000000011</v>
+      </c>
+      <c r="D32" s="50">
+        <f>Assumptions!C16</f>
+        <v>5.5E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B33" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="C33" s="24">
+        <f t="shared" ref="C33:C36" si="1">$C$29*D33</f>
+        <v>450.00000000000006</v>
+      </c>
+      <c r="D33" s="50">
+        <f>Assumptions!C17</f>
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B34" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="C34" s="24">
+        <f t="shared" si="1"/>
+        <v>1200.0000000000002</v>
+      </c>
+      <c r="D34" s="3">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B35" s="30" t="s">
+        <v>105</v>
+      </c>
+      <c r="C35" s="24">
+        <f t="shared" ca="1" si="1"/>
+        <v>600.00000000000011</v>
+      </c>
+      <c r="D35" s="3">
+        <f ca="1">IF(C$7&gt;=30,4%,0)</f>
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B36" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="C36" s="24">
+        <f t="shared" si="1"/>
+        <v>300.00000000000006</v>
+      </c>
+      <c r="D36" s="3">
         <v>0.02</v>
       </c>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B35" s="30" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B37" s="33" t="s">
+    <row r="37" spans="2:4" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B37" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="C37" s="33">
+        <v>0</v>
+      </c>
+      <c r="D37" s="52">
+        <f>C37/C29</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="2:4" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="B38" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="C38" s="44">
+        <f ca="1">C29-SUM(C31:C37)</f>
+        <v>10995.000000000002</v>
+      </c>
+      <c r="D38" s="50">
+        <f ca="1">C38/C29</f>
+        <v>0.73299999999999998</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B39" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="C39" s="45">
+        <f>Assumptions!C7</f>
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="41" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B41" s="27" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="43" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B43" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="C43" s="48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B44" s="31" t="s">
         <v>42</v>
       </c>
-      <c r="C37" s="53">
+      <c r="C44" s="41">
+        <f>(1+C43)^(1/C10)-1</f>
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B38" s="34" t="s">
-        <v>46</v>
-      </c>
-      <c r="C38" s="46">
-        <f>(1+C37)^(1/C10)-1</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B39" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="C39" s="47">
-        <f>D16*(1+C$37)</f>
+    <row r="45" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B45" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="C45" s="42">
+        <f>D16*(1+C$43)</f>
         <v>4279905</v>
       </c>
     </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B41" s="30" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B43" s="33" t="s">
-        <v>39</v>
-      </c>
-      <c r="C43" s="40" t="str">
+    <row r="47" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B47" s="27" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="49" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B49" s="30" t="s">
+        <v>35</v>
+      </c>
+      <c r="C49" s="35" t="str">
         <f>C14</f>
         <v>Asking Price</v>
       </c>
-      <c r="D43" s="40" t="str">
+      <c r="D49" s="35" t="str">
         <f>D14</f>
         <v>Comparable</v>
       </c>
-      <c r="E43" s="40" t="str">
+      <c r="E49" s="35" t="str">
         <f>E14</f>
         <v>IRR Netural Price</v>
       </c>
     </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B44" s="33" t="s">
-        <v>75</v>
-      </c>
-      <c r="C44" s="22">
+    <row r="50" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B50" s="30" t="s">
+        <v>66</v>
+      </c>
+      <c r="C50" s="20">
         <f>C16</f>
         <v>4280000</v>
       </c>
-      <c r="D44" s="22">
-        <f t="shared" ref="D44:E44" si="1">D16</f>
+      <c r="D50" s="20">
+        <f>D16</f>
         <v>4279905</v>
       </c>
-      <c r="E44" s="22">
-        <f t="shared" si="1"/>
+      <c r="E50" s="20">
+        <f>E16</f>
         <v>3862567.5322623369</v>
       </c>
     </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B45" s="33" t="s">
+    <row r="51" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B51" s="30" t="s">
+        <v>61</v>
+      </c>
+      <c r="C51" s="23">
+        <f>C23</f>
+        <v>4717480</v>
+      </c>
+      <c r="D51" s="23">
+        <f>D23</f>
+        <v>4717378.7300000004</v>
+      </c>
+      <c r="E51" s="23">
+        <f>E23</f>
+        <v>4272496.989391651</v>
+      </c>
+    </row>
+    <row r="52" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B52" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="C52" s="53">
+        <f ca="1">C$38*12</f>
+        <v>131940.00000000003</v>
+      </c>
+      <c r="D52" s="53"/>
+      <c r="E52" s="53"/>
+    </row>
+    <row r="53" spans="2:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B53" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C53" s="54">
+        <f>C$45</f>
+        <v>4279905</v>
+      </c>
+      <c r="D53" s="54"/>
+      <c r="E53" s="54"/>
+    </row>
+    <row r="54" spans="2:5" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="B54" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="C54" s="43">
+        <f ca="1">RATE(15, $C52*(1+$C$39), -C51, $C53 / (1+$C$39)^15) + $C$39</f>
+        <v>2.7990156949300824E-2</v>
+      </c>
+      <c r="D54" s="43">
+        <f t="shared" ref="D54:E54" ca="1" si="2">RATE(15, $C52*(1+$C$39), -D51, $C53 / (1+$C$39)^15) + $C$39</f>
+        <v>2.7991941145339455E-2</v>
+      </c>
+      <c r="E54" s="43">
+        <f t="shared" ca="1" si="2"/>
+        <v>3.6315289989234535E-2</v>
+      </c>
+    </row>
+    <row r="56" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B56" s="36" t="s">
         <v>68</v>
       </c>
-      <c r="C45" s="26">
-        <f>C22</f>
-        <v>4722480</v>
-      </c>
-      <c r="D45" s="26">
-        <f>D22</f>
-        <v>4722378.7300000004</v>
-      </c>
-      <c r="E45" s="26">
-        <f>E22</f>
-        <v>4277496.989391651</v>
-      </c>
-    </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B46" s="33" t="s">
-        <v>48</v>
-      </c>
-      <c r="C46" s="58">
-        <f ca="1">C$32*12</f>
-        <v>146340.00000000003</v>
-      </c>
-      <c r="D46" s="58"/>
-      <c r="E46" s="58"/>
-    </row>
-    <row r="47" spans="2:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B47" s="36" t="s">
-        <v>49</v>
-      </c>
-      <c r="C47" s="59">
-        <f>C$39</f>
-        <v>4279905</v>
-      </c>
-      <c r="D47" s="59"/>
-      <c r="E47" s="59"/>
-    </row>
-    <row r="48" spans="2:5" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="B48" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="C48" s="48">
-        <f ca="1">RATE(15, $C46*(1+$C$33), -C45, $C47 / (1+$C$33)^15) + $C$33</f>
-        <v>3.1538049414762341E-2</v>
-      </c>
-      <c r="D48" s="48">
-        <f t="shared" ref="D48:E48" ca="1" si="2">RATE(15, $C46*(1+$C$33), -D45, $C47 / (1+$C$33)^15) + $C$33</f>
-        <v>3.153987598185972E-2</v>
-      </c>
-      <c r="E48" s="48">
-        <f t="shared" ca="1" si="2"/>
-        <v>4.006688888639906E-2</v>
-      </c>
-    </row>
-    <row r="50" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B50" s="41" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="51" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B51" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="52" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B52" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="53" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B53" t="s">
-        <v>80</v>
+    </row>
+    <row r="57" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B57" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="58" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B58" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="59" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B59" t="s">
+        <v>71</v>
       </c>
     </row>
   </sheetData>
   <dataConsolidate/>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="C17:E17"/>
     <mergeCell ref="C19:E19"/>
     <mergeCell ref="C20:E20"/>
-    <mergeCell ref="C46:E46"/>
-    <mergeCell ref="C47:E47"/>
+    <mergeCell ref="C52:E52"/>
+    <mergeCell ref="C53:E53"/>
+    <mergeCell ref="C21:E21"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="94" fitToWidth="0" orientation="portrait" verticalDpi="0" r:id="rId1"/>
@@ -3179,115 +3251,115 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="37" t="s">
+        <v>72</v>
+      </c>
+      <c r="C2" s="38"/>
+      <c r="D2" s="37" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B3" s="38"/>
+      <c r="C3" s="38"/>
+      <c r="D3" s="38"/>
+    </row>
+    <row r="4" spans="2:4" ht="57" x14ac:dyDescent="0.45">
+      <c r="B4" s="39" t="s">
+        <v>95</v>
+      </c>
+      <c r="C4" s="38"/>
+      <c r="D4" s="39" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B5" s="38"/>
+      <c r="C5" s="38"/>
+      <c r="D5" s="38"/>
+    </row>
+    <row r="6" spans="2:4" ht="128.25" x14ac:dyDescent="0.45">
+      <c r="B6" s="39" t="s">
         <v>81</v>
       </c>
-      <c r="C2" s="43"/>
-      <c r="D2" s="42" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B3" s="43"/>
-      <c r="C3" s="43"/>
-      <c r="D3" s="43"/>
-    </row>
-    <row r="4" spans="2:4" ht="57" x14ac:dyDescent="0.45">
-      <c r="B4" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="C4" s="43"/>
-      <c r="D4" s="44" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B5" s="43"/>
-      <c r="C5" s="43"/>
-      <c r="D5" s="43"/>
-    </row>
-    <row r="6" spans="2:4" ht="128.25" x14ac:dyDescent="0.45">
-      <c r="B6" s="44" t="s">
+      <c r="C6" s="38"/>
+      <c r="D6" s="39" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B7" s="38"/>
+      <c r="C7" s="38"/>
+      <c r="D7" s="38"/>
+    </row>
+    <row r="8" spans="2:4" ht="85.5" x14ac:dyDescent="0.45">
+      <c r="B8" s="39" t="s">
+        <v>83</v>
+      </c>
+      <c r="C8" s="38"/>
+      <c r="D8" s="39" t="s">
         <v>90</v>
       </c>
-      <c r="C6" s="43"/>
-      <c r="D6" s="44" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B7" s="43"/>
-      <c r="C7" s="43"/>
-      <c r="D7" s="43"/>
-    </row>
-    <row r="8" spans="2:4" ht="85.5" x14ac:dyDescent="0.45">
-      <c r="B8" s="44" t="s">
+    </row>
+    <row r="9" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B9" s="38"/>
+      <c r="C9" s="38"/>
+      <c r="D9" s="38"/>
+    </row>
+    <row r="10" spans="2:4" ht="85.5" x14ac:dyDescent="0.45">
+      <c r="B10" s="39" t="s">
+        <v>82</v>
+      </c>
+      <c r="C10" s="38"/>
+      <c r="D10" s="39" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B11" s="38"/>
+      <c r="C11" s="38"/>
+      <c r="D11" s="38"/>
+    </row>
+    <row r="12" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B12" s="38"/>
+      <c r="C12" s="38"/>
+      <c r="D12" s="38"/>
+    </row>
+    <row r="13" spans="2:4" ht="71.25" x14ac:dyDescent="0.45">
+      <c r="B13" s="39" t="s">
+        <v>76</v>
+      </c>
+      <c r="C13" s="38"/>
+      <c r="D13" s="39" t="s">
         <v>92</v>
       </c>
-      <c r="C8" s="43"/>
-      <c r="D8" s="44" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B9" s="43"/>
-      <c r="C9" s="43"/>
-      <c r="D9" s="43"/>
-    </row>
-    <row r="10" spans="2:4" ht="85.5" x14ac:dyDescent="0.45">
-      <c r="B10" s="44" t="s">
-        <v>91</v>
-      </c>
-      <c r="C10" s="43"/>
-      <c r="D10" s="44" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B11" s="43"/>
-      <c r="C11" s="43"/>
-      <c r="D11" s="43"/>
-    </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B12" s="43"/>
-      <c r="C12" s="43"/>
-      <c r="D12" s="43"/>
-    </row>
-    <row r="13" spans="2:4" ht="71.25" x14ac:dyDescent="0.45">
-      <c r="B13" s="44" t="s">
-        <v>85</v>
-      </c>
-      <c r="C13" s="43"/>
-      <c r="D13" s="44" t="s">
-        <v>101</v>
-      </c>
     </row>
     <row r="14" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B14" s="43"/>
-      <c r="C14" s="43"/>
-      <c r="D14" s="43"/>
+      <c r="B14" s="38"/>
+      <c r="C14" s="38"/>
+      <c r="D14" s="38"/>
     </row>
     <row r="15" spans="2:4" ht="128.25" x14ac:dyDescent="0.45">
-      <c r="B15" s="44" t="s">
-        <v>95</v>
-      </c>
-      <c r="C15" s="43"/>
-      <c r="D15" s="44" t="s">
-        <v>102</v>
+      <c r="B15" s="39" t="s">
+        <v>86</v>
+      </c>
+      <c r="C15" s="38"/>
+      <c r="D15" s="39" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="16" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B16" s="43"/>
-      <c r="C16" s="43"/>
-      <c r="D16" s="43"/>
+      <c r="B16" s="38"/>
+      <c r="C16" s="38"/>
+      <c r="D16" s="38"/>
     </row>
     <row r="17" spans="2:4" ht="85.5" x14ac:dyDescent="0.45">
-      <c r="B17" s="44" t="s">
-        <v>96</v>
-      </c>
-      <c r="C17" s="43"/>
-      <c r="D17" s="44" t="s">
-        <v>103</v>
+      <c r="B17" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="C17" s="38"/>
+      <c r="D17" s="39" t="s">
+        <v>94</v>
       </c>
     </row>
   </sheetData>

--- a/financial_models/Res_Property_Monitor.xlsx
+++ b/financial_models/Res_Property_Monitor.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB076F1C-585D-4606-BF52-BDEB9E366D62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38AE6517-746D-41FC-B08D-2C49E1E59BC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="6150" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -202,9 +202,6 @@
   </si>
   <si>
     <t>Transfer Fee</t>
-  </si>
-  <si>
-    <t>NOI Breakdown</t>
   </si>
   <si>
     <t>Stamp Duty %</t>
@@ -737,6 +734,9 @@
   </si>
   <si>
     <t>Default Transaction Cost</t>
+  </si>
+  <si>
+    <t>Default NOI tax rate</t>
   </si>
 </sst>
 </file>
@@ -875,7 +875,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1015,24 +1015,25 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="10" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -1396,7 +1397,7 @@
         <v>0.04</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.45">
@@ -1410,13 +1411,13 @@
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C7" s="10">
         <v>0.02</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.45">
@@ -1424,7 +1425,7 @@
     </row>
     <row r="9" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B9" s="13" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C9" s="12" t="s">
         <v>0</v>
@@ -1472,7 +1473,7 @@
         <v>5000</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="14" spans="2:4" x14ac:dyDescent="0.45">
@@ -1480,7 +1481,7 @@
     </row>
     <row r="15" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B15" s="13" t="s">
-        <v>56</v>
+        <v>108</v>
       </c>
       <c r="C15" s="12" t="s">
         <v>0</v>
@@ -1494,10 +1495,10 @@
         <v>20</v>
       </c>
       <c r="C16" s="10">
-        <v>5.5E-2</v>
+        <v>0.05</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.45">
@@ -1677,7 +1678,7 @@
   <sheetData>
     <row r="2" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B2" s="28" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.45">
@@ -1685,7 +1686,7 @@
         <v>37</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.45">
@@ -1715,7 +1716,7 @@
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B8" s="30" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C8" s="18">
         <v>690</v>
@@ -1723,7 +1724,7 @@
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B9" s="30" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C9" s="19">
         <v>2.5</v>
@@ -1740,7 +1741,7 @@
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B12" s="27" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.45">
@@ -1754,12 +1755,12 @@
         <v>36</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B15" s="31" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C15" s="25">
         <f>C16/C8</f>
@@ -1770,7 +1771,7 @@
       </c>
       <c r="E15" s="25">
         <f>E16/C8</f>
-        <v>12318.840579710144</v>
+        <v>13623.188405797102</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.45">
@@ -1785,70 +1786,70 @@
         <v>9660000</v>
       </c>
       <c r="E16" s="40">
-        <v>8500000</v>
+        <v>9400000</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B17" s="30" t="s">
-        <v>60</v>
-      </c>
-      <c r="C17" s="58">
+        <v>59</v>
+      </c>
+      <c r="C17" s="56">
         <f>Assumptions!C10</f>
         <v>0.01</v>
       </c>
-      <c r="D17" s="58"/>
-      <c r="E17" s="58"/>
+      <c r="D17" s="56"/>
+      <c r="E17" s="56"/>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B18" s="30" t="s">
-        <v>57</v>
-      </c>
-      <c r="C18" s="57">
+        <v>56</v>
+      </c>
+      <c r="C18" s="53">
         <v>3.7499999999999999E-2</v>
       </c>
-      <c r="D18" s="57">
+      <c r="D18" s="53">
         <v>3.4500000000000003E-2</v>
       </c>
-      <c r="E18" s="57">
+      <c r="E18" s="53">
         <v>0.03</v>
       </c>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B19" s="30" t="s">
-        <v>59</v>
-      </c>
-      <c r="C19" s="55">
+        <v>58</v>
+      </c>
+      <c r="C19" s="57">
         <f>Assumptions!C11</f>
         <v>1E-3</v>
       </c>
-      <c r="D19" s="55"/>
-      <c r="E19" s="55"/>
+      <c r="D19" s="57"/>
+      <c r="E19" s="57"/>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B20" s="30" t="s">
-        <v>106</v>
-      </c>
-      <c r="C20" s="56">
+        <v>105</v>
+      </c>
+      <c r="C20" s="58">
         <f>Assumptions!C12</f>
         <v>20000</v>
       </c>
-      <c r="D20" s="56"/>
-      <c r="E20" s="56"/>
+      <c r="D20" s="58"/>
+      <c r="E20" s="58"/>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B21" s="30" t="s">
-        <v>107</v>
-      </c>
-      <c r="C21" s="56">
+        <v>106</v>
+      </c>
+      <c r="C21" s="58">
         <f>Assumptions!C13</f>
         <v>5000</v>
       </c>
-      <c r="D21" s="56"/>
-      <c r="E21" s="56"/>
+      <c r="D21" s="58"/>
+      <c r="E21" s="58"/>
     </row>
     <row r="22" spans="2:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B22" s="32" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C22" s="49">
         <v>150000</v>
@@ -1862,7 +1863,7 @@
     </row>
     <row r="23" spans="2:5" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
       <c r="B23" s="21" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C23" s="22">
         <f>C16+C16*($C$17+C18+$C$19)+$C$20+$C$21+C22</f>
@@ -1874,12 +1875,12 @@
       </c>
       <c r="E23" s="22">
         <f t="shared" si="0"/>
-        <v>9023500</v>
+        <v>9960400</v>
       </c>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B25" s="27" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="26" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -1887,7 +1888,7 @@
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B27" s="30" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C27" s="47">
         <v>2.8000000000000001E-2</v>
@@ -1904,7 +1905,7 @@
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B29" s="21" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C29" s="44">
         <f>C28*C$27/12</f>
@@ -1934,11 +1935,11 @@
       </c>
       <c r="C32" s="24">
         <f>$C$29*D32</f>
-        <v>1239.7</v>
-      </c>
-      <c r="D32" s="50">
+        <v>1127</v>
+      </c>
+      <c r="D32" s="59">
         <f>Assumptions!C16</f>
-        <v>5.5E-2</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="33" spans="2:4" x14ac:dyDescent="0.45">
@@ -1956,7 +1957,7 @@
     </row>
     <row r="34" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B34" s="30" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C34" s="24">
         <f t="shared" si="1"/>
@@ -1968,7 +1969,7 @@
     </row>
     <row r="35" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B35" s="30" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C35" s="24">
         <f t="shared" ca="1" si="1"/>
@@ -2005,15 +2006,15 @@
     </row>
     <row r="38" spans="2:4" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
       <c r="B38" s="21" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C38" s="44">
         <f ca="1">C29-SUM(C31:C37)</f>
-        <v>16645.099999999999</v>
+        <v>16757.8</v>
       </c>
       <c r="D38" s="50">
         <f ca="1">C38/C29</f>
-        <v>0.73846938775510196</v>
+        <v>0.74346938775510196</v>
       </c>
     </row>
     <row r="39" spans="2:4" x14ac:dyDescent="0.45">
@@ -2027,7 +2028,7 @@
     </row>
     <row r="41" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B41" s="27" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="43" spans="2:4" x14ac:dyDescent="0.45">
@@ -2058,7 +2059,7 @@
     </row>
     <row r="47" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B47" s="27" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="49" spans="2:5" x14ac:dyDescent="0.45">
@@ -2080,7 +2081,7 @@
     </row>
     <row r="50" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B50" s="30" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C50" s="20">
         <f>C16</f>
@@ -2092,12 +2093,12 @@
       </c>
       <c r="E50" s="20">
         <f t="shared" si="2"/>
-        <v>8500000</v>
+        <v>9400000</v>
       </c>
     </row>
     <row r="51" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B51" s="30" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C51" s="23">
         <f>C23</f>
@@ -2109,66 +2110,66 @@
       </c>
       <c r="E51" s="23">
         <f>E23</f>
-        <v>9023500</v>
+        <v>9960400</v>
       </c>
     </row>
     <row r="52" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B52" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="C52" s="53">
+      <c r="C52" s="54">
         <f ca="1">C$38*12</f>
-        <v>199741.19999999998</v>
-      </c>
-      <c r="D52" s="53"/>
-      <c r="E52" s="53"/>
+        <v>201093.59999999998</v>
+      </c>
+      <c r="D52" s="54"/>
+      <c r="E52" s="54"/>
     </row>
     <row r="53" spans="2:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B53" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="C53" s="54">
+      <c r="C53" s="55">
         <f>C$45</f>
         <v>13524000</v>
       </c>
-      <c r="D53" s="54"/>
-      <c r="E53" s="54"/>
+      <c r="D53" s="55"/>
+      <c r="E53" s="55"/>
     </row>
     <row r="54" spans="2:5" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
       <c r="B54" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C54" s="43">
         <f ca="1">RATE(15, $C52*(1+$C$39), -C51, $C53 / (1+$C$39)^15) + $C$39</f>
-        <v>1.8999155164258121E-2</v>
+        <v>1.9116404699180176E-2</v>
       </c>
       <c r="D54" s="43">
         <f t="shared" ref="D54:E54" ca="1" si="3">RATE(15, $C52*(1+$C$39), -D51, $C53 / (1+$C$39)^15) + $C$39</f>
-        <v>3.8543863508982534E-2</v>
+        <v>3.867937769139583E-2</v>
       </c>
       <c r="E54" s="43">
         <f t="shared" ca="1" si="3"/>
-        <v>4.8742541751567378E-2</v>
+        <v>4.1100689030016416E-2</v>
       </c>
     </row>
     <row r="56" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B56" s="36" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="57" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B57" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="58" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B58" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="59" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B59" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -2201,7 +2202,7 @@
   <sheetData>
     <row r="2" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B2" s="28" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.45">
@@ -2209,7 +2210,7 @@
         <v>37</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.45">
@@ -2239,7 +2240,7 @@
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B8" s="30" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C8" s="18">
         <v>485</v>
@@ -2247,7 +2248,7 @@
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B9" s="30" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C9" s="19">
         <v>2.2000000000000002</v>
@@ -2264,7 +2265,7 @@
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B12" s="27" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.45">
@@ -2278,12 +2279,12 @@
         <v>36</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B15" s="31" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C15" s="25">
         <f>C16/C8</f>
@@ -2314,18 +2315,18 @@
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B17" s="30" t="s">
-        <v>60</v>
-      </c>
-      <c r="C17" s="58">
+        <v>59</v>
+      </c>
+      <c r="C17" s="56">
         <f>Assumptions!C10</f>
         <v>0.01</v>
       </c>
-      <c r="D17" s="58"/>
-      <c r="E17" s="58"/>
+      <c r="D17" s="56"/>
+      <c r="E17" s="56"/>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B18" s="30" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C18" s="10">
         <v>0.03</v>
@@ -2339,40 +2340,40 @@
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B19" s="30" t="s">
-        <v>59</v>
-      </c>
-      <c r="C19" s="55">
+        <v>58</v>
+      </c>
+      <c r="C19" s="57">
         <f>Assumptions!C11</f>
         <v>1E-3</v>
       </c>
-      <c r="D19" s="55"/>
-      <c r="E19" s="55"/>
+      <c r="D19" s="57"/>
+      <c r="E19" s="57"/>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B20" s="30" t="s">
-        <v>106</v>
-      </c>
-      <c r="C20" s="56">
+        <v>105</v>
+      </c>
+      <c r="C20" s="58">
         <f>Assumptions!C12</f>
         <v>20000</v>
       </c>
-      <c r="D20" s="56"/>
-      <c r="E20" s="56"/>
+      <c r="D20" s="58"/>
+      <c r="E20" s="58"/>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B21" s="30" t="s">
-        <v>107</v>
-      </c>
-      <c r="C21" s="56">
+        <v>106</v>
+      </c>
+      <c r="C21" s="58">
         <f>Assumptions!C13</f>
         <v>5000</v>
       </c>
-      <c r="D21" s="56"/>
-      <c r="E21" s="56"/>
+      <c r="D21" s="58"/>
+      <c r="E21" s="58"/>
     </row>
     <row r="22" spans="2:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B22" s="32" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C22" s="49">
         <v>0</v>
@@ -2386,7 +2387,7 @@
     </row>
     <row r="23" spans="2:5" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
       <c r="B23" s="21" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C23" s="22">
         <f>C16+C16*($C$17+C18+$C$19)+$C$20+C22</f>
@@ -2403,7 +2404,7 @@
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B25" s="27" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="26" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -2411,7 +2412,7 @@
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B27" s="30" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C27" s="47">
         <v>3.1E-2</v>
@@ -2428,7 +2429,7 @@
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B29" s="21" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C29" s="44">
         <f>C28*C$27/12</f>
@@ -2458,11 +2459,11 @@
       </c>
       <c r="C32" s="24">
         <f>$C$29*D32</f>
-        <v>1068.1114583333333</v>
-      </c>
-      <c r="D32" s="50">
+        <v>971.01041666666663</v>
+      </c>
+      <c r="D32" s="59">
         <f>Assumptions!C16</f>
-        <v>5.5E-2</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="33" spans="2:4" x14ac:dyDescent="0.45">
@@ -2480,7 +2481,7 @@
     </row>
     <row r="34" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B34" s="30" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C34" s="24">
         <f t="shared" si="1"/>
@@ -2492,7 +2493,7 @@
     </row>
     <row r="35" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B35" s="30" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C35" s="24">
         <f t="shared" ca="1" si="1"/>
@@ -2529,15 +2530,15 @@
     </row>
     <row r="38" spans="2:4" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
       <c r="B38" s="21" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C38" s="44">
         <f ca="1">C29-SUM(C31:C37)</f>
-        <v>14760.469791666666</v>
+        <v>14857.570833333333</v>
       </c>
       <c r="D38" s="50">
         <f ca="1">C38/C29</f>
-        <v>0.76005723204994802</v>
+        <v>0.76505723204994802</v>
       </c>
     </row>
     <row r="39" spans="2:4" x14ac:dyDescent="0.45">
@@ -2551,7 +2552,7 @@
     </row>
     <row r="41" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B41" s="27" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="43" spans="2:4" x14ac:dyDescent="0.45">
@@ -2582,7 +2583,7 @@
     </row>
     <row r="47" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B47" s="27" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="49" spans="2:5" x14ac:dyDescent="0.45">
@@ -2604,7 +2605,7 @@
     </row>
     <row r="50" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B50" s="30" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C50" s="20">
         <f>C16</f>
@@ -2621,7 +2622,7 @@
     </row>
     <row r="51" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B51" s="30" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C51" s="23">
         <f>C23</f>
@@ -2640,59 +2641,59 @@
       <c r="B52" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="C52" s="53">
+      <c r="C52" s="54">
         <f ca="1">C$38*12</f>
-        <v>177125.63750000001</v>
-      </c>
-      <c r="D52" s="53"/>
-      <c r="E52" s="53"/>
+        <v>178290.85</v>
+      </c>
+      <c r="D52" s="54"/>
+      <c r="E52" s="54"/>
     </row>
     <row r="53" spans="2:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B53" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="C53" s="54">
+      <c r="C53" s="55">
         <f>C$45</f>
         <v>9772750</v>
       </c>
-      <c r="D53" s="54"/>
-      <c r="E53" s="54"/>
+      <c r="D53" s="55"/>
+      <c r="E53" s="55"/>
     </row>
     <row r="54" spans="2:5" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
       <c r="B54" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C54" s="43">
         <f ca="1">RATE(15, $C52*(1+$C$39), -C51, $C53 / (1+$C$39)^15) + $C$39</f>
-        <v>3.5761284334018234E-2</v>
+        <v>3.5914364953040269E-2</v>
       </c>
       <c r="D54" s="43">
         <f t="shared" ref="D54:E54" ca="1" si="2">RATE(15, $C52*(1+$C$39), -D51, $C53 / (1+$C$39)^15) + $C$39</f>
-        <v>3.8678982511552037E-2</v>
+        <v>3.8835369911174707E-2</v>
       </c>
       <c r="E54" s="43">
         <f t="shared" ca="1" si="2"/>
-        <v>4.37896958784229E-2</v>
+        <v>4.3952064966571072E-2</v>
       </c>
     </row>
     <row r="56" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B56" s="36" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="57" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B57" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="58" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B58" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="59" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B59" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -2725,7 +2726,7 @@
   <sheetData>
     <row r="2" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B2" s="28" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.45">
@@ -2733,7 +2734,7 @@
         <v>37</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.45">
@@ -2763,7 +2764,7 @@
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B8" s="30" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C8" s="18">
         <v>315</v>
@@ -2771,7 +2772,7 @@
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B9" s="30" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C9" s="19">
         <v>2</v>
@@ -2788,7 +2789,7 @@
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B12" s="27" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.45">
@@ -2802,12 +2803,12 @@
         <v>36</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B15" s="31" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C15" s="25">
         <f>C16/C8</f>
@@ -2838,18 +2839,18 @@
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B17" s="30" t="s">
-        <v>60</v>
-      </c>
-      <c r="C17" s="58">
+        <v>59</v>
+      </c>
+      <c r="C17" s="56">
         <f>Assumptions!C10</f>
         <v>0.01</v>
       </c>
-      <c r="D17" s="58"/>
-      <c r="E17" s="58"/>
+      <c r="D17" s="56"/>
+      <c r="E17" s="56"/>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B18" s="30" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C18" s="10">
         <v>5.5E-2</v>
@@ -2865,40 +2866,40 @@
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B19" s="30" t="s">
-        <v>59</v>
-      </c>
-      <c r="C19" s="55">
+        <v>58</v>
+      </c>
+      <c r="C19" s="57">
         <f>Assumptions!C11</f>
         <v>1E-3</v>
       </c>
-      <c r="D19" s="55"/>
-      <c r="E19" s="55"/>
+      <c r="D19" s="57"/>
+      <c r="E19" s="57"/>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B20" s="30" t="s">
-        <v>106</v>
-      </c>
-      <c r="C20" s="56">
+        <v>105</v>
+      </c>
+      <c r="C20" s="58">
         <f>Assumptions!C12</f>
         <v>20000</v>
       </c>
-      <c r="D20" s="56"/>
-      <c r="E20" s="56"/>
+      <c r="D20" s="58"/>
+      <c r="E20" s="58"/>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B21" s="30" t="s">
-        <v>107</v>
-      </c>
-      <c r="C21" s="56">
+        <v>106</v>
+      </c>
+      <c r="C21" s="58">
         <f>Assumptions!C13</f>
         <v>5000</v>
       </c>
-      <c r="D21" s="56"/>
-      <c r="E21" s="56"/>
+      <c r="D21" s="58"/>
+      <c r="E21" s="58"/>
     </row>
     <row r="22" spans="2:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B22" s="32" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C22" s="49">
         <v>135000</v>
@@ -2912,7 +2913,7 @@
     </row>
     <row r="23" spans="2:5" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
       <c r="B23" s="21" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C23" s="22">
         <f>C16+C16*($C$17+C18+$C$19)+$C$20+C22</f>
@@ -2929,7 +2930,7 @@
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B25" s="27" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="26" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -2937,7 +2938,7 @@
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B27" s="30" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C27" s="47">
         <v>4.2057008274716381E-2</v>
@@ -2954,7 +2955,7 @@
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B29" s="21" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C29" s="44">
         <f>C28*C$27/12</f>
@@ -2984,11 +2985,11 @@
       </c>
       <c r="C32" s="24">
         <f>$C$29*D32</f>
-        <v>825.00000000000011</v>
-      </c>
-      <c r="D32" s="50">
+        <v>750.00000000000011</v>
+      </c>
+      <c r="D32" s="59">
         <f>Assumptions!C16</f>
-        <v>5.5E-2</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="33" spans="2:4" x14ac:dyDescent="0.45">
@@ -3006,7 +3007,7 @@
     </row>
     <row r="34" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B34" s="30" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C34" s="24">
         <f t="shared" si="1"/>
@@ -3018,7 +3019,7 @@
     </row>
     <row r="35" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B35" s="30" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C35" s="24">
         <f t="shared" ca="1" si="1"/>
@@ -3055,15 +3056,15 @@
     </row>
     <row r="38" spans="2:4" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
       <c r="B38" s="21" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C38" s="44">
         <f ca="1">C29-SUM(C31:C37)</f>
-        <v>10995.000000000002</v>
+        <v>11070.000000000002</v>
       </c>
       <c r="D38" s="50">
         <f ca="1">C38/C29</f>
-        <v>0.73299999999999998</v>
+        <v>0.73799999999999999</v>
       </c>
     </row>
     <row r="39" spans="2:4" x14ac:dyDescent="0.45">
@@ -3077,7 +3078,7 @@
     </row>
     <row r="41" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B41" s="27" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="43" spans="2:4" x14ac:dyDescent="0.45">
@@ -3108,7 +3109,7 @@
     </row>
     <row r="47" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B47" s="27" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="49" spans="2:5" x14ac:dyDescent="0.45">
@@ -3130,7 +3131,7 @@
     </row>
     <row r="50" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B50" s="30" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C50" s="20">
         <f>C16</f>
@@ -3147,7 +3148,7 @@
     </row>
     <row r="51" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B51" s="30" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C51" s="23">
         <f>C23</f>
@@ -3166,59 +3167,59 @@
       <c r="B52" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="C52" s="53">
+      <c r="C52" s="54">
         <f ca="1">C$38*12</f>
-        <v>131940.00000000003</v>
-      </c>
-      <c r="D52" s="53"/>
-      <c r="E52" s="53"/>
+        <v>132840.00000000003</v>
+      </c>
+      <c r="D52" s="54"/>
+      <c r="E52" s="54"/>
     </row>
     <row r="53" spans="2:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B53" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="C53" s="54">
+      <c r="C53" s="55">
         <f>C$45</f>
         <v>4279905</v>
       </c>
-      <c r="D53" s="54"/>
-      <c r="E53" s="54"/>
+      <c r="D53" s="55"/>
+      <c r="E53" s="55"/>
     </row>
     <row r="54" spans="2:5" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
       <c r="B54" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C54" s="43">
         <f ca="1">RATE(15, $C52*(1+$C$39), -C51, $C53 / (1+$C$39)^15) + $C$39</f>
-        <v>2.7990156949300824E-2</v>
+        <v>2.8217902591055416E-2</v>
       </c>
       <c r="D54" s="43">
         <f t="shared" ref="D54:E54" ca="1" si="2">RATE(15, $C52*(1+$C$39), -D51, $C53 / (1+$C$39)^15) + $C$39</f>
-        <v>2.7991941145339455E-2</v>
+        <v>2.8219689572629422E-2</v>
       </c>
       <c r="E54" s="43">
         <f t="shared" ca="1" si="2"/>
-        <v>3.6315289989234535E-2</v>
+        <v>3.6556441291968569E-2</v>
       </c>
     </row>
     <row r="56" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B56" s="36" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="57" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B57" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="58" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B58" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="59" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B59" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -3252,11 +3253,11 @@
   <sheetData>
     <row r="2" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B2" s="37" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C2" s="38"/>
       <c r="D2" s="37" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.45">
@@ -3266,11 +3267,11 @@
     </row>
     <row r="4" spans="2:4" ht="57" x14ac:dyDescent="0.45">
       <c r="B4" s="39" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C4" s="38"/>
       <c r="D4" s="39" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.45">
@@ -3280,11 +3281,11 @@
     </row>
     <row r="6" spans="2:4" ht="128.25" x14ac:dyDescent="0.45">
       <c r="B6" s="39" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C6" s="38"/>
       <c r="D6" s="39" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.45">
@@ -3294,11 +3295,11 @@
     </row>
     <row r="8" spans="2:4" ht="85.5" x14ac:dyDescent="0.45">
       <c r="B8" s="39" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C8" s="38"/>
       <c r="D8" s="39" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9" spans="2:4" x14ac:dyDescent="0.45">
@@ -3308,11 +3309,11 @@
     </row>
     <row r="10" spans="2:4" ht="85.5" x14ac:dyDescent="0.45">
       <c r="B10" s="39" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C10" s="38"/>
       <c r="D10" s="39" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11" spans="2:4" x14ac:dyDescent="0.45">
@@ -3327,11 +3328,11 @@
     </row>
     <row r="13" spans="2:4" ht="71.25" x14ac:dyDescent="0.45">
       <c r="B13" s="39" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C13" s="38"/>
       <c r="D13" s="39" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14" spans="2:4" x14ac:dyDescent="0.45">
@@ -3341,11 +3342,11 @@
     </row>
     <row r="15" spans="2:4" ht="128.25" x14ac:dyDescent="0.45">
       <c r="B15" s="39" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C15" s="38"/>
       <c r="D15" s="39" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="16" spans="2:4" x14ac:dyDescent="0.45">
@@ -3355,11 +3356,11 @@
     </row>
     <row r="17" spans="2:4" ht="85.5" x14ac:dyDescent="0.45">
       <c r="B17" s="39" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C17" s="38"/>
       <c r="D17" s="39" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>

--- a/financial_models/Res_Property_Monitor.xlsx
+++ b/financial_models/Res_Property_Monitor.xlsx
@@ -8,22 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38AE6517-746D-41FC-B08D-2C49E1E59BC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECA0F2B5-B7D2-4E1A-9B3D-B34CA37BFBF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="6150" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="6150" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Assumptions" sheetId="13" r:id="rId1"/>
     <sheet name="銀海山莊" sheetId="14" r:id="rId2"/>
-    <sheet name="Quarry bay" sheetId="17" r:id="rId3"/>
-    <sheet name="翠荷苑" sheetId="18" r:id="rId4"/>
-    <sheet name="Logic_Summary" sheetId="15" r:id="rId5"/>
+    <sheet name="早禾坑" sheetId="19" r:id="rId3"/>
+    <sheet name="Quarry bay" sheetId="17" r:id="rId4"/>
+    <sheet name="翠荷苑" sheetId="18" r:id="rId5"/>
+    <sheet name="Logic_Summary" sheetId="15" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="AuraStyleDefaultsReset" hidden="1">#N/A</definedName>
     <definedName name="Cap_Rate">Assumptions!$C$5</definedName>
-    <definedName name="HKDCNY">Assumptions!$C$21</definedName>
-    <definedName name="HKDUSD">Assumptions!$C$20</definedName>
+    <definedName name="HKDCNY">Assumptions!$C$23</definedName>
+    <definedName name="HKDUSD">Assumptions!$C$22</definedName>
     <definedName name="Holding_Period">Assumptions!$C$6</definedName>
     <definedName name="Other_Annual_Expense_Percent">Assumptions!#REF!</definedName>
     <definedName name="WW3f877d8e32714ec8a8180854ed7f8276_634328481945590045" hidden="1">#REF!</definedName>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="117">
   <si>
     <t>Value</t>
   </si>
@@ -737,6 +738,30 @@
   </si>
   <si>
     <t>Default NOI tax rate</t>
+  </si>
+  <si>
+    <t>早禾坑</t>
+  </si>
+  <si>
+    <t>House</t>
+  </si>
+  <si>
+    <t>香港40年樓齡的舊樓進行強制驗樓及大維修，一般每戶費用約在 HK$30,000 至 HK$150,000 或更高。</t>
+  </si>
+  <si>
+    <t>一般2%，但村屋招租更麻煩</t>
+  </si>
+  <si>
+    <t>景觀好，升值潛力更高</t>
+  </si>
+  <si>
+    <t>有游泳池，但早禾坑比較遠</t>
+  </si>
+  <si>
+    <t>村務驗樓更貴</t>
+  </si>
+  <si>
+    <t>一般8%，但村屋不交管理費，維護費看物業情況可能較低</t>
   </si>
 </sst>
 </file>
@@ -1018,6 +1043,7 @@
     <xf numFmtId="10" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1033,7 +1059,6 @@
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -1362,7 +1387,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:D49"/>
+  <dimension ref="B2:D51"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="2.59765625" customWidth="1"/>
@@ -1410,250 +1435,266 @@
       <c r="D6" s="4"/>
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B7" t="s">
-        <v>64</v>
-      </c>
-      <c r="C7" s="10">
-        <v>0.02</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>76</v>
-      </c>
+      <c r="C7" s="3"/>
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="C8" s="3"/>
+      <c r="B8" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B9" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>1</v>
+      <c r="B9" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" s="10">
+        <v>0.01</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C10" s="10">
-        <v>0.01</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>52</v>
-      </c>
+        <v>1E-3</v>
+      </c>
+      <c r="D10" s="4"/>
     </row>
     <row r="11" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
-        <v>55</v>
-      </c>
-      <c r="C11" s="10">
-        <v>1E-3</v>
-      </c>
-      <c r="D11" s="4"/>
+        <v>50</v>
+      </c>
+      <c r="C11" s="14">
+        <v>20000</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="12" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C12" s="14">
-        <v>20000</v>
+        <v>5000</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B13" t="s">
-        <v>54</v>
-      </c>
-      <c r="C13" s="14">
-        <v>5000</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="C13" s="3"/>
     </row>
     <row r="14" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="C14" s="3"/>
+      <c r="B14" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B15" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="C15" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D15" s="12" t="s">
-        <v>1</v>
+      <c r="B15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="10">
+        <v>0.05</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="16" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C16" s="10">
-        <v>0.05</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>99</v>
-      </c>
+        <v>0.03</v>
+      </c>
+      <c r="D16" s="4"/>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B17" t="s">
-        <v>26</v>
+        <v>103</v>
       </c>
       <c r="C17" s="10">
-        <v>0.03</v>
-      </c>
-      <c r="D17" s="4"/>
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" s="10">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="19" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B19" s="13" t="s">
+      <c r="B19" t="s">
+        <v>64</v>
+      </c>
+      <c r="C19" s="10">
+        <v>0.02</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B21" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="C19" s="12" t="s">
+      <c r="C21" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="D19" s="12" t="s">
+      <c r="D21" s="12" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B20" t="s">
+    <row r="22" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B22" t="s">
         <v>3</v>
       </c>
-      <c r="C20" s="34">
+      <c r="C22" s="34">
         <v>7.8</v>
       </c>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B21" t="s">
+    <row r="23" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B23" t="s">
         <v>4</v>
       </c>
-      <c r="C21" s="34">
+      <c r="C23" s="34">
         <v>0.89</v>
       </c>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B23" s="1" t="s">
+    <row r="25" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B25" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B24" t="s">
+    <row r="26" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B26" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B25" t="s">
+    <row r="27" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B27" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B27" s="1" t="s">
+    <row r="29" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B29" s="1" t="s">
         <v>20</v>
-      </c>
-    </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B28" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B29" t="s">
-        <v>9</v>
-      </c>
-      <c r="C29" s="2">
-        <v>0.05</v>
       </c>
     </row>
     <row r="30" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B30" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="2">
-        <v>0.08</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B31" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C31" s="2">
-        <v>0.12</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="32" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B32" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="2">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B33" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="2">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="34" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B34" t="s">
         <v>21</v>
       </c>
-      <c r="C32" s="2"/>
-    </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B34" s="1" t="s">
+      <c r="C34" s="2"/>
+    </row>
+    <row r="36" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B36" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="35" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B35" t="s">
+    <row r="37" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B37" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B37" s="1" t="s">
+    <row r="39" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B39" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="38" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B38" t="s">
+    <row r="40" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B40" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="39" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B39" t="s">
+    <row r="41" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B41" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="40" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B40" t="s">
+    <row r="42" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B42" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B42" s="1" t="s">
+    <row r="44" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B44" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="43" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B43" t="s">
+    <row r="45" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B45" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="44" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B44" t="s">
+    <row r="46" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B46" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="45" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B45" t="s">
+    <row r="47" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B47" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="47" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B47" s="1" t="s">
+    <row r="49" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B49" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="48" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B48" t="s">
+    <row r="50" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B50" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="49" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B49" t="s">
+    <row r="51" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B51" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1668,44 +1709,56 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:E59"/>
+  <dimension ref="B2:G59"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
     <col min="2" max="2" width="29.86328125" customWidth="1"/>
-    <col min="3" max="9" width="16.59765625" customWidth="1"/>
+    <col min="3" max="5" width="16.59765625" customWidth="1"/>
+    <col min="6" max="6" width="2.59765625" customWidth="1"/>
+    <col min="7" max="7" width="90.59765625" customWidth="1"/>
+    <col min="8" max="9" width="16.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B2" s="28" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="G2" s="13" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="G3" s="4"/>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B4" s="30" t="s">
         <v>37</v>
       </c>
       <c r="C4" s="15" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="G4" s="4"/>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B5" s="30" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="15" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="G5" s="4"/>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B6" s="30" t="s">
         <v>22</v>
       </c>
       <c r="C6" s="16">
         <v>1997</v>
       </c>
-    </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="G6" s="4"/>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B7" s="30" t="s">
         <v>32</v>
       </c>
@@ -1713,24 +1766,27 @@
         <f ca="1">YEAR(TODAY())-C6</f>
         <v>29</v>
       </c>
-    </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="G7" s="4"/>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B8" s="30" t="s">
         <v>72</v>
       </c>
       <c r="C8" s="18">
         <v>690</v>
       </c>
-    </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="G8" s="4"/>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B9" s="30" t="s">
         <v>73</v>
       </c>
       <c r="C9" s="19">
         <v>2.5</v>
       </c>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="G9" s="4"/>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B10" s="30" t="s">
         <v>34</v>
       </c>
@@ -1738,13 +1794,23 @@
         <f>Holding_Period</f>
         <v>15</v>
       </c>
-    </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="G10" s="4"/>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="G11" s="4"/>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B12" s="27" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="G12" s="13" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="G13" s="4"/>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B14" s="30" t="s">
         <v>35</v>
       </c>
@@ -1757,8 +1823,9 @@
       <c r="E14" s="6" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="G14" s="4"/>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B15" s="31" t="s">
         <v>74</v>
       </c>
@@ -1773,8 +1840,9 @@
         <f>E16/C8</f>
         <v>13623.188405797102</v>
       </c>
-    </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="G15" s="4"/>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B16" s="30" t="s">
         <v>47</v>
       </c>
@@ -1788,19 +1856,21 @@
       <c r="E16" s="40">
         <v>9400000</v>
       </c>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="G16" s="4"/>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B17" s="30" t="s">
         <v>59</v>
       </c>
-      <c r="C17" s="56">
-        <f>Assumptions!C10</f>
+      <c r="C17" s="57">
+        <f>Assumptions!C9</f>
         <v>0.01</v>
       </c>
-      <c r="D17" s="56"/>
-      <c r="E17" s="56"/>
-    </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="D17" s="57"/>
+      <c r="E17" s="57"/>
+      <c r="G17" s="4"/>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B18" s="30" t="s">
         <v>56</v>
       </c>
@@ -1813,41 +1883,45 @@
       <c r="E18" s="53">
         <v>0.03</v>
       </c>
-    </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="G18" s="4"/>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B19" s="30" t="s">
         <v>58</v>
       </c>
-      <c r="C19" s="57">
-        <f>Assumptions!C11</f>
+      <c r="C19" s="58">
+        <f>Assumptions!C10</f>
         <v>1E-3</v>
       </c>
-      <c r="D19" s="57"/>
-      <c r="E19" s="57"/>
-    </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="D19" s="58"/>
+      <c r="E19" s="58"/>
+      <c r="G19" s="4"/>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B20" s="30" t="s">
         <v>105</v>
       </c>
-      <c r="C20" s="58">
-        <f>Assumptions!C12</f>
+      <c r="C20" s="59">
+        <f>Assumptions!C11</f>
         <v>20000</v>
       </c>
-      <c r="D20" s="58"/>
-      <c r="E20" s="58"/>
-    </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="D20" s="59"/>
+      <c r="E20" s="59"/>
+      <c r="G20" s="4"/>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B21" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="C21" s="58">
-        <f>Assumptions!C13</f>
+      <c r="C21" s="59">
+        <f>Assumptions!C12</f>
         <v>5000</v>
       </c>
-      <c r="D21" s="58"/>
-      <c r="E21" s="58"/>
-    </row>
-    <row r="22" spans="2:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="D21" s="59"/>
+      <c r="E21" s="59"/>
+      <c r="G21" s="4"/>
+    </row>
+    <row r="22" spans="2:7" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B22" s="32" t="s">
         <v>102</v>
       </c>
@@ -1860,8 +1934,11 @@
       <c r="E22" s="49">
         <v>150000</v>
       </c>
-    </row>
-    <row r="23" spans="2:5" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="G22" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
       <c r="B23" s="21" t="s">
         <v>60</v>
       </c>
@@ -1877,24 +1954,33 @@
         <f t="shared" si="0"/>
         <v>9960400</v>
       </c>
-    </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="G23" s="4"/>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="G24" s="4"/>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B25" s="27" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="26" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G25" s="13" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C26" s="5"/>
-    </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="G26" s="4"/>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B27" s="30" t="s">
         <v>61</v>
       </c>
       <c r="C27" s="47">
         <v>2.8000000000000001E-2</v>
       </c>
-    </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="G27" s="4"/>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B28" s="31" t="s">
         <v>40</v>
       </c>
@@ -1902,8 +1988,9 @@
         <f>D16</f>
         <v>9660000</v>
       </c>
-    </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="G28" s="4"/>
+    </row>
+    <row r="29" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B29" s="21" t="s">
         <v>62</v>
       </c>
@@ -1911,12 +1998,14 @@
         <f>C28*C$27/12</f>
         <v>22540</v>
       </c>
-    </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="G29" s="4"/>
+    </row>
+    <row r="30" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B30" s="7"/>
       <c r="C30" s="24"/>
-    </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="G30" s="4"/>
+    </row>
+    <row r="31" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B31" s="30" t="s">
         <v>7</v>
       </c>
@@ -1928,8 +2017,9 @@
         <f>C31/C29</f>
         <v>7.6530612244897961E-2</v>
       </c>
-    </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="G31" s="4"/>
+    </row>
+    <row r="32" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B32" s="30" t="s">
         <v>20</v>
       </c>
@@ -1937,12 +2027,13 @@
         <f>$C$29*D32</f>
         <v>1127</v>
       </c>
-      <c r="D32" s="59">
-        <f>Assumptions!C16</f>
+      <c r="D32" s="54">
+        <f>Assumptions!C15</f>
         <v>0.05</v>
       </c>
-    </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="G32" s="4"/>
+    </row>
+    <row r="33" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B33" s="30" t="s">
         <v>26</v>
       </c>
@@ -1951,11 +2042,12 @@
         <v>676.19999999999993</v>
       </c>
       <c r="D33" s="50">
-        <f>Assumptions!C17</f>
+        <f>Assumptions!C16</f>
         <v>0.03</v>
       </c>
-    </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="G33" s="4"/>
+    </row>
+    <row r="34" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B34" s="30" t="s">
         <v>103</v>
       </c>
@@ -1964,10 +2056,12 @@
         <v>1803.2</v>
       </c>
       <c r="D34" s="3">
+        <f>Assumptions!C17</f>
         <v>0.08</v>
       </c>
-    </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="G34" s="4"/>
+    </row>
+    <row r="35" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B35" s="30" t="s">
         <v>104</v>
       </c>
@@ -1979,8 +2073,9 @@
         <f ca="1">IF(C$7&gt;=30,4%,0)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="G35" s="4"/>
+    </row>
+    <row r="36" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B36" s="30" t="s">
         <v>16</v>
       </c>
@@ -1989,10 +2084,12 @@
         <v>450.8</v>
       </c>
       <c r="D36" s="3">
+        <f>Assumptions!C18</f>
         <v>0.02</v>
       </c>
-    </row>
-    <row r="37" spans="2:4" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="G36" s="4"/>
+    </row>
+    <row r="37" spans="2:7" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B37" s="32" t="s">
         <v>41</v>
       </c>
@@ -2003,8 +2100,9 @@
         <f>C37/C29</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="2:4" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="G37" s="4"/>
+    </row>
+    <row r="38" spans="2:7" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
       <c r="B38" s="21" t="s">
         <v>63</v>
       </c>
@@ -2016,30 +2114,44 @@
         <f ca="1">C38/C29</f>
         <v>0.74346938775510196</v>
       </c>
-    </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="G38" s="4"/>
+    </row>
+    <row r="39" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B39" s="21" t="s">
         <v>46</v>
       </c>
       <c r="C39" s="45">
-        <f>Assumptions!C7</f>
+        <f>Assumptions!C19</f>
         <v>0.02</v>
       </c>
-    </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="G39" s="4"/>
+    </row>
+    <row r="40" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="G40" s="4"/>
+    </row>
+    <row r="41" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B41" s="27" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="43" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="G41" s="13" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="G42" s="4"/>
+    </row>
+    <row r="43" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B43" s="30" t="s">
         <v>38</v>
       </c>
       <c r="C43" s="48">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="44" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="G43" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="44" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B44" s="31" t="s">
         <v>42</v>
       </c>
@@ -2047,8 +2159,9 @@
         <f>(1+C43)^(1/C10)-1</f>
         <v>2.268495988716035E-2</v>
       </c>
-    </row>
-    <row r="45" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="G44" s="4"/>
+    </row>
+    <row r="45" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B45" s="21" t="s">
         <v>39</v>
       </c>
@@ -2056,13 +2169,23 @@
         <f>D16*(1+C$43)</f>
         <v>13524000</v>
       </c>
-    </row>
-    <row r="47" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="G45" s="4"/>
+    </row>
+    <row r="46" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="G46" s="4"/>
+    </row>
+    <row r="47" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B47" s="27" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="G47" s="13" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="G48" s="4"/>
+    </row>
+    <row r="49" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B49" s="30" t="s">
         <v>35</v>
       </c>
@@ -2078,8 +2201,9 @@
         <f>E14</f>
         <v>IRR Netural Price</v>
       </c>
-    </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="G49" s="4"/>
+    </row>
+    <row r="50" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B50" s="30" t="s">
         <v>65</v>
       </c>
@@ -2095,8 +2219,9 @@
         <f t="shared" si="2"/>
         <v>9400000</v>
       </c>
-    </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="G50" s="4"/>
+    </row>
+    <row r="51" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B51" s="30" t="s">
         <v>60</v>
       </c>
@@ -2112,30 +2237,33 @@
         <f>E23</f>
         <v>9960400</v>
       </c>
-    </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="G51" s="4"/>
+    </row>
+    <row r="52" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B52" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="C52" s="54">
+      <c r="C52" s="55">
         <f ca="1">C$38*12</f>
         <v>201093.59999999998</v>
       </c>
-      <c r="D52" s="54"/>
-      <c r="E52" s="54"/>
-    </row>
-    <row r="53" spans="2:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="D52" s="55"/>
+      <c r="E52" s="55"/>
+      <c r="G52" s="4"/>
+    </row>
+    <row r="53" spans="2:7" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B53" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="C53" s="55">
+      <c r="C53" s="56">
         <f>C$45</f>
         <v>13524000</v>
       </c>
-      <c r="D53" s="55"/>
-      <c r="E53" s="55"/>
-    </row>
-    <row r="54" spans="2:5" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="D53" s="56"/>
+      <c r="E53" s="56"/>
+      <c r="G53" s="4"/>
+    </row>
+    <row r="54" spans="2:7" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
       <c r="B54" s="21" t="s">
         <v>66</v>
       </c>
@@ -2151,26 +2279,34 @@
         <f t="shared" ca="1" si="3"/>
         <v>4.1100689030016416E-2</v>
       </c>
-    </row>
-    <row r="56" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="G54" s="4"/>
+    </row>
+    <row r="55" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="G55" s="4"/>
+    </row>
+    <row r="56" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B56" s="36" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="57" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="G56" s="4"/>
+    </row>
+    <row r="57" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B57" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="58" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="G57" s="4"/>
+    </row>
+    <row r="58" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B58" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="59" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="G58" s="4"/>
+    </row>
+    <row r="59" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B59" t="s">
         <v>70</v>
       </c>
+      <c r="G59" s="4"/>
     </row>
   </sheetData>
   <dataConsolidate/>
@@ -2188,6 +2324,627 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8456DFB0-53ED-4BEE-BAF6-63FFB679C689}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B2:G59"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="2.6640625" customWidth="1"/>
+    <col min="2" max="2" width="29.86328125" customWidth="1"/>
+    <col min="3" max="5" width="16.59765625" customWidth="1"/>
+    <col min="6" max="6" width="2.59765625" customWidth="1"/>
+    <col min="7" max="7" width="90.59765625" customWidth="1"/>
+    <col min="8" max="9" width="16.59765625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B2" s="28" t="s">
+        <v>77</v>
+      </c>
+      <c r="G2" s="13" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="G3" s="4"/>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B4" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="G4" s="4"/>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B5" s="30" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="G5" s="4"/>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B6" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="16">
+        <v>1995</v>
+      </c>
+      <c r="G6" s="4"/>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B7" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="17">
+        <f ca="1">YEAR(TODAY())-C6</f>
+        <v>31</v>
+      </c>
+      <c r="G7" s="4"/>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B8" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8" s="18">
+        <v>2000</v>
+      </c>
+      <c r="G8" s="4"/>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B9" s="30" t="s">
+        <v>73</v>
+      </c>
+      <c r="C9" s="19">
+        <v>0</v>
+      </c>
+      <c r="G9" s="4"/>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B10" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="46">
+        <f>Holding_Period</f>
+        <v>15</v>
+      </c>
+      <c r="G10" s="4"/>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="G11" s="4"/>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B12" s="27" t="s">
+        <v>79</v>
+      </c>
+      <c r="G12" s="13" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="G13" s="4"/>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B14" s="30" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="G14" s="4"/>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B15" s="31" t="s">
+        <v>74</v>
+      </c>
+      <c r="C15" s="25">
+        <f>C16/C8</f>
+        <v>11000</v>
+      </c>
+      <c r="D15" s="26">
+        <v>10000</v>
+      </c>
+      <c r="E15" s="25">
+        <f>E16/C8</f>
+        <v>8583.3582151174596</v>
+      </c>
+      <c r="G15" s="4"/>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B16" s="30" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" s="14">
+        <v>22000000</v>
+      </c>
+      <c r="D16" s="20">
+        <f>D15*C$8</f>
+        <v>20000000</v>
+      </c>
+      <c r="E16" s="40">
+        <v>17166716.43023492</v>
+      </c>
+      <c r="G16" s="4"/>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B17" s="30" t="s">
+        <v>59</v>
+      </c>
+      <c r="C17" s="57">
+        <f>Assumptions!C9</f>
+        <v>0.01</v>
+      </c>
+      <c r="D17" s="57"/>
+      <c r="E17" s="57"/>
+      <c r="G17" s="4"/>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B18" s="30" t="s">
+        <v>56</v>
+      </c>
+      <c r="C18" s="53">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="D18" s="53">
+        <v>3.4500000000000003E-2</v>
+      </c>
+      <c r="E18" s="53">
+        <v>0.03</v>
+      </c>
+      <c r="G18" s="4"/>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B19" s="30" t="s">
+        <v>58</v>
+      </c>
+      <c r="C19" s="58">
+        <f>Assumptions!C10</f>
+        <v>1E-3</v>
+      </c>
+      <c r="D19" s="58"/>
+      <c r="E19" s="58"/>
+      <c r="G19" s="4"/>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B20" s="30" t="s">
+        <v>105</v>
+      </c>
+      <c r="C20" s="59">
+        <f>Assumptions!C11</f>
+        <v>20000</v>
+      </c>
+      <c r="D20" s="59"/>
+      <c r="E20" s="59"/>
+      <c r="G20" s="4"/>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B21" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="C21" s="59">
+        <v>10000</v>
+      </c>
+      <c r="D21" s="59"/>
+      <c r="E21" s="59"/>
+      <c r="G21" s="4" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B22" s="32" t="s">
+        <v>102</v>
+      </c>
+      <c r="C22" s="49">
+        <v>150000</v>
+      </c>
+      <c r="D22" s="49">
+        <v>150000</v>
+      </c>
+      <c r="E22" s="49">
+        <v>150000</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="B23" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="C23" s="22">
+        <f>C16+C16*($C$17+C18+$C$19)+$C$20+$C$21+C22</f>
+        <v>23247000</v>
+      </c>
+      <c r="D23" s="22">
+        <f t="shared" ref="D23:E23" si="0">D16+D16*($C$17+D18+$C$19)+$C$20+$C$21+D22</f>
+        <v>21090000</v>
+      </c>
+      <c r="E23" s="22">
+        <f t="shared" si="0"/>
+        <v>18050551.803874552</v>
+      </c>
+      <c r="G23" s="4"/>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="G24" s="4"/>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B25" s="27" t="s">
+        <v>78</v>
+      </c>
+      <c r="G25" s="13" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C26" s="5"/>
+      <c r="G26" s="4"/>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B27" s="30" t="s">
+        <v>61</v>
+      </c>
+      <c r="C27" s="47">
+        <v>3.3000000000000015E-2</v>
+      </c>
+      <c r="G27" s="4"/>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B28" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="C28" s="29">
+        <f>D16</f>
+        <v>20000000</v>
+      </c>
+      <c r="G28" s="4"/>
+    </row>
+    <row r="29" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B29" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="C29" s="44">
+        <f>C28*C$27/12</f>
+        <v>55000.000000000029</v>
+      </c>
+      <c r="G29" s="4"/>
+    </row>
+    <row r="30" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B30" s="7"/>
+      <c r="C30" s="24"/>
+      <c r="G30" s="4"/>
+    </row>
+    <row r="31" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B31" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="24">
+        <f>C$9*C$8</f>
+        <v>0</v>
+      </c>
+      <c r="D31" s="50">
+        <f>C31/C29</f>
+        <v>0</v>
+      </c>
+      <c r="G31" s="4"/>
+    </row>
+    <row r="32" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B32" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="C32" s="24">
+        <f>$C$29*D32</f>
+        <v>2750.0000000000018</v>
+      </c>
+      <c r="D32" s="54">
+        <f>Assumptions!C15</f>
+        <v>0.05</v>
+      </c>
+      <c r="G32" s="4"/>
+    </row>
+    <row r="33" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B33" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="C33" s="24">
+        <f t="shared" ref="C33:C36" si="1">$C$29*D33</f>
+        <v>1650.0000000000009</v>
+      </c>
+      <c r="D33" s="50">
+        <f>Assumptions!C16</f>
+        <v>0.03</v>
+      </c>
+      <c r="G33" s="4"/>
+    </row>
+    <row r="34" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B34" s="30" t="s">
+        <v>103</v>
+      </c>
+      <c r="C34" s="24">
+        <f t="shared" si="1"/>
+        <v>1100.0000000000007</v>
+      </c>
+      <c r="D34" s="3">
+        <v>0.02</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B35" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="C35" s="24">
+        <f t="shared" si="1"/>
+        <v>550.00000000000034</v>
+      </c>
+      <c r="D35" s="3">
+        <v>0.01</v>
+      </c>
+      <c r="G35" s="4"/>
+    </row>
+    <row r="36" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B36" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="C36" s="24">
+        <f t="shared" si="1"/>
+        <v>5500.0000000000036</v>
+      </c>
+      <c r="D36" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="37" spans="2:7" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B37" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="C37" s="51">
+        <v>0</v>
+      </c>
+      <c r="D37" s="52">
+        <f>C37/C29</f>
+        <v>0</v>
+      </c>
+      <c r="G37" s="4"/>
+    </row>
+    <row r="38" spans="2:7" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="B38" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="C38" s="44">
+        <f>C29-SUM(C31:C37)</f>
+        <v>43450.000000000022</v>
+      </c>
+      <c r="D38" s="50">
+        <f>C38/C29</f>
+        <v>0.78999999999999992</v>
+      </c>
+      <c r="G38" s="4"/>
+    </row>
+    <row r="39" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B39" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="C39" s="45">
+        <f>Assumptions!C19</f>
+        <v>0.02</v>
+      </c>
+      <c r="G39" s="4"/>
+    </row>
+    <row r="40" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="G40" s="4"/>
+    </row>
+    <row r="41" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B41" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="G41" s="13" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="G42" s="4"/>
+    </row>
+    <row r="43" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B43" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="C43" s="48">
+        <v>0.3</v>
+      </c>
+      <c r="G43" s="4" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="44" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B44" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="C44" s="41">
+        <f>(1+C43)^(1/C10)-1</f>
+        <v>1.7644813405053306E-2</v>
+      </c>
+      <c r="G44" s="4"/>
+    </row>
+    <row r="45" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B45" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="C45" s="42">
+        <f>D16*(1+C$43)</f>
+        <v>26000000</v>
+      </c>
+      <c r="G45" s="4"/>
+    </row>
+    <row r="46" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="G46" s="4"/>
+    </row>
+    <row r="47" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B47" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="G47" s="13" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="G48" s="4"/>
+    </row>
+    <row r="49" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B49" s="30" t="s">
+        <v>35</v>
+      </c>
+      <c r="C49" s="35" t="str">
+        <f>C14</f>
+        <v>Asking Price</v>
+      </c>
+      <c r="D49" s="35" t="str">
+        <f>D14</f>
+        <v>Comparable</v>
+      </c>
+      <c r="E49" s="35" t="str">
+        <f>E14</f>
+        <v>IRR Netural Price</v>
+      </c>
+      <c r="G49" s="4"/>
+    </row>
+    <row r="50" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B50" s="30" t="s">
+        <v>65</v>
+      </c>
+      <c r="C50" s="20">
+        <f>C16</f>
+        <v>22000000</v>
+      </c>
+      <c r="D50" s="20">
+        <f t="shared" ref="D50:E50" si="2">D16</f>
+        <v>20000000</v>
+      </c>
+      <c r="E50" s="20">
+        <f t="shared" si="2"/>
+        <v>17166716.43023492</v>
+      </c>
+      <c r="G50" s="4"/>
+    </row>
+    <row r="51" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B51" s="30" t="s">
+        <v>60</v>
+      </c>
+      <c r="C51" s="23">
+        <f>C23</f>
+        <v>23247000</v>
+      </c>
+      <c r="D51" s="23">
+        <f>D23</f>
+        <v>21090000</v>
+      </c>
+      <c r="E51" s="23">
+        <f>E23</f>
+        <v>18050551.803874552</v>
+      </c>
+      <c r="G51" s="4"/>
+    </row>
+    <row r="52" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B52" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="C52" s="55">
+        <f>C$38*12</f>
+        <v>521400.00000000023</v>
+      </c>
+      <c r="D52" s="55"/>
+      <c r="E52" s="55"/>
+      <c r="G52" s="4"/>
+    </row>
+    <row r="53" spans="2:7" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B53" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C53" s="56">
+        <f>C$45</f>
+        <v>26000000</v>
+      </c>
+      <c r="D53" s="56"/>
+      <c r="E53" s="56"/>
+      <c r="G53" s="4"/>
+    </row>
+    <row r="54" spans="2:7" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="B54" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="C54" s="43">
+        <f>RATE(15, $C52*(1+$C$39), -C51, $C53 / (1+$C$39)^15) + $C$39</f>
+        <v>3.2569232155100998E-2</v>
+      </c>
+      <c r="D54" s="43">
+        <f t="shared" ref="D54:E54" si="3">RATE(15, $C52*(1+$C$39), -D51, $C53 / (1+$C$39)^15) + $C$39</f>
+        <v>4.0372636869005607E-2</v>
+      </c>
+      <c r="E54" s="43">
+        <f t="shared" si="3"/>
+        <v>5.3153227719921953E-2</v>
+      </c>
+      <c r="G54" s="4"/>
+    </row>
+    <row r="55" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="G55" s="4"/>
+    </row>
+    <row r="56" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B56" s="36" t="s">
+        <v>67</v>
+      </c>
+      <c r="G56" s="4"/>
+    </row>
+    <row r="57" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B57" t="s">
+        <v>68</v>
+      </c>
+      <c r="G57" s="4"/>
+    </row>
+    <row r="58" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B58" t="s">
+        <v>69</v>
+      </c>
+      <c r="G58" s="4"/>
+    </row>
+    <row r="59" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B59" t="s">
+        <v>70</v>
+      </c>
+      <c r="G59" s="4"/>
+    </row>
+  </sheetData>
+  <dataConsolidate/>
+  <mergeCells count="6">
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="C52:E52"/>
+    <mergeCell ref="C53:E53"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="97" fitToWidth="0" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{443574DC-9638-4865-B3ED-3B836FA95BE0}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -2317,12 +3074,12 @@
       <c r="B17" s="30" t="s">
         <v>59</v>
       </c>
-      <c r="C17" s="56">
-        <f>Assumptions!C10</f>
+      <c r="C17" s="57">
+        <f>Assumptions!C9</f>
         <v>0.01</v>
       </c>
-      <c r="D17" s="56"/>
-      <c r="E17" s="56"/>
+      <c r="D17" s="57"/>
+      <c r="E17" s="57"/>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B18" s="30" t="s">
@@ -2342,34 +3099,34 @@
       <c r="B19" s="30" t="s">
         <v>58</v>
       </c>
-      <c r="C19" s="57">
-        <f>Assumptions!C11</f>
+      <c r="C19" s="58">
+        <f>Assumptions!C10</f>
         <v>1E-3</v>
       </c>
-      <c r="D19" s="57"/>
-      <c r="E19" s="57"/>
+      <c r="D19" s="58"/>
+      <c r="E19" s="58"/>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B20" s="30" t="s">
         <v>105</v>
       </c>
-      <c r="C20" s="58">
-        <f>Assumptions!C12</f>
+      <c r="C20" s="59">
+        <f>Assumptions!C11</f>
         <v>20000</v>
       </c>
-      <c r="D20" s="58"/>
-      <c r="E20" s="58"/>
+      <c r="D20" s="59"/>
+      <c r="E20" s="59"/>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B21" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="C21" s="58">
-        <f>Assumptions!C13</f>
+      <c r="C21" s="59">
+        <f>Assumptions!C12</f>
         <v>5000</v>
       </c>
-      <c r="D21" s="58"/>
-      <c r="E21" s="58"/>
+      <c r="D21" s="59"/>
+      <c r="E21" s="59"/>
     </row>
     <row r="22" spans="2:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B22" s="32" t="s">
@@ -2461,8 +3218,8 @@
         <f>$C$29*D32</f>
         <v>971.01041666666663</v>
       </c>
-      <c r="D32" s="59">
-        <f>Assumptions!C16</f>
+      <c r="D32" s="54">
+        <f>Assumptions!C15</f>
         <v>0.05</v>
       </c>
     </row>
@@ -2475,7 +3232,7 @@
         <v>582.60624999999993</v>
       </c>
       <c r="D33" s="50">
-        <f>Assumptions!C17</f>
+        <f>Assumptions!C16</f>
         <v>0.03</v>
       </c>
     </row>
@@ -2488,6 +3245,7 @@
         <v>1553.6166666666666</v>
       </c>
       <c r="D34" s="3">
+        <f>Assumptions!C17</f>
         <v>0.08</v>
       </c>
     </row>
@@ -2513,6 +3271,7 @@
         <v>388.40416666666664</v>
       </c>
       <c r="D36" s="3">
+        <f>Assumptions!C18</f>
         <v>0.02</v>
       </c>
     </row>
@@ -2546,7 +3305,7 @@
         <v>46</v>
       </c>
       <c r="C39" s="45">
-        <f>Assumptions!C7</f>
+        <f>Assumptions!C19</f>
         <v>0.02</v>
       </c>
     </row>
@@ -2641,23 +3400,23 @@
       <c r="B52" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="C52" s="54">
+      <c r="C52" s="55">
         <f ca="1">C$38*12</f>
         <v>178290.85</v>
       </c>
-      <c r="D52" s="54"/>
-      <c r="E52" s="54"/>
+      <c r="D52" s="55"/>
+      <c r="E52" s="55"/>
     </row>
     <row r="53" spans="2:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B53" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="C53" s="55">
+      <c r="C53" s="56">
         <f>C$45</f>
         <v>9772750</v>
       </c>
-      <c r="D53" s="55"/>
-      <c r="E53" s="55"/>
+      <c r="D53" s="56"/>
+      <c r="E53" s="56"/>
     </row>
     <row r="54" spans="2:5" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
       <c r="B54" s="21" t="s">
@@ -2711,7 +3470,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D09B748-33FA-4405-BB75-AAF1632A9069}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -2841,12 +3600,12 @@
       <c r="B17" s="30" t="s">
         <v>59</v>
       </c>
-      <c r="C17" s="56">
-        <f>Assumptions!C10</f>
+      <c r="C17" s="57">
+        <f>Assumptions!C9</f>
         <v>0.01</v>
       </c>
-      <c r="D17" s="56"/>
-      <c r="E17" s="56"/>
+      <c r="D17" s="57"/>
+      <c r="E17" s="57"/>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B18" s="30" t="s">
@@ -2868,34 +3627,34 @@
       <c r="B19" s="30" t="s">
         <v>58</v>
       </c>
-      <c r="C19" s="57">
-        <f>Assumptions!C11</f>
+      <c r="C19" s="58">
+        <f>Assumptions!C10</f>
         <v>1E-3</v>
       </c>
-      <c r="D19" s="57"/>
-      <c r="E19" s="57"/>
+      <c r="D19" s="58"/>
+      <c r="E19" s="58"/>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B20" s="30" t="s">
         <v>105</v>
       </c>
-      <c r="C20" s="58">
-        <f>Assumptions!C12</f>
+      <c r="C20" s="59">
+        <f>Assumptions!C11</f>
         <v>20000</v>
       </c>
-      <c r="D20" s="58"/>
-      <c r="E20" s="58"/>
+      <c r="D20" s="59"/>
+      <c r="E20" s="59"/>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B21" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="C21" s="58">
-        <f>Assumptions!C13</f>
+      <c r="C21" s="59">
+        <f>Assumptions!C12</f>
         <v>5000</v>
       </c>
-      <c r="D21" s="58"/>
-      <c r="E21" s="58"/>
+      <c r="D21" s="59"/>
+      <c r="E21" s="59"/>
     </row>
     <row r="22" spans="2:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B22" s="32" t="s">
@@ -2987,8 +3746,8 @@
         <f>$C$29*D32</f>
         <v>750.00000000000011</v>
       </c>
-      <c r="D32" s="59">
-        <f>Assumptions!C16</f>
+      <c r="D32" s="54">
+        <f>Assumptions!C15</f>
         <v>0.05</v>
       </c>
     </row>
@@ -3001,7 +3760,7 @@
         <v>450.00000000000006</v>
       </c>
       <c r="D33" s="50">
-        <f>Assumptions!C17</f>
+        <f>Assumptions!C16</f>
         <v>0.03</v>
       </c>
     </row>
@@ -3014,6 +3773,7 @@
         <v>1200.0000000000002</v>
       </c>
       <c r="D34" s="3">
+        <f>Assumptions!C17</f>
         <v>0.08</v>
       </c>
     </row>
@@ -3039,6 +3799,7 @@
         <v>300.00000000000006</v>
       </c>
       <c r="D36" s="3">
+        <f>Assumptions!C18</f>
         <v>0.02</v>
       </c>
     </row>
@@ -3072,7 +3833,7 @@
         <v>46</v>
       </c>
       <c r="C39" s="45">
-        <f>Assumptions!C7</f>
+        <f>Assumptions!C19</f>
         <v>0.02</v>
       </c>
     </row>
@@ -3167,23 +3928,23 @@
       <c r="B52" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="C52" s="54">
+      <c r="C52" s="55">
         <f ca="1">C$38*12</f>
         <v>132840.00000000003</v>
       </c>
-      <c r="D52" s="54"/>
-      <c r="E52" s="54"/>
+      <c r="D52" s="55"/>
+      <c r="E52" s="55"/>
     </row>
     <row r="53" spans="2:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B53" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="C53" s="55">
+      <c r="C53" s="56">
         <f>C$45</f>
         <v>4279905</v>
       </c>
-      <c r="D53" s="55"/>
-      <c r="E53" s="55"/>
+      <c r="D53" s="56"/>
+      <c r="E53" s="56"/>
     </row>
     <row r="54" spans="2:5" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
       <c r="B54" s="21" t="s">
@@ -3237,7 +3998,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45BF1B36-25FE-4F70-8854-2FC395D8FBE5}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>

--- a/financial_models/Res_Property_Monitor.xlsx
+++ b/financial_models/Res_Property_Monitor.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECA0F2B5-B7D2-4E1A-9B3D-B34CA37BFBF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08816543-49A7-459A-8D52-6B61DD807D47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="6150" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="6150" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Assumptions" sheetId="13" r:id="rId1"/>
@@ -704,9 +704,6 @@
     <t>IRR Netural Price</t>
   </si>
   <si>
-    <t>typical unlevered hurdle rates range from 4.0%–5.0%</t>
-  </si>
-  <si>
     <t>銀海山莊</t>
   </si>
   <si>
@@ -762,6 +759,9 @@
   </si>
   <si>
     <t>一般8%，但村屋不交管理費，維護費看物業情況可能較低</t>
+  </si>
+  <si>
+    <t>潘石屹 suggested to use at least the Mortgage rate.</t>
   </si>
 </sst>
 </file>
@@ -1422,7 +1422,7 @@
         <v>0.04</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>97</v>
+        <v>116</v>
       </c>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.45">
@@ -1439,7 +1439,7 @@
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B8" s="13" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C8" s="12" t="s">
         <v>0</v>
@@ -1452,7 +1452,7 @@
       <c r="B9" t="s">
         <v>51</v>
       </c>
-      <c r="C9" s="10">
+      <c r="C9" s="53">
         <v>0.01</v>
       </c>
       <c r="D9" s="4" t="s">
@@ -1463,7 +1463,7 @@
       <c r="B10" t="s">
         <v>55</v>
       </c>
-      <c r="C10" s="10">
+      <c r="C10" s="53">
         <v>1E-3</v>
       </c>
       <c r="D10" s="4"/>
@@ -1472,7 +1472,7 @@
       <c r="B11" t="s">
         <v>50</v>
       </c>
-      <c r="C11" s="14">
+      <c r="C11" s="40">
         <v>20000</v>
       </c>
       <c r="D11" s="4" t="s">
@@ -1483,7 +1483,7 @@
       <c r="B12" t="s">
         <v>54</v>
       </c>
-      <c r="C12" s="14">
+      <c r="C12" s="40">
         <v>5000</v>
       </c>
       <c r="D12" s="4" t="s">
@@ -1495,7 +1495,7 @@
     </row>
     <row r="14" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B14" s="13" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C14" s="12" t="s">
         <v>0</v>
@@ -1508,25 +1508,25 @@
       <c r="B15" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="10">
+      <c r="C15" s="53">
         <v>0.05</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="16" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="10">
+      <c r="C16" s="53">
         <v>0.03</v>
       </c>
       <c r="D16" s="4"/>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B17" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C17" s="10">
         <v>0.08</v>
@@ -1736,7 +1736,7 @@
         <v>37</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G4" s="4"/>
     </row>
@@ -1899,7 +1899,7 @@
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B20" s="30" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C20" s="59">
         <f>Assumptions!C11</f>
@@ -1911,7 +1911,7 @@
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B21" s="30" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C21" s="59">
         <f>Assumptions!C12</f>
@@ -1923,7 +1923,7 @@
     </row>
     <row r="22" spans="2:7" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B22" s="32" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C22" s="49">
         <v>150000</v>
@@ -1935,7 +1935,7 @@
         <v>150000</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="23" spans="2:7" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
@@ -2049,7 +2049,7 @@
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B34" s="30" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C34" s="24">
         <f t="shared" si="1"/>
@@ -2063,7 +2063,7 @@
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B35" s="30" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C35" s="24">
         <f t="shared" ca="1" si="1"/>
@@ -2148,7 +2148,7 @@
         <v>0.4</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.45">
@@ -2355,7 +2355,7 @@
         <v>37</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G4" s="4"/>
     </row>
@@ -2364,7 +2364,7 @@
         <v>5</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G5" s="4"/>
     </row>
@@ -2518,7 +2518,7 @@
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B20" s="30" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C20" s="59">
         <f>Assumptions!C11</f>
@@ -2530,7 +2530,7 @@
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B21" s="30" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C21" s="59">
         <v>10000</v>
@@ -2538,12 +2538,12 @@
       <c r="D21" s="59"/>
       <c r="E21" s="59"/>
       <c r="G21" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="22" spans="2:7" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B22" s="32" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C22" s="49">
         <v>150000</v>
@@ -2555,7 +2555,7 @@
         <v>150000</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="23" spans="2:7" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
@@ -2669,7 +2669,7 @@
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B34" s="30" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C34" s="24">
         <f t="shared" si="1"/>
@@ -2679,12 +2679,12 @@
         <v>0.02</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B35" s="30" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C35" s="24">
         <f t="shared" si="1"/>
@@ -2707,7 +2707,7 @@
         <v>0.1</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="37" spans="2:7" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -2769,7 +2769,7 @@
         <v>0.3</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.45">
@@ -2932,12 +2932,12 @@
   </sheetData>
   <dataConsolidate/>
   <mergeCells count="6">
+    <mergeCell ref="C53:E53"/>
     <mergeCell ref="C17:E17"/>
     <mergeCell ref="C19:E19"/>
     <mergeCell ref="C20:E20"/>
     <mergeCell ref="C21:E21"/>
     <mergeCell ref="C52:E52"/>
-    <mergeCell ref="C53:E53"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="97" fitToWidth="0" orientation="portrait" verticalDpi="0" r:id="rId1"/>
@@ -2967,7 +2967,7 @@
         <v>37</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.45">
@@ -3108,7 +3108,7 @@
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B20" s="30" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C20" s="59">
         <f>Assumptions!C11</f>
@@ -3119,7 +3119,7 @@
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B21" s="30" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C21" s="59">
         <f>Assumptions!C12</f>
@@ -3130,7 +3130,7 @@
     </row>
     <row r="22" spans="2:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B22" s="32" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C22" s="49">
         <v>0</v>
@@ -3238,7 +3238,7 @@
     </row>
     <row r="34" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B34" s="30" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C34" s="24">
         <f t="shared" si="1"/>
@@ -3251,7 +3251,7 @@
     </row>
     <row r="35" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B35" s="30" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C35" s="24">
         <f t="shared" ca="1" si="1"/>
@@ -3493,7 +3493,7 @@
         <v>37</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.45">
@@ -3636,7 +3636,7 @@
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B20" s="30" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C20" s="59">
         <f>Assumptions!C11</f>
@@ -3647,7 +3647,7 @@
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B21" s="30" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C21" s="59">
         <f>Assumptions!C12</f>
@@ -3658,7 +3658,7 @@
     </row>
     <row r="22" spans="2:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B22" s="32" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C22" s="49">
         <v>135000</v>
@@ -3766,7 +3766,7 @@
     </row>
     <row r="34" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B34" s="30" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C34" s="24">
         <f t="shared" si="1"/>
@@ -3779,7 +3779,7 @@
     </row>
     <row r="35" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B35" s="30" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C35" s="24">
         <f t="shared" ca="1" si="1"/>

--- a/financial_models/Res_Property_Monitor.xlsx
+++ b/financial_models/Res_Property_Monitor.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08816543-49A7-459A-8D52-6B61DD807D47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{531730FD-ED7A-4E96-8E30-B326D23403BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="6150" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="6150" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Assumptions" sheetId="13" r:id="rId1"/>
@@ -1419,7 +1419,8 @@
         <v>33</v>
       </c>
       <c r="C5" s="10">
-        <v>0.04</v>
+        <f>2.75%+1.5%</f>
+        <v>4.2499999999999996E-2</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>116</v>
@@ -1529,7 +1530,7 @@
         <v>102</v>
       </c>
       <c r="C17" s="10">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.45">
@@ -1838,7 +1839,7 @@
       </c>
       <c r="E15" s="25">
         <f>E16/C8</f>
-        <v>13623.188405797102</v>
+        <v>13333.333333333334</v>
       </c>
       <c r="G15" s="4"/>
     </row>
@@ -1854,7 +1855,7 @@
         <v>9660000</v>
       </c>
       <c r="E16" s="40">
-        <v>9400000</v>
+        <v>9200000</v>
       </c>
       <c r="G16" s="4"/>
     </row>
@@ -1952,7 +1953,7 @@
       </c>
       <c r="E23" s="22">
         <f t="shared" si="0"/>
-        <v>9960400</v>
+        <v>9752200</v>
       </c>
       <c r="G23" s="4"/>
     </row>
@@ -2053,11 +2054,11 @@
       </c>
       <c r="C34" s="24">
         <f t="shared" si="1"/>
-        <v>1803.2</v>
+        <v>1127</v>
       </c>
       <c r="D34" s="3">
         <f>Assumptions!C17</f>
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="G34" s="4"/>
     </row>
@@ -2070,7 +2071,7 @@
         <v>0</v>
       </c>
       <c r="D35" s="3">
-        <f ca="1">IF(C$7&gt;=30,4%,0)</f>
+        <f ca="1">IF(C$7&gt;=30,2%,0)</f>
         <v>0</v>
       </c>
       <c r="G35" s="4"/>
@@ -2108,11 +2109,11 @@
       </c>
       <c r="C38" s="44">
         <f ca="1">C29-SUM(C31:C37)</f>
-        <v>16757.8</v>
+        <v>17434</v>
       </c>
       <c r="D38" s="50">
         <f ca="1">C38/C29</f>
-        <v>0.74346938775510196</v>
+        <v>0.77346938775510199</v>
       </c>
       <c r="G38" s="4"/>
     </row>
@@ -2217,7 +2218,7 @@
       </c>
       <c r="E50" s="20">
         <f t="shared" si="2"/>
-        <v>9400000</v>
+        <v>9200000</v>
       </c>
       <c r="G50" s="4"/>
     </row>
@@ -2235,7 +2236,7 @@
       </c>
       <c r="E51" s="23">
         <f>E23</f>
-        <v>9960400</v>
+        <v>9752200</v>
       </c>
       <c r="G51" s="4"/>
     </row>
@@ -2245,7 +2246,7 @@
       </c>
       <c r="C52" s="55">
         <f ca="1">C$38*12</f>
-        <v>201093.59999999998</v>
+        <v>209208</v>
       </c>
       <c r="D52" s="55"/>
       <c r="E52" s="55"/>
@@ -2269,15 +2270,15 @@
       </c>
       <c r="C54" s="43">
         <f ca="1">RATE(15, $C52*(1+$C$39), -C51, $C53 / (1+$C$39)^15) + $C$39</f>
-        <v>1.9116404699180176E-2</v>
+        <v>1.9819704376533902E-2</v>
       </c>
       <c r="D54" s="43">
         <f t="shared" ref="D54:E54" ca="1" si="3">RATE(15, $C52*(1+$C$39), -D51, $C53 / (1+$C$39)^15) + $C$39</f>
-        <v>3.867937769139583E-2</v>
+        <v>3.9492442229939861E-2</v>
       </c>
       <c r="E54" s="43">
         <f t="shared" ca="1" si="3"/>
-        <v>4.1100689030016416E-2</v>
+        <v>4.3593380984128127E-2</v>
       </c>
       <c r="G54" s="4"/>
     </row>
@@ -2457,7 +2458,7 @@
       </c>
       <c r="E15" s="25">
         <f>E16/C8</f>
-        <v>8583.3582151174596</v>
+        <v>9750</v>
       </c>
       <c r="G15" s="4"/>
     </row>
@@ -2473,7 +2474,7 @@
         <v>20000000</v>
       </c>
       <c r="E16" s="40">
-        <v>17166716.43023492</v>
+        <v>19500000</v>
       </c>
       <c r="G16" s="4"/>
     </row>
@@ -2572,7 +2573,7 @@
       </c>
       <c r="E23" s="22">
         <f t="shared" si="0"/>
-        <v>18050551.803874552</v>
+        <v>20479500</v>
       </c>
       <c r="G23" s="4"/>
     </row>
@@ -2838,7 +2839,7 @@
       </c>
       <c r="E50" s="20">
         <f t="shared" si="2"/>
-        <v>17166716.43023492</v>
+        <v>19500000</v>
       </c>
       <c r="G50" s="4"/>
     </row>
@@ -2856,7 +2857,7 @@
       </c>
       <c r="E51" s="23">
         <f>E23</f>
-        <v>18050551.803874552</v>
+        <v>20479500</v>
       </c>
       <c r="G51" s="4"/>
     </row>
@@ -2898,7 +2899,7 @@
       </c>
       <c r="E54" s="43">
         <f t="shared" si="3"/>
-        <v>5.3153227719921953E-2</v>
+        <v>4.2755034579381089E-2</v>
       </c>
       <c r="G54" s="4"/>
     </row>
@@ -3052,7 +3053,7 @@
       </c>
       <c r="E15" s="25">
         <f>E16/C8</f>
-        <v>14538.53385789773</v>
+        <v>14969.072164948453</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.45">
@@ -3067,7 +3068,7 @@
         <v>7517500</v>
       </c>
       <c r="E16" s="40">
-        <v>7051188.9210803993</v>
+        <v>7260000</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.45">
@@ -3156,7 +3157,7 @@
       </c>
       <c r="E23" s="22">
         <f t="shared" si="0"/>
-        <v>7360287.6668446958</v>
+        <v>7577660</v>
       </c>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.45">
@@ -3242,11 +3243,11 @@
       </c>
       <c r="C34" s="24">
         <f t="shared" si="1"/>
-        <v>1553.6166666666666</v>
+        <v>971.01041666666663</v>
       </c>
       <c r="D34" s="3">
         <f>Assumptions!C17</f>
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="35" spans="2:4" x14ac:dyDescent="0.45">
@@ -3258,7 +3259,7 @@
         <v>0</v>
       </c>
       <c r="D35" s="3">
-        <f ca="1">IF(C$7&gt;=30,4%,0)</f>
+        <f ca="1">IF(C$7&gt;=30,2%,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -3293,11 +3294,11 @@
       </c>
       <c r="C38" s="44">
         <f ca="1">C29-SUM(C31:C37)</f>
-        <v>14857.570833333333</v>
+        <v>15440.177083333332</v>
       </c>
       <c r="D38" s="50">
         <f ca="1">C38/C29</f>
-        <v>0.76505723204994802</v>
+        <v>0.79505723204994794</v>
       </c>
     </row>
     <row r="39" spans="2:4" x14ac:dyDescent="0.45">
@@ -3376,7 +3377,7 @@
       </c>
       <c r="E50" s="20">
         <f>E16</f>
-        <v>7051188.9210803993</v>
+        <v>7260000</v>
       </c>
     </row>
     <row r="51" spans="2:5" x14ac:dyDescent="0.45">
@@ -3393,7 +3394,7 @@
       </c>
       <c r="E51" s="23">
         <f>E23</f>
-        <v>7360287.6668446958</v>
+        <v>7577660</v>
       </c>
     </row>
     <row r="52" spans="2:5" x14ac:dyDescent="0.45">
@@ -3402,7 +3403,7 @@
       </c>
       <c r="C52" s="55">
         <f ca="1">C$38*12</f>
-        <v>178290.85</v>
+        <v>185282.125</v>
       </c>
       <c r="D52" s="55"/>
       <c r="E52" s="55"/>
@@ -3424,15 +3425,15 @@
       </c>
       <c r="C54" s="43">
         <f ca="1">RATE(15, $C52*(1+$C$39), -C51, $C53 / (1+$C$39)^15) + $C$39</f>
-        <v>3.5914364953040269E-2</v>
+        <v>3.6832714190914793E-2</v>
       </c>
       <c r="D54" s="43">
         <f t="shared" ref="D54:E54" ca="1" si="2">RATE(15, $C52*(1+$C$39), -D51, $C53 / (1+$C$39)^15) + $C$39</f>
-        <v>3.8835369911174707E-2</v>
+        <v>3.9773599542230753E-2</v>
       </c>
       <c r="E54" s="43">
         <f t="shared" ca="1" si="2"/>
-        <v>4.3952064966571072E-2</v>
+        <v>4.2570446092166862E-2</v>
       </c>
     </row>
     <row r="56" spans="2:5" x14ac:dyDescent="0.45">
@@ -3578,7 +3579,7 @@
       </c>
       <c r="E15" s="25">
         <f>E16/C8</f>
-        <v>12262.119150039165</v>
+        <v>11619.047619047618</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.45">
@@ -3593,7 +3594,7 @@
         <v>4279905</v>
       </c>
       <c r="E16" s="40">
-        <v>3862567.5322623369</v>
+        <v>3660000</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.45">
@@ -3684,7 +3685,7 @@
       </c>
       <c r="E23" s="22">
         <f t="shared" si="0"/>
-        <v>4272496.989391651</v>
+        <v>4056560</v>
       </c>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.45">
@@ -3770,11 +3771,11 @@
       </c>
       <c r="C34" s="24">
         <f t="shared" si="1"/>
-        <v>1200.0000000000002</v>
+        <v>750.00000000000011</v>
       </c>
       <c r="D34" s="3">
         <f>Assumptions!C17</f>
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="35" spans="2:4" x14ac:dyDescent="0.45">
@@ -3783,11 +3784,11 @@
       </c>
       <c r="C35" s="24">
         <f t="shared" ca="1" si="1"/>
-        <v>600.00000000000011</v>
+        <v>300.00000000000006</v>
       </c>
       <c r="D35" s="3">
-        <f ca="1">IF(C$7&gt;=30,4%,0)</f>
-        <v>0.04</v>
+        <f ca="1">IF(C$7&gt;=30,2%,0)</f>
+        <v>0.02</v>
       </c>
     </row>
     <row r="36" spans="2:4" x14ac:dyDescent="0.45">
@@ -3821,11 +3822,11 @@
       </c>
       <c r="C38" s="44">
         <f ca="1">C29-SUM(C31:C37)</f>
-        <v>11070.000000000002</v>
+        <v>11820.000000000002</v>
       </c>
       <c r="D38" s="50">
         <f ca="1">C38/C29</f>
-        <v>0.73799999999999999</v>
+        <v>0.78800000000000003</v>
       </c>
     </row>
     <row r="39" spans="2:4" x14ac:dyDescent="0.45">
@@ -3904,7 +3905,7 @@
       </c>
       <c r="E50" s="20">
         <f>E16</f>
-        <v>3862567.5322623369</v>
+        <v>3660000</v>
       </c>
     </row>
     <row r="51" spans="2:5" x14ac:dyDescent="0.45">
@@ -3921,7 +3922,7 @@
       </c>
       <c r="E51" s="23">
         <f>E23</f>
-        <v>4272496.989391651</v>
+        <v>4056560</v>
       </c>
     </row>
     <row r="52" spans="2:5" x14ac:dyDescent="0.45">
@@ -3930,7 +3931,7 @@
       </c>
       <c r="C52" s="55">
         <f ca="1">C$38*12</f>
-        <v>132840.00000000003</v>
+        <v>141840.00000000003</v>
       </c>
       <c r="D52" s="55"/>
       <c r="E52" s="55"/>
@@ -3952,15 +3953,15 @@
       </c>
       <c r="C54" s="43">
         <f ca="1">RATE(15, $C52*(1+$C$39), -C51, $C53 / (1+$C$39)^15) + $C$39</f>
-        <v>2.8217902591055416E-2</v>
+        <v>3.0492697271019137E-2</v>
       </c>
       <c r="D54" s="43">
         <f t="shared" ref="D54:E54" ca="1" si="2">RATE(15, $C52*(1+$C$39), -D51, $C53 / (1+$C$39)^15) + $C$39</f>
-        <v>2.8219689572629422E-2</v>
+        <v>3.0494512194345638E-2</v>
       </c>
       <c r="E54" s="43">
         <f t="shared" ca="1" si="2"/>
-        <v>3.6556441291968569E-2</v>
+        <v>4.3481297128932075E-2</v>
       </c>
     </row>
     <row r="56" spans="2:5" x14ac:dyDescent="0.45">

--- a/financial_models/Res_Property_Monitor.xlsx
+++ b/financial_models/Res_Property_Monitor.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{531730FD-ED7A-4E96-8E30-B326D23403BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56B994E4-E2C7-48D0-871C-A09D17F2B965}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="6150" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Assumptions" sheetId="13" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="164">
   <si>
     <t>Value</t>
   </si>
@@ -763,6 +763,147 @@
   <si>
     <t>潘石屹 suggested to use at least the Mortgage rate.</t>
   </si>
+  <si>
+    <t>第一步：收集物業基本資料</t>
+  </si>
+  <si>
+    <t>類型</t>
+  </si>
+  <si>
+    <t>地址</t>
+  </si>
+  <si>
+    <t>竣工(OP/CC)年份</t>
+  </si>
+  <si>
+    <t>樓齡</t>
+  </si>
+  <si>
+    <t>可售面積 (Sqft)</t>
+  </si>
+  <si>
+    <t>管理費 ($/Sqft)</t>
+  </si>
+  <si>
+    <t>持有期</t>
+  </si>
+  <si>
+    <t>第二步：用市場比較法估算市值</t>
+  </si>
+  <si>
+    <t>可比單價/尺</t>
+  </si>
+  <si>
+    <t>情景</t>
+  </si>
+  <si>
+    <t>物業價格 (HKD)</t>
+  </si>
+  <si>
+    <t>代理佣金率</t>
+  </si>
+  <si>
+    <t>印花稅率</t>
+  </si>
+  <si>
+    <t>轉讓費率</t>
+  </si>
+  <si>
+    <t>法律費用</t>
+  </si>
+  <si>
+    <t>驗樓費</t>
+  </si>
+  <si>
+    <t>其他成本</t>
+  </si>
+  <si>
+    <t>總購置成本</t>
+  </si>
+  <si>
+    <t>第三步：計算淨租金收入（NOI）</t>
+  </si>
+  <si>
+    <t>參考市場毛租金收益率</t>
+  </si>
+  <si>
+    <t>參考市值</t>
+  </si>
+  <si>
+    <t>推算月租金</t>
+  </si>
+  <si>
+    <t>每月管理費</t>
+  </si>
+  <si>
+    <t>政府差餉</t>
+  </si>
+  <si>
+    <t>地租</t>
+  </si>
+  <si>
+    <t>維修/保養/儲備基金</t>
+  </si>
+  <si>
+    <t>舊樓溢價成本</t>
+  </si>
+  <si>
+    <t>空置準備</t>
+  </si>
+  <si>
+    <t>其他月度費用</t>
+  </si>
+  <si>
+    <t>預計年租金增長率</t>
+  </si>
+  <si>
+    <t>第四步：估算退出價值</t>
+  </si>
+  <si>
+    <t>預計升值幅度</t>
+  </si>
+  <si>
+    <t>預計年均複合增長率</t>
+  </si>
+  <si>
+    <t>升值後出售價格</t>
+  </si>
+  <si>
+    <t>第五步：計算IRR</t>
+  </si>
+  <si>
+    <t>物業價格</t>
+  </si>
+  <si>
+    <t>退出價值</t>
+  </si>
+  <si>
+    <t>持有期IRR</t>
+  </si>
+  <si>
+    <t>決策規則:</t>
+  </si>
+  <si>
+    <t>1. IRR &gt; 貸款利率 → 有吸引力</t>
+  </si>
+  <si>
+    <t>2. IRR = 貸款利率 → 盈虧平衡</t>
+  </si>
+  <si>
+    <t>3. IRR &lt; 貸款利率 → 無吸引力</t>
+  </si>
+  <si>
+    <t>備註</t>
+  </si>
+  <si>
+    <t>每月淨租金 (HKD)</t>
+  </si>
+  <si>
+    <t>年度淨租金</t>
+  </si>
+  <si>
+    <t>Decision rule:</t>
+  </si>
 </sst>
 </file>
 
@@ -773,7 +914,7 @@
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="166" formatCode="#,##0&quot;yrs&quot;"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -845,6 +986,50 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -900,7 +1085,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="108">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1058,6 +1243,136 @@
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2287,7 +2602,7 @@
     </row>
     <row r="56" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B56" s="36" t="s">
-        <v>67</v>
+        <v>163</v>
       </c>
       <c r="G56" s="4"/>
     </row>
@@ -2330,605 +2645,606 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B2:G59"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="15" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" customWidth="1"/>
-    <col min="2" max="2" width="29.86328125" customWidth="1"/>
-    <col min="3" max="5" width="16.59765625" customWidth="1"/>
-    <col min="6" max="6" width="2.59765625" customWidth="1"/>
-    <col min="7" max="7" width="90.59765625" customWidth="1"/>
-    <col min="8" max="9" width="16.59765625" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" style="61" customWidth="1"/>
+    <col min="2" max="2" width="29.86328125" style="61" customWidth="1"/>
+    <col min="3" max="5" width="16.59765625" style="61" customWidth="1"/>
+    <col min="6" max="6" width="2.59765625" style="61" customWidth="1"/>
+    <col min="7" max="7" width="90.59765625" style="61" customWidth="1"/>
+    <col min="8" max="9" width="16.59765625" style="61" customWidth="1"/>
+    <col min="10" max="16384" width="8.796875" style="61"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B2" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="G2" s="13" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="G3" s="4"/>
-    </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B4" s="30" t="s">
-        <v>37</v>
-      </c>
-      <c r="C4" s="15" t="s">
+    <row r="2" spans="2:7" ht="15.75" x14ac:dyDescent="0.55000000000000004">
+      <c r="B2" s="60" t="s">
+        <v>117</v>
+      </c>
+      <c r="G2" s="62" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="G3" s="63"/>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="B4" s="64" t="s">
+        <v>119</v>
+      </c>
+      <c r="C4" s="65" t="s">
         <v>108</v>
       </c>
-      <c r="G4" s="4"/>
-    </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B5" s="30" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="15" t="s">
+      <c r="G4" s="63"/>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="B5" s="64" t="s">
+        <v>118</v>
+      </c>
+      <c r="C5" s="65" t="s">
         <v>109</v>
       </c>
-      <c r="G5" s="4"/>
-    </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B6" s="30" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" s="16">
+      <c r="G5" s="63"/>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="B6" s="64" t="s">
+        <v>120</v>
+      </c>
+      <c r="C6" s="66">
         <v>1995</v>
       </c>
-      <c r="G6" s="4"/>
-    </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B7" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" s="17">
+      <c r="G6" s="63"/>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="B7" s="64" t="s">
+        <v>121</v>
+      </c>
+      <c r="C7" s="67">
         <f ca="1">YEAR(TODAY())-C6</f>
         <v>31</v>
       </c>
-      <c r="G7" s="4"/>
-    </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B8" s="30" t="s">
-        <v>72</v>
-      </c>
-      <c r="C8" s="18">
+      <c r="G7" s="63"/>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="B8" s="64" t="s">
+        <v>122</v>
+      </c>
+      <c r="C8" s="68">
         <v>2000</v>
       </c>
-      <c r="G8" s="4"/>
-    </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B9" s="30" t="s">
-        <v>73</v>
-      </c>
-      <c r="C9" s="19">
+      <c r="G8" s="63"/>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="B9" s="64" t="s">
+        <v>123</v>
+      </c>
+      <c r="C9" s="69">
         <v>0</v>
       </c>
-      <c r="G9" s="4"/>
-    </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B10" s="30" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" s="46">
+      <c r="G9" s="63"/>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="B10" s="64" t="s">
+        <v>124</v>
+      </c>
+      <c r="C10" s="70">
         <f>Holding_Period</f>
         <v>15</v>
       </c>
-      <c r="G10" s="4"/>
-    </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="G11" s="4"/>
-    </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B12" s="27" t="s">
-        <v>79</v>
-      </c>
-      <c r="G12" s="13" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="G13" s="4"/>
-    </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B14" s="30" t="s">
-        <v>35</v>
-      </c>
-      <c r="C14" s="6" t="s">
+      <c r="G10" s="63"/>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="G11" s="63"/>
+    </row>
+    <row r="12" spans="2:7" ht="15.75" x14ac:dyDescent="0.55000000000000004">
+      <c r="B12" s="71" t="s">
+        <v>125</v>
+      </c>
+      <c r="G12" s="62" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="G13" s="63"/>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="B14" s="64" t="s">
+        <v>127</v>
+      </c>
+      <c r="C14" s="72" t="s">
         <v>43</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="72" t="s">
         <v>36</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="E14" s="72" t="s">
         <v>96</v>
       </c>
-      <c r="G14" s="4"/>
-    </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B15" s="31" t="s">
-        <v>74</v>
-      </c>
-      <c r="C15" s="25">
+      <c r="G14" s="63"/>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="B15" s="73" t="s">
+        <v>126</v>
+      </c>
+      <c r="C15" s="74">
         <f>C16/C8</f>
         <v>11000</v>
       </c>
-      <c r="D15" s="26">
+      <c r="D15" s="75">
         <v>10000</v>
       </c>
-      <c r="E15" s="25">
+      <c r="E15" s="74">
         <f>E16/C8</f>
         <v>9750</v>
       </c>
-      <c r="G15" s="4"/>
-    </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B16" s="30" t="s">
-        <v>47</v>
-      </c>
-      <c r="C16" s="14">
+      <c r="G15" s="63"/>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="B16" s="64" t="s">
+        <v>128</v>
+      </c>
+      <c r="C16" s="76">
         <v>22000000</v>
       </c>
-      <c r="D16" s="20">
+      <c r="D16" s="77">
         <f>D15*C$8</f>
         <v>20000000</v>
       </c>
-      <c r="E16" s="40">
+      <c r="E16" s="78">
         <v>19500000</v>
       </c>
-      <c r="G16" s="4"/>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B17" s="30" t="s">
-        <v>59</v>
-      </c>
-      <c r="C17" s="57">
+      <c r="G16" s="63"/>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="B17" s="64" t="s">
+        <v>129</v>
+      </c>
+      <c r="C17" s="79">
         <f>Assumptions!C9</f>
         <v>0.01</v>
       </c>
-      <c r="D17" s="57"/>
-      <c r="E17" s="57"/>
-      <c r="G17" s="4"/>
-    </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B18" s="30" t="s">
-        <v>56</v>
-      </c>
-      <c r="C18" s="53">
+      <c r="D17" s="79"/>
+      <c r="E17" s="79"/>
+      <c r="G17" s="63"/>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="B18" s="64" t="s">
+        <v>130</v>
+      </c>
+      <c r="C18" s="80">
         <v>3.7499999999999999E-2</v>
       </c>
-      <c r="D18" s="53">
+      <c r="D18" s="80">
         <v>3.4500000000000003E-2</v>
       </c>
-      <c r="E18" s="53">
+      <c r="E18" s="80">
         <v>0.03</v>
       </c>
-      <c r="G18" s="4"/>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B19" s="30" t="s">
-        <v>58</v>
-      </c>
-      <c r="C19" s="58">
+      <c r="G18" s="63"/>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="B19" s="64" t="s">
+        <v>131</v>
+      </c>
+      <c r="C19" s="81">
         <f>Assumptions!C10</f>
         <v>1E-3</v>
       </c>
-      <c r="D19" s="58"/>
-      <c r="E19" s="58"/>
-      <c r="G19" s="4"/>
-    </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B20" s="30" t="s">
-        <v>104</v>
-      </c>
-      <c r="C20" s="59">
+      <c r="D19" s="81"/>
+      <c r="E19" s="81"/>
+      <c r="G19" s="63"/>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="B20" s="64" t="s">
+        <v>132</v>
+      </c>
+      <c r="C20" s="82">
         <f>Assumptions!C11</f>
         <v>20000</v>
       </c>
-      <c r="D20" s="59"/>
-      <c r="E20" s="59"/>
-      <c r="G20" s="4"/>
-    </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B21" s="30" t="s">
-        <v>105</v>
-      </c>
-      <c r="C21" s="59">
+      <c r="D20" s="82"/>
+      <c r="E20" s="82"/>
+      <c r="G20" s="63"/>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="B21" s="64" t="s">
+        <v>133</v>
+      </c>
+      <c r="C21" s="82">
         <v>10000</v>
       </c>
-      <c r="D21" s="59"/>
-      <c r="E21" s="59"/>
-      <c r="G21" s="4" t="s">
+      <c r="D21" s="82"/>
+      <c r="E21" s="82"/>
+      <c r="G21" s="63" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="22" spans="2:7" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B22" s="32" t="s">
-        <v>101</v>
-      </c>
-      <c r="C22" s="49">
+    <row r="22" spans="2:7" ht="15.4" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B22" s="83" t="s">
+        <v>134</v>
+      </c>
+      <c r="C22" s="84">
         <v>150000</v>
       </c>
-      <c r="D22" s="49">
+      <c r="D22" s="84">
         <v>150000</v>
       </c>
-      <c r="E22" s="49">
+      <c r="E22" s="84">
         <v>150000</v>
       </c>
-      <c r="G22" s="4" t="s">
+      <c r="G22" s="63" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="23" spans="2:7" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="B23" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="C23" s="22">
+    <row r="23" spans="2:7" ht="16.149999999999999" thickTop="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B23" s="85" t="s">
+        <v>135</v>
+      </c>
+      <c r="C23" s="86">
         <f>C16+C16*($C$17+C18+$C$19)+$C$20+$C$21+C22</f>
         <v>23247000</v>
       </c>
-      <c r="D23" s="22">
+      <c r="D23" s="86">
         <f t="shared" ref="D23:E23" si="0">D16+D16*($C$17+D18+$C$19)+$C$20+$C$21+D22</f>
         <v>21090000</v>
       </c>
-      <c r="E23" s="22">
+      <c r="E23" s="86">
         <f t="shared" si="0"/>
         <v>20479500</v>
       </c>
-      <c r="G23" s="4"/>
-    </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="G24" s="4"/>
-    </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B25" s="27" t="s">
-        <v>78</v>
-      </c>
-      <c r="G25" s="13" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="C26" s="5"/>
-      <c r="G26" s="4"/>
-    </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B27" s="30" t="s">
-        <v>61</v>
-      </c>
-      <c r="C27" s="47">
+      <c r="G23" s="63"/>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="G24" s="63"/>
+    </row>
+    <row r="25" spans="2:7" ht="15.75" x14ac:dyDescent="0.55000000000000004">
+      <c r="B25" s="71" t="s">
+        <v>136</v>
+      </c>
+      <c r="G25" s="62" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="C26" s="87"/>
+      <c r="G26" s="63"/>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="B27" s="64" t="s">
+        <v>137</v>
+      </c>
+      <c r="C27" s="88">
         <v>3.3000000000000015E-2</v>
       </c>
-      <c r="G27" s="4"/>
-    </row>
-    <row r="28" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B28" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="C28" s="29">
+      <c r="G27" s="63"/>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="B28" s="73" t="s">
+        <v>138</v>
+      </c>
+      <c r="C28" s="89">
         <f>D16</f>
         <v>20000000</v>
       </c>
-      <c r="G28" s="4"/>
-    </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B29" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="C29" s="44">
+      <c r="G28" s="63"/>
+    </row>
+    <row r="29" spans="2:7" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="B29" s="85" t="s">
+        <v>139</v>
+      </c>
+      <c r="C29" s="90">
         <f>C28*C$27/12</f>
         <v>55000.000000000029</v>
       </c>
-      <c r="G29" s="4"/>
-    </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B30" s="7"/>
-      <c r="C30" s="24"/>
-      <c r="G30" s="4"/>
-    </row>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B31" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="C31" s="24">
+      <c r="G29" s="63"/>
+    </row>
+    <row r="30" spans="2:7" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="B30" s="91"/>
+      <c r="C30" s="92"/>
+      <c r="G30" s="63"/>
+    </row>
+    <row r="31" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="B31" s="64" t="s">
+        <v>140</v>
+      </c>
+      <c r="C31" s="92">
         <f>C$9*C$8</f>
         <v>0</v>
       </c>
-      <c r="D31" s="50">
+      <c r="D31" s="93">
         <f>C31/C29</f>
         <v>0</v>
       </c>
-      <c r="G31" s="4"/>
-    </row>
-    <row r="32" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B32" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="C32" s="24">
+      <c r="G31" s="63"/>
+    </row>
+    <row r="32" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="B32" s="64" t="s">
+        <v>141</v>
+      </c>
+      <c r="C32" s="92">
         <f>$C$29*D32</f>
         <v>2750.0000000000018</v>
       </c>
-      <c r="D32" s="54">
+      <c r="D32" s="94">
         <f>Assumptions!C15</f>
         <v>0.05</v>
       </c>
-      <c r="G32" s="4"/>
-    </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B33" s="30" t="s">
-        <v>26</v>
-      </c>
-      <c r="C33" s="24">
+      <c r="G32" s="63"/>
+    </row>
+    <row r="33" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="B33" s="64" t="s">
+        <v>142</v>
+      </c>
+      <c r="C33" s="92">
         <f t="shared" ref="C33:C36" si="1">$C$29*D33</f>
         <v>1650.0000000000009</v>
       </c>
-      <c r="D33" s="50">
+      <c r="D33" s="93">
         <f>Assumptions!C16</f>
         <v>0.03</v>
       </c>
-      <c r="G33" s="4"/>
-    </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B34" s="30" t="s">
-        <v>102</v>
-      </c>
-      <c r="C34" s="24">
+      <c r="G33" s="63"/>
+    </row>
+    <row r="34" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="B34" s="64" t="s">
+        <v>143</v>
+      </c>
+      <c r="C34" s="92">
         <f t="shared" si="1"/>
         <v>1100.0000000000007</v>
       </c>
-      <c r="D34" s="3">
+      <c r="D34" s="95">
         <v>0.02</v>
       </c>
-      <c r="G34" s="4" t="s">
+      <c r="G34" s="63" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="35" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B35" s="30" t="s">
-        <v>103</v>
-      </c>
-      <c r="C35" s="24">
+    <row r="35" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="B35" s="64" t="s">
+        <v>144</v>
+      </c>
+      <c r="C35" s="92">
         <f t="shared" si="1"/>
         <v>550.00000000000034</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D35" s="95">
         <v>0.01</v>
       </c>
-      <c r="G35" s="4"/>
-    </row>
-    <row r="36" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B36" s="30" t="s">
-        <v>16</v>
-      </c>
-      <c r="C36" s="24">
+      <c r="G35" s="63"/>
+    </row>
+    <row r="36" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="B36" s="64" t="s">
+        <v>145</v>
+      </c>
+      <c r="C36" s="92">
         <f t="shared" si="1"/>
         <v>5500.0000000000036</v>
       </c>
-      <c r="D36" s="3">
+      <c r="D36" s="95">
         <v>0.1</v>
       </c>
-      <c r="G36" s="4" t="s">
+      <c r="G36" s="63" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="37" spans="2:7" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B37" s="32" t="s">
-        <v>41</v>
-      </c>
-      <c r="C37" s="51">
+    <row r="37" spans="2:7" ht="15.4" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B37" s="83" t="s">
+        <v>146</v>
+      </c>
+      <c r="C37" s="96">
         <v>0</v>
       </c>
-      <c r="D37" s="52">
+      <c r="D37" s="97">
         <f>C37/C29</f>
         <v>0</v>
       </c>
-      <c r="G37" s="4"/>
-    </row>
-    <row r="38" spans="2:7" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="B38" s="21" t="s">
-        <v>63</v>
-      </c>
-      <c r="C38" s="44">
+      <c r="G37" s="63"/>
+    </row>
+    <row r="38" spans="2:7" ht="16.149999999999999" thickTop="1" x14ac:dyDescent="0.5">
+      <c r="B38" s="85" t="s">
+        <v>161</v>
+      </c>
+      <c r="C38" s="90">
         <f>C29-SUM(C31:C37)</f>
         <v>43450.000000000022</v>
       </c>
-      <c r="D38" s="50">
+      <c r="D38" s="93">
         <f>C38/C29</f>
         <v>0.78999999999999992</v>
       </c>
-      <c r="G38" s="4"/>
-    </row>
-    <row r="39" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B39" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="C39" s="45">
+      <c r="G38" s="63"/>
+    </row>
+    <row r="39" spans="2:7" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="B39" s="85" t="s">
+        <v>147</v>
+      </c>
+      <c r="C39" s="98">
         <f>Assumptions!C19</f>
         <v>0.02</v>
       </c>
-      <c r="G39" s="4"/>
-    </row>
-    <row r="40" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="G40" s="4"/>
-    </row>
-    <row r="41" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B41" s="27" t="s">
-        <v>83</v>
-      </c>
-      <c r="G41" s="13" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="G42" s="4"/>
-    </row>
-    <row r="43" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B43" s="30" t="s">
-        <v>38</v>
-      </c>
-      <c r="C43" s="48">
+      <c r="G39" s="63"/>
+    </row>
+    <row r="40" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="G40" s="63"/>
+    </row>
+    <row r="41" spans="2:7" ht="15.75" x14ac:dyDescent="0.55000000000000004">
+      <c r="B41" s="71" t="s">
+        <v>148</v>
+      </c>
+      <c r="G41" s="62" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="42" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="G42" s="63"/>
+    </row>
+    <row r="43" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="B43" s="64" t="s">
+        <v>149</v>
+      </c>
+      <c r="C43" s="99">
         <v>0.3</v>
       </c>
-      <c r="G43" s="4" t="s">
+      <c r="G43" s="63" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="44" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B44" s="31" t="s">
-        <v>42</v>
-      </c>
-      <c r="C44" s="41">
+    <row r="44" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="B44" s="73" t="s">
+        <v>150</v>
+      </c>
+      <c r="C44" s="100">
         <f>(1+C43)^(1/C10)-1</f>
         <v>1.7644813405053306E-2</v>
       </c>
-      <c r="G44" s="4"/>
-    </row>
-    <row r="45" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B45" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="C45" s="42">
+      <c r="G44" s="63"/>
+    </row>
+    <row r="45" spans="2:7" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="B45" s="85" t="s">
+        <v>151</v>
+      </c>
+      <c r="C45" s="101">
         <f>D16*(1+C$43)</f>
         <v>26000000</v>
       </c>
-      <c r="G45" s="4"/>
-    </row>
-    <row r="46" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="G46" s="4"/>
-    </row>
-    <row r="47" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B47" s="27" t="s">
-        <v>84</v>
-      </c>
-      <c r="G47" s="13" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="G48" s="4"/>
-    </row>
-    <row r="49" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B49" s="30" t="s">
-        <v>35</v>
-      </c>
-      <c r="C49" s="35" t="str">
+      <c r="G45" s="63"/>
+    </row>
+    <row r="46" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="G46" s="63"/>
+    </row>
+    <row r="47" spans="2:7" ht="15.75" x14ac:dyDescent="0.55000000000000004">
+      <c r="B47" s="71" t="s">
+        <v>152</v>
+      </c>
+      <c r="G47" s="62" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="48" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="G48" s="63"/>
+    </row>
+    <row r="49" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="B49" s="64" t="s">
+        <v>127</v>
+      </c>
+      <c r="C49" s="102" t="str">
         <f>C14</f>
         <v>Asking Price</v>
       </c>
-      <c r="D49" s="35" t="str">
+      <c r="D49" s="102" t="str">
         <f>D14</f>
         <v>Comparable</v>
       </c>
-      <c r="E49" s="35" t="str">
+      <c r="E49" s="102" t="str">
         <f>E14</f>
         <v>IRR Netural Price</v>
       </c>
-      <c r="G49" s="4"/>
-    </row>
-    <row r="50" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B50" s="30" t="s">
-        <v>65</v>
-      </c>
-      <c r="C50" s="20">
+      <c r="G49" s="63"/>
+    </row>
+    <row r="50" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="B50" s="64" t="s">
+        <v>153</v>
+      </c>
+      <c r="C50" s="77">
         <f>C16</f>
         <v>22000000</v>
       </c>
-      <c r="D50" s="20">
+      <c r="D50" s="77">
         <f t="shared" ref="D50:E50" si="2">D16</f>
         <v>20000000</v>
       </c>
-      <c r="E50" s="20">
+      <c r="E50" s="77">
         <f t="shared" si="2"/>
         <v>19500000</v>
       </c>
-      <c r="G50" s="4"/>
-    </row>
-    <row r="51" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B51" s="30" t="s">
-        <v>60</v>
-      </c>
-      <c r="C51" s="23">
+      <c r="G50" s="63"/>
+    </row>
+    <row r="51" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="B51" s="64" t="s">
+        <v>135</v>
+      </c>
+      <c r="C51" s="103">
         <f>C23</f>
         <v>23247000</v>
       </c>
-      <c r="D51" s="23">
+      <c r="D51" s="103">
         <f>D23</f>
         <v>21090000</v>
       </c>
-      <c r="E51" s="23">
+      <c r="E51" s="103">
         <f>E23</f>
         <v>20479500</v>
       </c>
-      <c r="G51" s="4"/>
-    </row>
-    <row r="52" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B52" s="30" t="s">
-        <v>44</v>
-      </c>
-      <c r="C52" s="55">
+      <c r="G51" s="63"/>
+    </row>
+    <row r="52" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="B52" s="64" t="s">
+        <v>162</v>
+      </c>
+      <c r="C52" s="104">
         <f>C$38*12</f>
         <v>521400.00000000023</v>
       </c>
-      <c r="D52" s="55"/>
-      <c r="E52" s="55"/>
-      <c r="G52" s="4"/>
-    </row>
-    <row r="53" spans="2:7" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B53" s="32" t="s">
-        <v>45</v>
-      </c>
-      <c r="C53" s="56">
+      <c r="D52" s="104"/>
+      <c r="E52" s="104"/>
+      <c r="G52" s="63"/>
+    </row>
+    <row r="53" spans="2:7" ht="15.4" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B53" s="83" t="s">
+        <v>154</v>
+      </c>
+      <c r="C53" s="105">
         <f>C$45</f>
         <v>26000000</v>
       </c>
-      <c r="D53" s="56"/>
-      <c r="E53" s="56"/>
-      <c r="G53" s="4"/>
-    </row>
-    <row r="54" spans="2:7" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="B54" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="C54" s="43">
+      <c r="D53" s="105"/>
+      <c r="E53" s="105"/>
+      <c r="G53" s="63"/>
+    </row>
+    <row r="54" spans="2:7" ht="16.149999999999999" thickTop="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B54" s="85" t="s">
+        <v>155</v>
+      </c>
+      <c r="C54" s="106">
         <f>RATE(15, $C52*(1+$C$39), -C51, $C53 / (1+$C$39)^15) + $C$39</f>
         <v>3.2569232155100998E-2</v>
       </c>
-      <c r="D54" s="43">
+      <c r="D54" s="106">
         <f t="shared" ref="D54:E54" si="3">RATE(15, $C52*(1+$C$39), -D51, $C53 / (1+$C$39)^15) + $C$39</f>
         <v>4.0372636869005607E-2</v>
       </c>
-      <c r="E54" s="43">
+      <c r="E54" s="106">
         <f t="shared" si="3"/>
         <v>4.2755034579381089E-2</v>
       </c>
-      <c r="G54" s="4"/>
-    </row>
-    <row r="55" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="G55" s="4"/>
-    </row>
-    <row r="56" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B56" s="36" t="s">
-        <v>67</v>
-      </c>
-      <c r="G56" s="4"/>
-    </row>
-    <row r="57" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B57" t="s">
-        <v>68</v>
-      </c>
-      <c r="G57" s="4"/>
-    </row>
-    <row r="58" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B58" t="s">
-        <v>69</v>
-      </c>
-      <c r="G58" s="4"/>
-    </row>
-    <row r="59" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B59" t="s">
-        <v>70</v>
-      </c>
-      <c r="G59" s="4"/>
+      <c r="G54" s="63"/>
+    </row>
+    <row r="55" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="G55" s="63"/>
+    </row>
+    <row r="56" spans="2:7" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="B56" s="107" t="s">
+        <v>156</v>
+      </c>
+      <c r="G56" s="63"/>
+    </row>
+    <row r="57" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="B57" s="61" t="s">
+        <v>157</v>
+      </c>
+      <c r="G57" s="63"/>
+    </row>
+    <row r="58" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="B58" s="61" t="s">
+        <v>158</v>
+      </c>
+      <c r="G58" s="63"/>
+    </row>
+    <row r="59" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="B59" s="61" t="s">
+        <v>159</v>
+      </c>
+      <c r="G59" s="63"/>
     </row>
   </sheetData>
   <dataConsolidate/>

--- a/financial_models/Res_Property_Monitor.xlsx
+++ b/financial_models/Res_Property_Monitor.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56B994E4-E2C7-48D0-871C-A09D17F2B965}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85E43CB5-3DFF-4999-99D5-198D56981D66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Assumptions" sheetId="13" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="166">
   <si>
     <t>Value</t>
   </si>
@@ -236,9 +236,6 @@
   </si>
   <si>
     <t>Holding Period IRR</t>
-  </si>
-  <si>
-    <t>Decision rule (standard real-estate practice):</t>
   </si>
   <si>
     <t>1. IRR &gt; Hurdle rate → Attractive</t>
@@ -740,9 +737,6 @@
     <t>早禾坑</t>
   </si>
   <si>
-    <t>House</t>
-  </si>
-  <si>
     <t>香港40年樓齡的舊樓進行強制驗樓及大維修，一般每戶費用約在 HK$30,000 至 HK$150,000 或更高。</t>
   </si>
   <si>
@@ -903,6 +897,18 @@
   </si>
   <si>
     <t>Decision rule:</t>
+  </si>
+  <si>
+    <t>要價</t>
+  </si>
+  <si>
+    <t>可比售價</t>
+  </si>
+  <si>
+    <t>IRR中性售價</t>
+  </si>
+  <si>
+    <t>Village House</t>
   </si>
 </sst>
 </file>
@@ -1229,21 +1235,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1296,15 +1287,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1362,17 +1344,41 @@
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="10" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1738,7 +1744,7 @@
         <v>4.2499999999999996E-2</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.45">
@@ -1755,7 +1761,7 @@
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B8" s="13" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C8" s="12" t="s">
         <v>0</v>
@@ -1811,7 +1817,7 @@
     </row>
     <row r="14" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B14" s="13" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C14" s="12" t="s">
         <v>0</v>
@@ -1828,7 +1834,7 @@
         <v>0.05</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="16" spans="2:4" x14ac:dyDescent="0.45">
@@ -1842,7 +1848,7 @@
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B17" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C17" s="10">
         <v>0.05</v>
@@ -1864,7 +1870,7 @@
         <v>0.02</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.45">
@@ -2038,7 +2044,7 @@
   <sheetData>
     <row r="2" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B2" s="28" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G2" s="13" t="s">
         <v>1</v>
@@ -2052,7 +2058,7 @@
         <v>37</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G4" s="4"/>
     </row>
@@ -2086,7 +2092,7 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B8" s="30" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C8" s="18">
         <v>690</v>
@@ -2095,7 +2101,7 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B9" s="30" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C9" s="19">
         <v>2.5</v>
@@ -2117,7 +2123,7 @@
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B12" s="27" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G12" s="13" t="s">
         <v>1</v>
@@ -2137,13 +2143,13 @@
         <v>36</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G14" s="4"/>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B15" s="31" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C15" s="25">
         <f>C16/C8</f>
@@ -2178,12 +2184,12 @@
       <c r="B17" s="30" t="s">
         <v>59</v>
       </c>
-      <c r="C17" s="57">
+      <c r="C17" s="100">
         <f>Assumptions!C9</f>
         <v>0.01</v>
       </c>
-      <c r="D17" s="57"/>
-      <c r="E17" s="57"/>
+      <c r="D17" s="100"/>
+      <c r="E17" s="100"/>
       <c r="G17" s="4"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.45">
@@ -2205,41 +2211,41 @@
       <c r="B19" s="30" t="s">
         <v>58</v>
       </c>
-      <c r="C19" s="58">
+      <c r="C19" s="101">
         <f>Assumptions!C10</f>
         <v>1E-3</v>
       </c>
-      <c r="D19" s="58"/>
-      <c r="E19" s="58"/>
+      <c r="D19" s="101"/>
+      <c r="E19" s="101"/>
       <c r="G19" s="4"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B20" s="30" t="s">
-        <v>104</v>
-      </c>
-      <c r="C20" s="59">
+        <v>103</v>
+      </c>
+      <c r="C20" s="102">
         <f>Assumptions!C11</f>
         <v>20000</v>
       </c>
-      <c r="D20" s="59"/>
-      <c r="E20" s="59"/>
+      <c r="D20" s="102"/>
+      <c r="E20" s="102"/>
       <c r="G20" s="4"/>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B21" s="30" t="s">
-        <v>105</v>
-      </c>
-      <c r="C21" s="59">
+        <v>104</v>
+      </c>
+      <c r="C21" s="102">
         <f>Assumptions!C12</f>
         <v>5000</v>
       </c>
-      <c r="D21" s="59"/>
-      <c r="E21" s="59"/>
+      <c r="D21" s="102"/>
+      <c r="E21" s="102"/>
       <c r="G21" s="4"/>
     </row>
     <row r="22" spans="2:7" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B22" s="32" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C22" s="49">
         <v>150000</v>
@@ -2251,7 +2257,7 @@
         <v>150000</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="23" spans="2:7" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
@@ -2277,7 +2283,7 @@
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B25" s="27" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G25" s="13" t="s">
         <v>1</v>
@@ -2365,7 +2371,7 @@
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B34" s="30" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C34" s="24">
         <f t="shared" si="1"/>
@@ -2379,7 +2385,7 @@
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B35" s="30" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C35" s="24">
         <f t="shared" ca="1" si="1"/>
@@ -2447,7 +2453,7 @@
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B41" s="27" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G41" s="13" t="s">
         <v>1</v>
@@ -2464,7 +2470,7 @@
         <v>0.4</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.45">
@@ -2492,7 +2498,7 @@
     </row>
     <row r="47" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B47" s="27" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G47" s="13" t="s">
         <v>1</v>
@@ -2559,24 +2565,24 @@
       <c r="B52" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="C52" s="55">
+      <c r="C52" s="98">
         <f ca="1">C$38*12</f>
         <v>209208</v>
       </c>
-      <c r="D52" s="55"/>
-      <c r="E52" s="55"/>
+      <c r="D52" s="98"/>
+      <c r="E52" s="98"/>
       <c r="G52" s="4"/>
     </row>
     <row r="53" spans="2:7" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B53" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="C53" s="56">
+      <c r="C53" s="99">
         <f>C$45</f>
         <v>13524000</v>
       </c>
-      <c r="D53" s="56"/>
-      <c r="E53" s="56"/>
+      <c r="D53" s="99"/>
+      <c r="E53" s="99"/>
       <c r="G53" s="4"/>
     </row>
     <row r="54" spans="2:7" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
@@ -2602,25 +2608,25 @@
     </row>
     <row r="56" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B56" s="36" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="G56" s="4"/>
     </row>
     <row r="57" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B57" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G57" s="4"/>
     </row>
     <row r="58" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B58" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G58" s="4"/>
     </row>
     <row r="59" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B59" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G59" s="4"/>
     </row>
@@ -2647,604 +2653,604 @@
   <dimension ref="B2:G59"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="15" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="61" customWidth="1"/>
-    <col min="2" max="2" width="29.86328125" style="61" customWidth="1"/>
-    <col min="3" max="5" width="16.59765625" style="61" customWidth="1"/>
-    <col min="6" max="6" width="2.59765625" style="61" customWidth="1"/>
-    <col min="7" max="7" width="90.59765625" style="61" customWidth="1"/>
-    <col min="8" max="9" width="16.59765625" style="61" customWidth="1"/>
-    <col min="10" max="16384" width="8.796875" style="61"/>
+    <col min="1" max="1" width="2.6640625" style="56" customWidth="1"/>
+    <col min="2" max="2" width="29.86328125" style="56" customWidth="1"/>
+    <col min="3" max="5" width="16.59765625" style="56" customWidth="1"/>
+    <col min="6" max="6" width="2.59765625" style="56" customWidth="1"/>
+    <col min="7" max="7" width="90.59765625" style="56" customWidth="1"/>
+    <col min="8" max="9" width="16.59765625" style="56" customWidth="1"/>
+    <col min="10" max="16384" width="8.796875" style="56"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="15.75" x14ac:dyDescent="0.55000000000000004">
-      <c r="B2" s="60" t="s">
+      <c r="B2" s="55" t="s">
+        <v>115</v>
+      </c>
+      <c r="G2" s="57" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="G3" s="58"/>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="B4" s="59" t="s">
         <v>117</v>
       </c>
-      <c r="G2" s="62" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.5">
-      <c r="G3" s="63"/>
-    </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.5">
-      <c r="B4" s="64" t="s">
+      <c r="C4" s="60" t="s">
+        <v>107</v>
+      </c>
+      <c r="G4" s="58"/>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="B5" s="59" t="s">
+        <v>116</v>
+      </c>
+      <c r="C5" s="60" t="s">
+        <v>165</v>
+      </c>
+      <c r="G5" s="58"/>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="B6" s="59" t="s">
+        <v>118</v>
+      </c>
+      <c r="C6" s="61">
+        <v>1995</v>
+      </c>
+      <c r="G6" s="58"/>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="B7" s="59" t="s">
         <v>119</v>
       </c>
-      <c r="C4" s="65" t="s">
-        <v>108</v>
-      </c>
-      <c r="G4" s="63"/>
-    </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.5">
-      <c r="B5" s="64" t="s">
-        <v>118</v>
-      </c>
-      <c r="C5" s="65" t="s">
-        <v>109</v>
-      </c>
-      <c r="G5" s="63"/>
-    </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.5">
-      <c r="B6" s="64" t="s">
-        <v>120</v>
-      </c>
-      <c r="C6" s="66">
-        <v>1995</v>
-      </c>
-      <c r="G6" s="63"/>
-    </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.5">
-      <c r="B7" s="64" t="s">
-        <v>121</v>
-      </c>
-      <c r="C7" s="67">
+      <c r="C7" s="62">
         <f ca="1">YEAR(TODAY())-C6</f>
         <v>31</v>
       </c>
-      <c r="G7" s="63"/>
+      <c r="G7" s="58"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.5">
-      <c r="B8" s="64" t="s">
+      <c r="B8" s="59" t="s">
+        <v>120</v>
+      </c>
+      <c r="C8" s="63">
+        <v>2000</v>
+      </c>
+      <c r="G8" s="58"/>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="B9" s="59" t="s">
+        <v>121</v>
+      </c>
+      <c r="C9" s="64">
+        <v>0</v>
+      </c>
+      <c r="G9" s="58"/>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="B10" s="59" t="s">
         <v>122</v>
       </c>
-      <c r="C8" s="68">
-        <v>2000</v>
-      </c>
-      <c r="G8" s="63"/>
-    </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.5">
-      <c r="B9" s="64" t="s">
-        <v>123</v>
-      </c>
-      <c r="C9" s="69">
-        <v>0</v>
-      </c>
-      <c r="G9" s="63"/>
-    </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.5">
-      <c r="B10" s="64" t="s">
-        <v>124</v>
-      </c>
-      <c r="C10" s="70">
+      <c r="C10" s="65">
         <f>Holding_Period</f>
         <v>15</v>
       </c>
-      <c r="G10" s="63"/>
+      <c r="G10" s="58"/>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.5">
-      <c r="G11" s="63"/>
+      <c r="G11" s="58"/>
     </row>
     <row r="12" spans="2:7" ht="15.75" x14ac:dyDescent="0.55000000000000004">
-      <c r="B12" s="71" t="s">
+      <c r="B12" s="66" t="s">
+        <v>123</v>
+      </c>
+      <c r="G12" s="57" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="G13" s="58"/>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="B14" s="59" t="s">
         <v>125</v>
       </c>
-      <c r="G12" s="62" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.5">
-      <c r="G13" s="63"/>
-    </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.5">
-      <c r="B14" s="64" t="s">
-        <v>127</v>
-      </c>
-      <c r="C14" s="72" t="s">
-        <v>43</v>
-      </c>
-      <c r="D14" s="72" t="s">
-        <v>36</v>
-      </c>
-      <c r="E14" s="72" t="s">
-        <v>96</v>
-      </c>
-      <c r="G14" s="63"/>
+      <c r="C14" s="67" t="s">
+        <v>162</v>
+      </c>
+      <c r="D14" s="67" t="s">
+        <v>163</v>
+      </c>
+      <c r="E14" s="67" t="s">
+        <v>164</v>
+      </c>
+      <c r="G14" s="58"/>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.5">
-      <c r="B15" s="73" t="s">
-        <v>126</v>
-      </c>
-      <c r="C15" s="74">
+      <c r="B15" s="68" t="s">
+        <v>124</v>
+      </c>
+      <c r="C15" s="69">
         <f>C16/C8</f>
         <v>11000</v>
       </c>
-      <c r="D15" s="75">
+      <c r="D15" s="70">
         <v>10000</v>
       </c>
-      <c r="E15" s="74">
+      <c r="E15" s="69">
         <f>E16/C8</f>
         <v>9750</v>
       </c>
-      <c r="G15" s="63"/>
+      <c r="G15" s="58"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.5">
-      <c r="B16" s="64" t="s">
-        <v>128</v>
-      </c>
-      <c r="C16" s="76">
+      <c r="B16" s="59" t="s">
+        <v>126</v>
+      </c>
+      <c r="C16" s="71">
         <v>22000000</v>
       </c>
-      <c r="D16" s="77">
+      <c r="D16" s="72">
         <f>D15*C$8</f>
         <v>20000000</v>
       </c>
-      <c r="E16" s="78">
+      <c r="E16" s="73">
         <v>19500000</v>
       </c>
-      <c r="G16" s="63"/>
+      <c r="G16" s="58"/>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.5">
-      <c r="B17" s="64" t="s">
-        <v>129</v>
-      </c>
-      <c r="C17" s="79">
+      <c r="B17" s="59" t="s">
+        <v>127</v>
+      </c>
+      <c r="C17" s="104">
         <f>Assumptions!C9</f>
         <v>0.01</v>
       </c>
-      <c r="D17" s="79"/>
-      <c r="E17" s="79"/>
-      <c r="G17" s="63"/>
+      <c r="D17" s="104"/>
+      <c r="E17" s="104"/>
+      <c r="G17" s="58"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.5">
-      <c r="B18" s="64" t="s">
-        <v>130</v>
-      </c>
-      <c r="C18" s="80">
+      <c r="B18" s="59" t="s">
+        <v>128</v>
+      </c>
+      <c r="C18" s="74">
         <v>3.7499999999999999E-2</v>
       </c>
-      <c r="D18" s="80">
+      <c r="D18" s="74">
         <v>3.4500000000000003E-2</v>
       </c>
-      <c r="E18" s="80">
+      <c r="E18" s="74">
         <v>0.03</v>
       </c>
-      <c r="G18" s="63"/>
+      <c r="G18" s="58"/>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.5">
-      <c r="B19" s="64" t="s">
-        <v>131</v>
-      </c>
-      <c r="C19" s="81">
+      <c r="B19" s="59" t="s">
+        <v>129</v>
+      </c>
+      <c r="C19" s="105">
         <f>Assumptions!C10</f>
         <v>1E-3</v>
       </c>
-      <c r="D19" s="81"/>
-      <c r="E19" s="81"/>
-      <c r="G19" s="63"/>
+      <c r="D19" s="105"/>
+      <c r="E19" s="105"/>
+      <c r="G19" s="58"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.5">
-      <c r="B20" s="64" t="s">
-        <v>132</v>
-      </c>
-      <c r="C20" s="82">
+      <c r="B20" s="59" t="s">
+        <v>130</v>
+      </c>
+      <c r="C20" s="106">
         <f>Assumptions!C11</f>
         <v>20000</v>
       </c>
-      <c r="D20" s="82"/>
-      <c r="E20" s="82"/>
-      <c r="G20" s="63"/>
+      <c r="D20" s="106"/>
+      <c r="E20" s="106"/>
+      <c r="G20" s="58"/>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.5">
-      <c r="B21" s="64" t="s">
+      <c r="B21" s="59" t="s">
+        <v>131</v>
+      </c>
+      <c r="C21" s="106">
+        <v>10000</v>
+      </c>
+      <c r="D21" s="106"/>
+      <c r="E21" s="106"/>
+      <c r="G21" s="58" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" ht="15.4" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B22" s="75" t="s">
+        <v>132</v>
+      </c>
+      <c r="C22" s="76">
+        <v>150000</v>
+      </c>
+      <c r="D22" s="76">
+        <v>150000</v>
+      </c>
+      <c r="E22" s="76">
+        <v>150000</v>
+      </c>
+      <c r="G22" s="58" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" ht="16.149999999999999" thickTop="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B23" s="77" t="s">
         <v>133</v>
       </c>
-      <c r="C21" s="82">
-        <v>10000</v>
-      </c>
-      <c r="D21" s="82"/>
-      <c r="E21" s="82"/>
-      <c r="G21" s="63" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="22" spans="2:7" ht="15.4" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B22" s="83" t="s">
-        <v>134</v>
-      </c>
-      <c r="C22" s="84">
-        <v>150000</v>
-      </c>
-      <c r="D22" s="84">
-        <v>150000</v>
-      </c>
-      <c r="E22" s="84">
-        <v>150000</v>
-      </c>
-      <c r="G22" s="63" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="23" spans="2:7" ht="16.149999999999999" thickTop="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B23" s="85" t="s">
-        <v>135</v>
-      </c>
-      <c r="C23" s="86">
+      <c r="C23" s="78">
         <f>C16+C16*($C$17+C18+$C$19)+$C$20+$C$21+C22</f>
         <v>23247000</v>
       </c>
-      <c r="D23" s="86">
+      <c r="D23" s="78">
         <f t="shared" ref="D23:E23" si="0">D16+D16*($C$17+D18+$C$19)+$C$20+$C$21+D22</f>
         <v>21090000</v>
       </c>
-      <c r="E23" s="86">
+      <c r="E23" s="78">
         <f t="shared" si="0"/>
         <v>20479500</v>
       </c>
-      <c r="G23" s="63"/>
+      <c r="G23" s="58"/>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.5">
-      <c r="G24" s="63"/>
+      <c r="G24" s="58"/>
     </row>
     <row r="25" spans="2:7" ht="15.75" x14ac:dyDescent="0.55000000000000004">
-      <c r="B25" s="71" t="s">
+      <c r="B25" s="66" t="s">
+        <v>134</v>
+      </c>
+      <c r="G25" s="57" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="C26" s="79"/>
+      <c r="G26" s="58"/>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="B27" s="59" t="s">
+        <v>135</v>
+      </c>
+      <c r="C27" s="80">
+        <v>3.3000000000000015E-2</v>
+      </c>
+      <c r="G27" s="58"/>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="B28" s="68" t="s">
         <v>136</v>
       </c>
-      <c r="G25" s="62" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="26" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="C26" s="87"/>
-      <c r="G26" s="63"/>
-    </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.5">
-      <c r="B27" s="64" t="s">
-        <v>137</v>
-      </c>
-      <c r="C27" s="88">
-        <v>3.3000000000000015E-2</v>
-      </c>
-      <c r="G27" s="63"/>
-    </row>
-    <row r="28" spans="2:7" x14ac:dyDescent="0.5">
-      <c r="B28" s="73" t="s">
-        <v>138</v>
-      </c>
-      <c r="C28" s="89">
+      <c r="C28" s="81">
         <f>D16</f>
         <v>20000000</v>
       </c>
-      <c r="G28" s="63"/>
+      <c r="G28" s="58"/>
     </row>
     <row r="29" spans="2:7" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="B29" s="85" t="s">
-        <v>139</v>
-      </c>
-      <c r="C29" s="90">
+      <c r="B29" s="77" t="s">
+        <v>137</v>
+      </c>
+      <c r="C29" s="82">
         <f>C28*C$27/12</f>
         <v>55000.000000000029</v>
       </c>
-      <c r="G29" s="63"/>
+      <c r="G29" s="58"/>
     </row>
     <row r="30" spans="2:7" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="B30" s="91"/>
-      <c r="C30" s="92"/>
-      <c r="G30" s="63"/>
+      <c r="B30" s="83"/>
+      <c r="C30" s="84"/>
+      <c r="G30" s="58"/>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.5">
-      <c r="B31" s="64" t="s">
-        <v>140</v>
-      </c>
-      <c r="C31" s="92">
+      <c r="B31" s="59" t="s">
+        <v>138</v>
+      </c>
+      <c r="C31" s="84">
         <f>C$9*C$8</f>
         <v>0</v>
       </c>
-      <c r="D31" s="93">
+      <c r="D31" s="85">
         <f>C31/C29</f>
         <v>0</v>
       </c>
-      <c r="G31" s="63"/>
+      <c r="G31" s="58"/>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.5">
-      <c r="B32" s="64" t="s">
-        <v>141</v>
-      </c>
-      <c r="C32" s="92">
+      <c r="B32" s="59" t="s">
+        <v>139</v>
+      </c>
+      <c r="C32" s="84">
         <f>$C$29*D32</f>
         <v>2750.0000000000018</v>
       </c>
-      <c r="D32" s="94">
+      <c r="D32" s="86">
         <f>Assumptions!C15</f>
         <v>0.05</v>
       </c>
-      <c r="G32" s="63"/>
+      <c r="G32" s="58"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.5">
-      <c r="B33" s="64" t="s">
-        <v>142</v>
-      </c>
-      <c r="C33" s="92">
+      <c r="B33" s="59" t="s">
+        <v>140</v>
+      </c>
+      <c r="C33" s="84">
         <f t="shared" ref="C33:C36" si="1">$C$29*D33</f>
         <v>1650.0000000000009</v>
       </c>
-      <c r="D33" s="93">
+      <c r="D33" s="85">
         <f>Assumptions!C16</f>
         <v>0.03</v>
       </c>
-      <c r="G33" s="63"/>
+      <c r="G33" s="58"/>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.5">
-      <c r="B34" s="64" t="s">
-        <v>143</v>
-      </c>
-      <c r="C34" s="92">
+      <c r="B34" s="59" t="s">
+        <v>141</v>
+      </c>
+      <c r="C34" s="84">
         <f t="shared" si="1"/>
         <v>1100.0000000000007</v>
       </c>
-      <c r="D34" s="95">
+      <c r="D34" s="87">
         <v>0.02</v>
       </c>
-      <c r="G34" s="63" t="s">
-        <v>115</v>
+      <c r="G34" s="58" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.5">
-      <c r="B35" s="64" t="s">
-        <v>144</v>
-      </c>
-      <c r="C35" s="92">
+      <c r="B35" s="59" t="s">
+        <v>142</v>
+      </c>
+      <c r="C35" s="84">
         <f t="shared" si="1"/>
         <v>550.00000000000034</v>
       </c>
-      <c r="D35" s="95">
+      <c r="D35" s="87">
         <v>0.01</v>
       </c>
-      <c r="G35" s="63"/>
+      <c r="G35" s="58"/>
     </row>
     <row r="36" spans="2:7" x14ac:dyDescent="0.5">
-      <c r="B36" s="64" t="s">
-        <v>145</v>
-      </c>
-      <c r="C36" s="92">
+      <c r="B36" s="59" t="s">
+        <v>143</v>
+      </c>
+      <c r="C36" s="84">
         <f t="shared" si="1"/>
         <v>5500.0000000000036</v>
       </c>
-      <c r="D36" s="95">
+      <c r="D36" s="87">
         <v>0.1</v>
       </c>
-      <c r="G36" s="63" t="s">
-        <v>111</v>
+      <c r="G36" s="58" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="37" spans="2:7" ht="15.4" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B37" s="83" t="s">
-        <v>146</v>
-      </c>
-      <c r="C37" s="96">
+      <c r="B37" s="75" t="s">
+        <v>144</v>
+      </c>
+      <c r="C37" s="88">
         <v>0</v>
       </c>
-      <c r="D37" s="97">
+      <c r="D37" s="89">
         <f>C37/C29</f>
         <v>0</v>
       </c>
-      <c r="G37" s="63"/>
+      <c r="G37" s="58"/>
     </row>
     <row r="38" spans="2:7" ht="16.149999999999999" thickTop="1" x14ac:dyDescent="0.5">
-      <c r="B38" s="85" t="s">
-        <v>161</v>
-      </c>
-      <c r="C38" s="90">
+      <c r="B38" s="77" t="s">
+        <v>159</v>
+      </c>
+      <c r="C38" s="82">
         <f>C29-SUM(C31:C37)</f>
         <v>43450.000000000022</v>
       </c>
-      <c r="D38" s="93">
+      <c r="D38" s="85">
         <f>C38/C29</f>
         <v>0.78999999999999992</v>
       </c>
-      <c r="G38" s="63"/>
+      <c r="G38" s="58"/>
     </row>
     <row r="39" spans="2:7" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="B39" s="85" t="s">
-        <v>147</v>
-      </c>
-      <c r="C39" s="98">
+      <c r="B39" s="77" t="s">
+        <v>145</v>
+      </c>
+      <c r="C39" s="90">
         <f>Assumptions!C19</f>
         <v>0.02</v>
       </c>
-      <c r="G39" s="63"/>
+      <c r="G39" s="58"/>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.5">
-      <c r="G40" s="63"/>
+      <c r="G40" s="58"/>
     </row>
     <row r="41" spans="2:7" ht="15.75" x14ac:dyDescent="0.55000000000000004">
-      <c r="B41" s="71" t="s">
+      <c r="B41" s="66" t="s">
+        <v>146</v>
+      </c>
+      <c r="G41" s="57" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="42" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="G42" s="58"/>
+    </row>
+    <row r="43" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="B43" s="59" t="s">
+        <v>147</v>
+      </c>
+      <c r="C43" s="91">
+        <v>0.3</v>
+      </c>
+      <c r="G43" s="58" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="44" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="B44" s="68" t="s">
         <v>148</v>
       </c>
-      <c r="G41" s="62" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="42" spans="2:7" x14ac:dyDescent="0.5">
-      <c r="G42" s="63"/>
-    </row>
-    <row r="43" spans="2:7" x14ac:dyDescent="0.5">
-      <c r="B43" s="64" t="s">
-        <v>149</v>
-      </c>
-      <c r="C43" s="99">
-        <v>0.3</v>
-      </c>
-      <c r="G43" s="63" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="44" spans="2:7" x14ac:dyDescent="0.5">
-      <c r="B44" s="73" t="s">
-        <v>150</v>
-      </c>
-      <c r="C44" s="100">
+      <c r="C44" s="92">
         <f>(1+C43)^(1/C10)-1</f>
         <v>1.7644813405053306E-2</v>
       </c>
-      <c r="G44" s="63"/>
+      <c r="G44" s="58"/>
     </row>
     <row r="45" spans="2:7" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="B45" s="85" t="s">
-        <v>151</v>
-      </c>
-      <c r="C45" s="101">
+      <c r="B45" s="77" t="s">
+        <v>149</v>
+      </c>
+      <c r="C45" s="93">
         <f>D16*(1+C$43)</f>
         <v>26000000</v>
       </c>
-      <c r="G45" s="63"/>
+      <c r="G45" s="58"/>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.5">
-      <c r="G46" s="63"/>
+      <c r="G46" s="58"/>
     </row>
     <row r="47" spans="2:7" ht="15.75" x14ac:dyDescent="0.55000000000000004">
-      <c r="B47" s="71" t="s">
-        <v>152</v>
-      </c>
-      <c r="G47" s="62" t="s">
-        <v>160</v>
+      <c r="B47" s="66" t="s">
+        <v>150</v>
+      </c>
+      <c r="G47" s="57" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.5">
-      <c r="G48" s="63"/>
+      <c r="G48" s="58"/>
     </row>
     <row r="49" spans="2:7" x14ac:dyDescent="0.5">
-      <c r="B49" s="64" t="s">
-        <v>127</v>
-      </c>
-      <c r="C49" s="102" t="str">
+      <c r="B49" s="59" t="s">
+        <v>125</v>
+      </c>
+      <c r="C49" s="94" t="str">
         <f>C14</f>
-        <v>Asking Price</v>
-      </c>
-      <c r="D49" s="102" t="str">
+        <v>要價</v>
+      </c>
+      <c r="D49" s="94" t="str">
         <f>D14</f>
-        <v>Comparable</v>
-      </c>
-      <c r="E49" s="102" t="str">
+        <v>可比售價</v>
+      </c>
+      <c r="E49" s="94" t="str">
         <f>E14</f>
-        <v>IRR Netural Price</v>
-      </c>
-      <c r="G49" s="63"/>
+        <v>IRR中性售價</v>
+      </c>
+      <c r="G49" s="58"/>
     </row>
     <row r="50" spans="2:7" x14ac:dyDescent="0.5">
-      <c r="B50" s="64" t="s">
-        <v>153</v>
-      </c>
-      <c r="C50" s="77">
+      <c r="B50" s="59" t="s">
+        <v>151</v>
+      </c>
+      <c r="C50" s="72">
         <f>C16</f>
         <v>22000000</v>
       </c>
-      <c r="D50" s="77">
+      <c r="D50" s="72">
         <f t="shared" ref="D50:E50" si="2">D16</f>
         <v>20000000</v>
       </c>
-      <c r="E50" s="77">
+      <c r="E50" s="72">
         <f t="shared" si="2"/>
         <v>19500000</v>
       </c>
-      <c r="G50" s="63"/>
+      <c r="G50" s="58"/>
     </row>
     <row r="51" spans="2:7" x14ac:dyDescent="0.5">
-      <c r="B51" s="64" t="s">
-        <v>135</v>
-      </c>
-      <c r="C51" s="103">
+      <c r="B51" s="59" t="s">
+        <v>133</v>
+      </c>
+      <c r="C51" s="95">
         <f>C23</f>
         <v>23247000</v>
       </c>
-      <c r="D51" s="103">
+      <c r="D51" s="95">
         <f>D23</f>
         <v>21090000</v>
       </c>
-      <c r="E51" s="103">
+      <c r="E51" s="95">
         <f>E23</f>
         <v>20479500</v>
       </c>
-      <c r="G51" s="63"/>
+      <c r="G51" s="58"/>
     </row>
     <row r="52" spans="2:7" x14ac:dyDescent="0.5">
-      <c r="B52" s="64" t="s">
-        <v>162</v>
-      </c>
-      <c r="C52" s="104">
+      <c r="B52" s="59" t="s">
+        <v>160</v>
+      </c>
+      <c r="C52" s="107">
         <f>C$38*12</f>
         <v>521400.00000000023</v>
       </c>
-      <c r="D52" s="104"/>
-      <c r="E52" s="104"/>
-      <c r="G52" s="63"/>
+      <c r="D52" s="107"/>
+      <c r="E52" s="107"/>
+      <c r="G52" s="58"/>
     </row>
     <row r="53" spans="2:7" ht="15.4" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B53" s="83" t="s">
-        <v>154</v>
-      </c>
-      <c r="C53" s="105">
+      <c r="B53" s="75" t="s">
+        <v>152</v>
+      </c>
+      <c r="C53" s="103">
         <f>C$45</f>
         <v>26000000</v>
       </c>
-      <c r="D53" s="105"/>
-      <c r="E53" s="105"/>
-      <c r="G53" s="63"/>
+      <c r="D53" s="103"/>
+      <c r="E53" s="103"/>
+      <c r="G53" s="58"/>
     </row>
     <row r="54" spans="2:7" ht="16.149999999999999" thickTop="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B54" s="85" t="s">
-        <v>155</v>
-      </c>
-      <c r="C54" s="106">
+      <c r="B54" s="77" t="s">
+        <v>153</v>
+      </c>
+      <c r="C54" s="96">
         <f>RATE(15, $C52*(1+$C$39), -C51, $C53 / (1+$C$39)^15) + $C$39</f>
         <v>3.2569232155100998E-2</v>
       </c>
-      <c r="D54" s="106">
+      <c r="D54" s="96">
         <f t="shared" ref="D54:E54" si="3">RATE(15, $C52*(1+$C$39), -D51, $C53 / (1+$C$39)^15) + $C$39</f>
         <v>4.0372636869005607E-2</v>
       </c>
-      <c r="E54" s="106">
+      <c r="E54" s="96">
         <f t="shared" si="3"/>
         <v>4.2755034579381089E-2</v>
       </c>
-      <c r="G54" s="63"/>
+      <c r="G54" s="58"/>
     </row>
     <row r="55" spans="2:7" x14ac:dyDescent="0.5">
-      <c r="G55" s="63"/>
+      <c r="G55" s="58"/>
     </row>
     <row r="56" spans="2:7" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="B56" s="107" t="s">
+      <c r="B56" s="97" t="s">
+        <v>154</v>
+      </c>
+      <c r="G56" s="58"/>
+    </row>
+    <row r="57" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="B57" s="56" t="s">
+        <v>155</v>
+      </c>
+      <c r="G57" s="58"/>
+    </row>
+    <row r="58" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="B58" s="56" t="s">
         <v>156</v>
       </c>
-      <c r="G56" s="63"/>
-    </row>
-    <row r="57" spans="2:7" x14ac:dyDescent="0.5">
-      <c r="B57" s="61" t="s">
+      <c r="G58" s="58"/>
+    </row>
+    <row r="59" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="B59" s="56" t="s">
         <v>157</v>
       </c>
-      <c r="G57" s="63"/>
-    </row>
-    <row r="58" spans="2:7" x14ac:dyDescent="0.5">
-      <c r="B58" s="61" t="s">
-        <v>158</v>
-      </c>
-      <c r="G58" s="63"/>
-    </row>
-    <row r="59" spans="2:7" x14ac:dyDescent="0.5">
-      <c r="B59" s="61" t="s">
-        <v>159</v>
-      </c>
-      <c r="G59" s="63"/>
+      <c r="G59" s="58"/>
     </row>
   </sheetData>
   <dataConsolidate/>
@@ -3276,7 +3282,7 @@
   <sheetData>
     <row r="2" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B2" s="28" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.45">
@@ -3284,7 +3290,7 @@
         <v>37</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.45">
@@ -3314,7 +3320,7 @@
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B8" s="30" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C8" s="18">
         <v>485</v>
@@ -3322,7 +3328,7 @@
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B9" s="30" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C9" s="19">
         <v>2.2000000000000002</v>
@@ -3339,7 +3345,7 @@
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B12" s="27" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.45">
@@ -3353,12 +3359,12 @@
         <v>36</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B15" s="31" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C15" s="25">
         <f>C16/C8</f>
@@ -3391,12 +3397,12 @@
       <c r="B17" s="30" t="s">
         <v>59</v>
       </c>
-      <c r="C17" s="57">
+      <c r="C17" s="100">
         <f>Assumptions!C9</f>
         <v>0.01</v>
       </c>
-      <c r="D17" s="57"/>
-      <c r="E17" s="57"/>
+      <c r="D17" s="100"/>
+      <c r="E17" s="100"/>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B18" s="30" t="s">
@@ -3416,38 +3422,38 @@
       <c r="B19" s="30" t="s">
         <v>58</v>
       </c>
-      <c r="C19" s="58">
+      <c r="C19" s="101">
         <f>Assumptions!C10</f>
         <v>1E-3</v>
       </c>
-      <c r="D19" s="58"/>
-      <c r="E19" s="58"/>
+      <c r="D19" s="101"/>
+      <c r="E19" s="101"/>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B20" s="30" t="s">
-        <v>104</v>
-      </c>
-      <c r="C20" s="59">
+        <v>103</v>
+      </c>
+      <c r="C20" s="102">
         <f>Assumptions!C11</f>
         <v>20000</v>
       </c>
-      <c r="D20" s="59"/>
-      <c r="E20" s="59"/>
+      <c r="D20" s="102"/>
+      <c r="E20" s="102"/>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B21" s="30" t="s">
-        <v>105</v>
-      </c>
-      <c r="C21" s="59">
+        <v>104</v>
+      </c>
+      <c r="C21" s="102">
         <f>Assumptions!C12</f>
         <v>5000</v>
       </c>
-      <c r="D21" s="59"/>
-      <c r="E21" s="59"/>
+      <c r="D21" s="102"/>
+      <c r="E21" s="102"/>
     </row>
     <row r="22" spans="2:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B22" s="32" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C22" s="49">
         <v>0</v>
@@ -3478,7 +3484,7 @@
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B25" s="27" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="26" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -3555,7 +3561,7 @@
     </row>
     <row r="34" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B34" s="30" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C34" s="24">
         <f t="shared" si="1"/>
@@ -3568,7 +3574,7 @@
     </row>
     <row r="35" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B35" s="30" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C35" s="24">
         <f t="shared" ca="1" si="1"/>
@@ -3628,7 +3634,7 @@
     </row>
     <row r="41" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B41" s="27" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="43" spans="2:4" x14ac:dyDescent="0.45">
@@ -3659,7 +3665,7 @@
     </row>
     <row r="47" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B47" s="27" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="49" spans="2:5" x14ac:dyDescent="0.45">
@@ -3717,23 +3723,23 @@
       <c r="B52" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="C52" s="55">
+      <c r="C52" s="98">
         <f ca="1">C$38*12</f>
         <v>185282.125</v>
       </c>
-      <c r="D52" s="55"/>
-      <c r="E52" s="55"/>
+      <c r="D52" s="98"/>
+      <c r="E52" s="98"/>
     </row>
     <row r="53" spans="2:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B53" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="C53" s="56">
+      <c r="C53" s="99">
         <f>C$45</f>
         <v>9772750</v>
       </c>
-      <c r="D53" s="56"/>
-      <c r="E53" s="56"/>
+      <c r="D53" s="99"/>
+      <c r="E53" s="99"/>
     </row>
     <row r="54" spans="2:5" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
       <c r="B54" s="21" t="s">
@@ -3754,22 +3760,22 @@
     </row>
     <row r="56" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B56" s="36" t="s">
-        <v>67</v>
+        <v>161</v>
       </c>
     </row>
     <row r="57" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B57" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="58" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B58" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="59" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B59" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -3802,7 +3808,7 @@
   <sheetData>
     <row r="2" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B2" s="28" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.45">
@@ -3810,7 +3816,7 @@
         <v>37</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.45">
@@ -3840,7 +3846,7 @@
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B8" s="30" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C8" s="18">
         <v>315</v>
@@ -3848,7 +3854,7 @@
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B9" s="30" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C9" s="19">
         <v>2</v>
@@ -3865,7 +3871,7 @@
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B12" s="27" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.45">
@@ -3879,12 +3885,12 @@
         <v>36</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B15" s="31" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C15" s="25">
         <f>C16/C8</f>
@@ -3917,12 +3923,12 @@
       <c r="B17" s="30" t="s">
         <v>59</v>
       </c>
-      <c r="C17" s="57">
+      <c r="C17" s="100">
         <f>Assumptions!C9</f>
         <v>0.01</v>
       </c>
-      <c r="D17" s="57"/>
-      <c r="E17" s="57"/>
+      <c r="D17" s="100"/>
+      <c r="E17" s="100"/>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B18" s="30" t="s">
@@ -3944,38 +3950,38 @@
       <c r="B19" s="30" t="s">
         <v>58</v>
       </c>
-      <c r="C19" s="58">
+      <c r="C19" s="101">
         <f>Assumptions!C10</f>
         <v>1E-3</v>
       </c>
-      <c r="D19" s="58"/>
-      <c r="E19" s="58"/>
+      <c r="D19" s="101"/>
+      <c r="E19" s="101"/>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B20" s="30" t="s">
-        <v>104</v>
-      </c>
-      <c r="C20" s="59">
+        <v>103</v>
+      </c>
+      <c r="C20" s="102">
         <f>Assumptions!C11</f>
         <v>20000</v>
       </c>
-      <c r="D20" s="59"/>
-      <c r="E20" s="59"/>
+      <c r="D20" s="102"/>
+      <c r="E20" s="102"/>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B21" s="30" t="s">
-        <v>105</v>
-      </c>
-      <c r="C21" s="59">
+        <v>104</v>
+      </c>
+      <c r="C21" s="102">
         <f>Assumptions!C12</f>
         <v>5000</v>
       </c>
-      <c r="D21" s="59"/>
-      <c r="E21" s="59"/>
+      <c r="D21" s="102"/>
+      <c r="E21" s="102"/>
     </row>
     <row r="22" spans="2:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B22" s="32" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C22" s="49">
         <v>135000</v>
@@ -4006,7 +4012,7 @@
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B25" s="27" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="26" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -4083,7 +4089,7 @@
     </row>
     <row r="34" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B34" s="30" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C34" s="24">
         <f t="shared" si="1"/>
@@ -4096,7 +4102,7 @@
     </row>
     <row r="35" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B35" s="30" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C35" s="24">
         <f t="shared" ca="1" si="1"/>
@@ -4156,7 +4162,7 @@
     </row>
     <row r="41" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B41" s="27" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="43" spans="2:4" x14ac:dyDescent="0.45">
@@ -4187,7 +4193,7 @@
     </row>
     <row r="47" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B47" s="27" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="49" spans="2:5" x14ac:dyDescent="0.45">
@@ -4245,23 +4251,23 @@
       <c r="B52" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="C52" s="55">
+      <c r="C52" s="98">
         <f ca="1">C$38*12</f>
         <v>141840.00000000003</v>
       </c>
-      <c r="D52" s="55"/>
-      <c r="E52" s="55"/>
+      <c r="D52" s="98"/>
+      <c r="E52" s="98"/>
     </row>
     <row r="53" spans="2:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B53" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="C53" s="56">
+      <c r="C53" s="99">
         <f>C$45</f>
         <v>4279905</v>
       </c>
-      <c r="D53" s="56"/>
-      <c r="E53" s="56"/>
+      <c r="D53" s="99"/>
+      <c r="E53" s="99"/>
     </row>
     <row r="54" spans="2:5" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
       <c r="B54" s="21" t="s">
@@ -4282,22 +4288,22 @@
     </row>
     <row r="56" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B56" s="36" t="s">
-        <v>67</v>
+        <v>161</v>
       </c>
     </row>
     <row r="57" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B57" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="58" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B58" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="59" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B59" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -4331,11 +4337,11 @@
   <sheetData>
     <row r="2" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B2" s="37" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C2" s="38"/>
       <c r="D2" s="37" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.45">
@@ -4345,11 +4351,11 @@
     </row>
     <row r="4" spans="2:4" ht="57" x14ac:dyDescent="0.45">
       <c r="B4" s="39" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C4" s="38"/>
       <c r="D4" s="39" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.45">
@@ -4359,11 +4365,11 @@
     </row>
     <row r="6" spans="2:4" ht="128.25" x14ac:dyDescent="0.45">
       <c r="B6" s="39" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C6" s="38"/>
       <c r="D6" s="39" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.45">
@@ -4373,11 +4379,11 @@
     </row>
     <row r="8" spans="2:4" ht="85.5" x14ac:dyDescent="0.45">
       <c r="B8" s="39" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C8" s="38"/>
       <c r="D8" s="39" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" spans="2:4" x14ac:dyDescent="0.45">
@@ -4387,11 +4393,11 @@
     </row>
     <row r="10" spans="2:4" ht="85.5" x14ac:dyDescent="0.45">
       <c r="B10" s="39" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C10" s="38"/>
       <c r="D10" s="39" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="11" spans="2:4" x14ac:dyDescent="0.45">
@@ -4406,11 +4412,11 @@
     </row>
     <row r="13" spans="2:4" ht="71.25" x14ac:dyDescent="0.45">
       <c r="B13" s="39" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C13" s="38"/>
       <c r="D13" s="39" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="14" spans="2:4" x14ac:dyDescent="0.45">
@@ -4420,11 +4426,11 @@
     </row>
     <row r="15" spans="2:4" ht="128.25" x14ac:dyDescent="0.45">
       <c r="B15" s="39" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C15" s="38"/>
       <c r="D15" s="39" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16" spans="2:4" x14ac:dyDescent="0.45">
@@ -4434,11 +4440,11 @@
     </row>
     <row r="17" spans="2:4" ht="85.5" x14ac:dyDescent="0.45">
       <c r="B17" s="39" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C17" s="38"/>
       <c r="D17" s="39" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>

--- a/financial_models/Res_Property_Monitor.xlsx
+++ b/financial_models/Res_Property_Monitor.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85E43CB5-3DFF-4999-99D5-198D56981D66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA155BF1-28E9-44AC-82B7-869A681DF749}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="6150" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Assumptions" sheetId="13" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="166">
   <si>
     <t>Value</t>
   </si>
@@ -839,9 +839,6 @@
     <t>維修/保養/儲備基金</t>
   </si>
   <si>
-    <t>舊樓溢價成本</t>
-  </si>
-  <si>
     <t>空置準備</t>
   </si>
   <si>
@@ -909,6 +906,9 @@
   </si>
   <si>
     <t>Village House</t>
+  </si>
+  <si>
+    <t>舊樓維修成本</t>
   </si>
 </sst>
 </file>
@@ -1091,7 +1091,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="108">
+  <cellXfs count="110">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1379,6 +1379,12 @@
     </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2608,7 +2614,7 @@
     </row>
     <row r="56" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B56" s="36" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G56" s="4"/>
     </row>
@@ -2667,7 +2673,7 @@
         <v>115</v>
       </c>
       <c r="G2" s="57" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.5">
@@ -2687,7 +2693,7 @@
         <v>116</v>
       </c>
       <c r="C5" s="60" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G5" s="58"/>
     </row>
@@ -2746,7 +2752,7 @@
         <v>123</v>
       </c>
       <c r="G12" s="57" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.5">
@@ -2757,13 +2763,13 @@
         <v>125</v>
       </c>
       <c r="C14" s="67" t="s">
+        <v>161</v>
+      </c>
+      <c r="D14" s="67" t="s">
         <v>162</v>
       </c>
-      <c r="D14" s="67" t="s">
+      <c r="E14" s="67" t="s">
         <v>163</v>
-      </c>
-      <c r="E14" s="67" t="s">
-        <v>164</v>
       </c>
       <c r="G14" s="58"/>
     </row>
@@ -2907,7 +2913,7 @@
         <v>134</v>
       </c>
       <c r="G25" s="57" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="26" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.5">
@@ -3007,7 +3013,7 @@
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.5">
       <c r="B35" s="59" t="s">
-        <v>142</v>
+        <v>165</v>
       </c>
       <c r="C35" s="84">
         <f t="shared" si="1"/>
@@ -3020,7 +3026,7 @@
     </row>
     <row r="36" spans="2:7" x14ac:dyDescent="0.5">
       <c r="B36" s="59" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C36" s="84">
         <f t="shared" si="1"/>
@@ -3035,7 +3041,7 @@
     </row>
     <row r="37" spans="2:7" ht="15.4" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B37" s="75" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C37" s="88">
         <v>0</v>
@@ -3048,7 +3054,7 @@
     </row>
     <row r="38" spans="2:7" ht="16.149999999999999" thickTop="1" x14ac:dyDescent="0.5">
       <c r="B38" s="77" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C38" s="82">
         <f>C29-SUM(C31:C37)</f>
@@ -3062,7 +3068,7 @@
     </row>
     <row r="39" spans="2:7" ht="15.75" x14ac:dyDescent="0.5">
       <c r="B39" s="77" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C39" s="90">
         <f>Assumptions!C19</f>
@@ -3075,10 +3081,10 @@
     </row>
     <row r="41" spans="2:7" ht="15.75" x14ac:dyDescent="0.55000000000000004">
       <c r="B41" s="66" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G41" s="57" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.5">
@@ -3086,7 +3092,7 @@
     </row>
     <row r="43" spans="2:7" x14ac:dyDescent="0.5">
       <c r="B43" s="59" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C43" s="91">
         <v>0.3</v>
@@ -3097,7 +3103,7 @@
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.5">
       <c r="B44" s="68" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C44" s="92">
         <f>(1+C43)^(1/C10)-1</f>
@@ -3107,7 +3113,7 @@
     </row>
     <row r="45" spans="2:7" ht="15.75" x14ac:dyDescent="0.5">
       <c r="B45" s="77" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C45" s="93">
         <f>D16*(1+C$43)</f>
@@ -3120,10 +3126,10 @@
     </row>
     <row r="47" spans="2:7" ht="15.75" x14ac:dyDescent="0.55000000000000004">
       <c r="B47" s="66" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G47" s="57" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.5">
@@ -3149,7 +3155,7 @@
     </row>
     <row r="50" spans="2:7" x14ac:dyDescent="0.5">
       <c r="B50" s="59" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C50" s="72">
         <f>C16</f>
@@ -3185,7 +3191,7 @@
     </row>
     <row r="52" spans="2:7" x14ac:dyDescent="0.5">
       <c r="B52" s="59" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C52" s="107">
         <f>C$38*12</f>
@@ -3197,7 +3203,7 @@
     </row>
     <row r="53" spans="2:7" ht="15.4" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B53" s="75" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C53" s="103">
         <f>C$45</f>
@@ -3209,7 +3215,7 @@
     </row>
     <row r="54" spans="2:7" ht="16.149999999999999" thickTop="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B54" s="77" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C54" s="96">
         <f>RATE(15, $C52*(1+$C$39), -C51, $C53 / (1+$C$39)^15) + $C$39</f>
@@ -3230,25 +3236,25 @@
     </row>
     <row r="56" spans="2:7" ht="15.75" x14ac:dyDescent="0.5">
       <c r="B56" s="97" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G56" s="58"/>
     </row>
     <row r="57" spans="2:7" x14ac:dyDescent="0.5">
       <c r="B57" s="56" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G57" s="58"/>
     </row>
     <row r="58" spans="2:7" x14ac:dyDescent="0.5">
       <c r="B58" s="56" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G58" s="58"/>
     </row>
     <row r="59" spans="2:7" x14ac:dyDescent="0.5">
       <c r="B59" s="56" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G59" s="58"/>
     </row>
@@ -3760,7 +3766,7 @@
     </row>
     <row r="56" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B56" s="36" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="57" spans="2:5" x14ac:dyDescent="0.45">
@@ -3798,513 +3804,605 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:E59"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="B2:G59"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="15" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" customWidth="1"/>
-    <col min="2" max="2" width="29.86328125" customWidth="1"/>
-    <col min="3" max="9" width="16.59765625" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" style="56" customWidth="1"/>
+    <col min="2" max="2" width="29.86328125" style="56" customWidth="1"/>
+    <col min="3" max="5" width="16.59765625" style="56" customWidth="1"/>
+    <col min="6" max="6" width="2.59765625" style="56" customWidth="1"/>
+    <col min="7" max="7" width="90.59765625" style="56" customWidth="1"/>
+    <col min="8" max="9" width="16.59765625" style="56" customWidth="1"/>
+    <col min="10" max="16384" width="8.796875" style="56"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B2" s="28" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B4" s="30" t="s">
-        <v>37</v>
-      </c>
-      <c r="C4" s="15" t="s">
+    <row r="2" spans="2:7" ht="15.75" x14ac:dyDescent="0.55000000000000004">
+      <c r="B2" s="55" t="s">
+        <v>115</v>
+      </c>
+      <c r="G2" s="57" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="G3" s="58"/>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="B4" s="59" t="s">
+        <v>117</v>
+      </c>
+      <c r="C4" s="60" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B5" s="30" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="15" t="s">
+      <c r="G4" s="58"/>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="B5" s="59" t="s">
+        <v>116</v>
+      </c>
+      <c r="C5" s="60" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B6" s="30" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" s="16">
+      <c r="G5" s="58"/>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="B6" s="59" t="s">
+        <v>118</v>
+      </c>
+      <c r="C6" s="61">
         <v>1995</v>
       </c>
-    </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B7" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" s="17">
+      <c r="G6" s="58"/>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="B7" s="59" t="s">
+        <v>119</v>
+      </c>
+      <c r="C7" s="62">
         <f ca="1">YEAR(TODAY())-C6</f>
         <v>31</v>
       </c>
-    </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B8" s="30" t="s">
-        <v>71</v>
-      </c>
-      <c r="C8" s="18">
+      <c r="G7" s="58"/>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="B8" s="59" t="s">
+        <v>120</v>
+      </c>
+      <c r="C8" s="63">
         <v>315</v>
       </c>
-    </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B9" s="30" t="s">
-        <v>72</v>
-      </c>
-      <c r="C9" s="19">
+      <c r="G8" s="58"/>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="B9" s="59" t="s">
+        <v>121</v>
+      </c>
+      <c r="C9" s="64">
         <v>2</v>
       </c>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B10" s="30" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" s="46">
+      <c r="G9" s="58"/>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="B10" s="59" t="s">
+        <v>122</v>
+      </c>
+      <c r="C10" s="65">
         <f>Holding_Period</f>
         <v>15</v>
       </c>
-    </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B12" s="27" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B14" s="30" t="s">
-        <v>35</v>
-      </c>
-      <c r="C14" s="6" t="s">
+      <c r="G10" s="58"/>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="G11" s="58"/>
+    </row>
+    <row r="12" spans="2:7" ht="15.75" x14ac:dyDescent="0.55000000000000004">
+      <c r="B12" s="66" t="s">
+        <v>123</v>
+      </c>
+      <c r="G12" s="57" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="G13" s="58"/>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="B14" s="59" t="s">
+        <v>125</v>
+      </c>
+      <c r="C14" s="67" t="s">
         <v>43</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="67" t="s">
         <v>36</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="E14" s="67" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B15" s="31" t="s">
-        <v>73</v>
-      </c>
-      <c r="C15" s="25">
+      <c r="G14" s="58"/>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="B15" s="68" t="s">
+        <v>124</v>
+      </c>
+      <c r="C15" s="69">
         <f>C16/C8</f>
         <v>13587.301587301587</v>
       </c>
-      <c r="D15" s="26">
+      <c r="D15" s="70">
         <v>13587</v>
       </c>
-      <c r="E15" s="25">
+      <c r="E15" s="69">
         <f>E16/C8</f>
         <v>11619.047619047618</v>
       </c>
-    </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B16" s="30" t="s">
-        <v>47</v>
-      </c>
-      <c r="C16" s="14">
+      <c r="G15" s="58"/>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="B16" s="59" t="s">
+        <v>126</v>
+      </c>
+      <c r="C16" s="71">
         <v>4280000</v>
       </c>
-      <c r="D16" s="20">
+      <c r="D16" s="72">
         <f>D15*C$8</f>
         <v>4279905</v>
       </c>
-      <c r="E16" s="40">
+      <c r="E16" s="73">
         <v>3660000</v>
       </c>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B17" s="30" t="s">
-        <v>59</v>
-      </c>
-      <c r="C17" s="100">
+      <c r="G16" s="58"/>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="B17" s="59" t="s">
+        <v>127</v>
+      </c>
+      <c r="C17" s="104">
         <f>Assumptions!C9</f>
         <v>0.01</v>
       </c>
-      <c r="D17" s="100"/>
-      <c r="E17" s="100"/>
-    </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B18" s="30" t="s">
-        <v>56</v>
-      </c>
-      <c r="C18" s="10">
+      <c r="D17" s="104"/>
+      <c r="E17" s="104"/>
+      <c r="G17" s="58"/>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="B18" s="59" t="s">
+        <v>128</v>
+      </c>
+      <c r="C18" s="108">
         <v>5.5E-2</v>
       </c>
-      <c r="D18" s="10">
+      <c r="D18" s="108">
         <f>C18</f>
         <v>5.5E-2</v>
       </c>
-      <c r="E18" s="10">
+      <c r="E18" s="108">
         <f>D18</f>
         <v>5.5E-2</v>
       </c>
-    </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B19" s="30" t="s">
-        <v>58</v>
-      </c>
-      <c r="C19" s="101">
+      <c r="G18" s="58"/>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="B19" s="59" t="s">
+        <v>129</v>
+      </c>
+      <c r="C19" s="105">
         <f>Assumptions!C10</f>
         <v>1E-3</v>
       </c>
-      <c r="D19" s="101"/>
-      <c r="E19" s="101"/>
-    </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B20" s="30" t="s">
-        <v>103</v>
-      </c>
-      <c r="C20" s="102">
+      <c r="D19" s="105"/>
+      <c r="E19" s="105"/>
+      <c r="G19" s="58"/>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="B20" s="59" t="s">
+        <v>130</v>
+      </c>
+      <c r="C20" s="106">
         <f>Assumptions!C11</f>
         <v>20000</v>
       </c>
-      <c r="D20" s="102"/>
-      <c r="E20" s="102"/>
-    </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B21" s="30" t="s">
-        <v>104</v>
-      </c>
-      <c r="C21" s="102">
+      <c r="D20" s="106"/>
+      <c r="E20" s="106"/>
+      <c r="G20" s="58"/>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="B21" s="59" t="s">
+        <v>131</v>
+      </c>
+      <c r="C21" s="106">
         <f>Assumptions!C12</f>
         <v>5000</v>
       </c>
-      <c r="D21" s="102"/>
-      <c r="E21" s="102"/>
-    </row>
-    <row r="22" spans="2:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B22" s="32" t="s">
-        <v>100</v>
-      </c>
-      <c r="C22" s="49">
+      <c r="D21" s="106"/>
+      <c r="E21" s="106"/>
+      <c r="G21" s="58"/>
+    </row>
+    <row r="22" spans="2:7" ht="15.4" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B22" s="75" t="s">
+        <v>132</v>
+      </c>
+      <c r="C22" s="76">
         <v>135000</v>
       </c>
-      <c r="D22" s="49">
+      <c r="D22" s="76">
         <v>135000</v>
       </c>
-      <c r="E22" s="49">
+      <c r="E22" s="76">
         <v>135000</v>
       </c>
-    </row>
-    <row r="23" spans="2:5" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="B23" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="C23" s="22">
+      <c r="G22" s="58" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" ht="16.149999999999999" thickTop="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B23" s="77" t="s">
+        <v>133</v>
+      </c>
+      <c r="C23" s="78">
         <f>C16+C16*($C$17+C18+$C$19)+$C$20+C22</f>
         <v>4717480</v>
       </c>
-      <c r="D23" s="22">
+      <c r="D23" s="78">
         <f t="shared" ref="D23:E23" si="0">D16+D16*($C$17+D18+$C$19)+$C$20+D22</f>
         <v>4717378.7300000004</v>
       </c>
-      <c r="E23" s="22">
+      <c r="E23" s="78">
         <f t="shared" si="0"/>
         <v>4056560</v>
       </c>
-    </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B25" s="27" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="26" spans="2:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="C26" s="5"/>
-    </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B27" s="30" t="s">
-        <v>61</v>
-      </c>
-      <c r="C27" s="47">
+      <c r="G23" s="58"/>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="G24" s="58"/>
+    </row>
+    <row r="25" spans="2:7" ht="15.75" x14ac:dyDescent="0.55000000000000004">
+      <c r="B25" s="66" t="s">
+        <v>134</v>
+      </c>
+      <c r="G25" s="57" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="C26" s="79"/>
+      <c r="G26" s="58"/>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="B27" s="59" t="s">
+        <v>135</v>
+      </c>
+      <c r="C27" s="80">
         <v>4.2057008274716381E-2</v>
       </c>
-    </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B28" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="C28" s="29">
+      <c r="G27" s="58"/>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="B28" s="68" t="s">
+        <v>136</v>
+      </c>
+      <c r="C28" s="81">
         <f>D16</f>
         <v>4279905</v>
       </c>
-    </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B29" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="C29" s="44">
+      <c r="G28" s="58"/>
+    </row>
+    <row r="29" spans="2:7" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="B29" s="77" t="s">
+        <v>137</v>
+      </c>
+      <c r="C29" s="82">
         <f>C28*C$27/12</f>
         <v>15000.000000000002</v>
       </c>
-    </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B30" s="7"/>
-      <c r="C30" s="24"/>
-    </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B31" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="C31" s="24">
+      <c r="G29" s="58"/>
+    </row>
+    <row r="30" spans="2:7" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="B30" s="83"/>
+      <c r="C30" s="84"/>
+      <c r="G30" s="58"/>
+    </row>
+    <row r="31" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="B31" s="59" t="s">
+        <v>138</v>
+      </c>
+      <c r="C31" s="84">
         <f>C$9*C$8</f>
         <v>630</v>
       </c>
-      <c r="D31" s="50">
+      <c r="D31" s="85">
         <f>C31/C29</f>
         <v>4.1999999999999996E-2</v>
       </c>
-    </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B32" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="C32" s="24">
+      <c r="G31" s="58"/>
+    </row>
+    <row r="32" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="B32" s="59" t="s">
+        <v>139</v>
+      </c>
+      <c r="C32" s="84">
         <f>$C$29*D32</f>
         <v>750.00000000000011</v>
       </c>
-      <c r="D32" s="54">
+      <c r="D32" s="86">
         <f>Assumptions!C15</f>
         <v>0.05</v>
       </c>
-    </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B33" s="30" t="s">
-        <v>26</v>
-      </c>
-      <c r="C33" s="24">
+      <c r="G32" s="58"/>
+    </row>
+    <row r="33" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="B33" s="59" t="s">
+        <v>140</v>
+      </c>
+      <c r="C33" s="84">
         <f t="shared" ref="C33:C36" si="1">$C$29*D33</f>
         <v>450.00000000000006</v>
       </c>
-      <c r="D33" s="50">
+      <c r="D33" s="85">
         <f>Assumptions!C16</f>
         <v>0.03</v>
       </c>
-    </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B34" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="C34" s="24">
+      <c r="G33" s="58"/>
+    </row>
+    <row r="34" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="B34" s="59" t="s">
+        <v>141</v>
+      </c>
+      <c r="C34" s="84">
         <f t="shared" si="1"/>
         <v>750.00000000000011</v>
       </c>
-      <c r="D34" s="3">
+      <c r="D34" s="87">
         <f>Assumptions!C17</f>
         <v>0.05</v>
       </c>
-    </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B35" s="30" t="s">
-        <v>102</v>
-      </c>
-      <c r="C35" s="24">
+      <c r="G34" s="58"/>
+    </row>
+    <row r="35" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="B35" s="59" t="s">
+        <v>165</v>
+      </c>
+      <c r="C35" s="84">
         <f t="shared" ca="1" si="1"/>
         <v>300.00000000000006</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D35" s="87">
         <f ca="1">IF(C$7&gt;=30,2%,0)</f>
         <v>0.02</v>
       </c>
-    </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B36" s="30" t="s">
-        <v>16</v>
-      </c>
-      <c r="C36" s="24">
+      <c r="G35" s="58"/>
+    </row>
+    <row r="36" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="B36" s="59" t="s">
+        <v>142</v>
+      </c>
+      <c r="C36" s="84">
         <f t="shared" si="1"/>
         <v>300.00000000000006</v>
       </c>
-      <c r="D36" s="3">
+      <c r="D36" s="87">
         <f>Assumptions!C18</f>
         <v>0.02</v>
       </c>
-    </row>
-    <row r="37" spans="2:4" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B37" s="32" t="s">
-        <v>41</v>
-      </c>
-      <c r="C37" s="33">
+      <c r="G36" s="58"/>
+    </row>
+    <row r="37" spans="2:7" ht="15.4" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B37" s="75" t="s">
+        <v>143</v>
+      </c>
+      <c r="C37" s="109">
         <v>0</v>
       </c>
-      <c r="D37" s="52">
+      <c r="D37" s="89">
         <f>C37/C29</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="2:4" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="B38" s="21" t="s">
-        <v>63</v>
-      </c>
-      <c r="C38" s="44">
+      <c r="G37" s="58"/>
+    </row>
+    <row r="38" spans="2:7" ht="16.149999999999999" thickTop="1" x14ac:dyDescent="0.5">
+      <c r="B38" s="77" t="s">
+        <v>158</v>
+      </c>
+      <c r="C38" s="82">
         <f ca="1">C29-SUM(C31:C37)</f>
         <v>11820.000000000002</v>
       </c>
-      <c r="D38" s="50">
+      <c r="D38" s="85">
         <f ca="1">C38/C29</f>
         <v>0.78800000000000003</v>
       </c>
-    </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B39" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="C39" s="45">
+      <c r="G38" s="58"/>
+    </row>
+    <row r="39" spans="2:7" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="B39" s="77" t="s">
+        <v>144</v>
+      </c>
+      <c r="C39" s="90">
         <f>Assumptions!C19</f>
         <v>0.02</v>
       </c>
-    </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B41" s="27" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="43" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B43" s="30" t="s">
-        <v>38</v>
-      </c>
-      <c r="C43" s="48">
+      <c r="G39" s="58"/>
+    </row>
+    <row r="40" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="G40" s="58"/>
+    </row>
+    <row r="41" spans="2:7" ht="15.75" x14ac:dyDescent="0.55000000000000004">
+      <c r="B41" s="66" t="s">
+        <v>145</v>
+      </c>
+      <c r="G41" s="57" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="42" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="G42" s="58"/>
+    </row>
+    <row r="43" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="B43" s="59" t="s">
+        <v>146</v>
+      </c>
+      <c r="C43" s="91">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B44" s="31" t="s">
-        <v>42</v>
-      </c>
-      <c r="C44" s="41">
+      <c r="G43" s="58"/>
+    </row>
+    <row r="44" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="B44" s="68" t="s">
+        <v>147</v>
+      </c>
+      <c r="C44" s="92">
         <f>(1+C43)^(1/C10)-1</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B45" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="C45" s="42">
+      <c r="G44" s="58"/>
+    </row>
+    <row r="45" spans="2:7" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="B45" s="77" t="s">
+        <v>148</v>
+      </c>
+      <c r="C45" s="93">
         <f>D16*(1+C$43)</f>
         <v>4279905</v>
       </c>
-    </row>
-    <row r="47" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B47" s="27" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B49" s="30" t="s">
-        <v>35</v>
-      </c>
-      <c r="C49" s="35" t="str">
+      <c r="G45" s="58"/>
+    </row>
+    <row r="46" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="G46" s="58"/>
+    </row>
+    <row r="47" spans="2:7" ht="15.75" x14ac:dyDescent="0.55000000000000004">
+      <c r="B47" s="66" t="s">
+        <v>149</v>
+      </c>
+      <c r="G47" s="57" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="48" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="G48" s="58"/>
+    </row>
+    <row r="49" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="B49" s="59" t="s">
+        <v>125</v>
+      </c>
+      <c r="C49" s="94" t="str">
         <f>C14</f>
         <v>Asking Price</v>
       </c>
-      <c r="D49" s="35" t="str">
+      <c r="D49" s="94" t="str">
         <f>D14</f>
         <v>Comparable</v>
       </c>
-      <c r="E49" s="35" t="str">
+      <c r="E49" s="94" t="str">
         <f>E14</f>
         <v>IRR Netural Price</v>
       </c>
-    </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B50" s="30" t="s">
-        <v>65</v>
-      </c>
-      <c r="C50" s="20">
+      <c r="G49" s="58"/>
+    </row>
+    <row r="50" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="B50" s="59" t="s">
+        <v>150</v>
+      </c>
+      <c r="C50" s="72">
         <f>C16</f>
         <v>4280000</v>
       </c>
-      <c r="D50" s="20">
+      <c r="D50" s="72">
         <f>D16</f>
         <v>4279905</v>
       </c>
-      <c r="E50" s="20">
+      <c r="E50" s="72">
         <f>E16</f>
         <v>3660000</v>
       </c>
-    </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B51" s="30" t="s">
-        <v>60</v>
-      </c>
-      <c r="C51" s="23">
+      <c r="G50" s="58"/>
+    </row>
+    <row r="51" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="B51" s="59" t="s">
+        <v>133</v>
+      </c>
+      <c r="C51" s="95">
         <f>C23</f>
         <v>4717480</v>
       </c>
-      <c r="D51" s="23">
+      <c r="D51" s="95">
         <f>D23</f>
         <v>4717378.7300000004</v>
       </c>
-      <c r="E51" s="23">
+      <c r="E51" s="95">
         <f>E23</f>
         <v>4056560</v>
       </c>
-    </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B52" s="30" t="s">
-        <v>44</v>
-      </c>
-      <c r="C52" s="98">
+      <c r="G51" s="58"/>
+    </row>
+    <row r="52" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="B52" s="59" t="s">
+        <v>159</v>
+      </c>
+      <c r="C52" s="107">
         <f ca="1">C$38*12</f>
         <v>141840.00000000003</v>
       </c>
-      <c r="D52" s="98"/>
-      <c r="E52" s="98"/>
-    </row>
-    <row r="53" spans="2:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B53" s="32" t="s">
-        <v>45</v>
-      </c>
-      <c r="C53" s="99">
+      <c r="D52" s="107"/>
+      <c r="E52" s="107"/>
+      <c r="G52" s="58"/>
+    </row>
+    <row r="53" spans="2:7" ht="15.4" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B53" s="75" t="s">
+        <v>151</v>
+      </c>
+      <c r="C53" s="103">
         <f>C$45</f>
         <v>4279905</v>
       </c>
-      <c r="D53" s="99"/>
-      <c r="E53" s="99"/>
-    </row>
-    <row r="54" spans="2:5" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="B54" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="C54" s="43">
+      <c r="D53" s="103"/>
+      <c r="E53" s="103"/>
+      <c r="G53" s="58"/>
+    </row>
+    <row r="54" spans="2:7" ht="16.149999999999999" thickTop="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B54" s="77" t="s">
+        <v>152</v>
+      </c>
+      <c r="C54" s="96">
         <f ca="1">RATE(15, $C52*(1+$C$39), -C51, $C53 / (1+$C$39)^15) + $C$39</f>
         <v>3.0492697271019137E-2</v>
       </c>
-      <c r="D54" s="43">
+      <c r="D54" s="96">
         <f t="shared" ref="D54:E54" ca="1" si="2">RATE(15, $C52*(1+$C$39), -D51, $C53 / (1+$C$39)^15) + $C$39</f>
         <v>3.0494512194345638E-2</v>
       </c>
-      <c r="E54" s="43">
+      <c r="E54" s="96">
         <f t="shared" ca="1" si="2"/>
         <v>4.3481297128932075E-2</v>
       </c>
-    </row>
-    <row r="56" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B56" s="36" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="57" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B57" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="58" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B58" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="59" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B59" t="s">
-        <v>69</v>
-      </c>
+      <c r="G54" s="58"/>
+    </row>
+    <row r="55" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="G55" s="58"/>
+    </row>
+    <row r="56" spans="2:7" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="B56" s="97" t="s">
+        <v>153</v>
+      </c>
+      <c r="G56" s="58"/>
+    </row>
+    <row r="57" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="B57" s="56" t="s">
+        <v>154</v>
+      </c>
+      <c r="G57" s="58"/>
+    </row>
+    <row r="58" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="B58" s="56" t="s">
+        <v>155</v>
+      </c>
+      <c r="G58" s="58"/>
+    </row>
+    <row r="59" spans="2:7" x14ac:dyDescent="0.5">
+      <c r="B59" s="56" t="s">
+        <v>156</v>
+      </c>
+      <c r="G59" s="58"/>
     </row>
   </sheetData>
   <dataConsolidate/>

--- a/financial_models/Res_Property_Monitor.xlsx
+++ b/financial_models/Res_Property_Monitor.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA155BF1-28E9-44AC-82B7-869A681DF749}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{586A5EFB-9424-442D-B523-1DB7A52E1568}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="6150" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1350,6 +1350,12 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="10" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1379,12 +1385,6 @@
     </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2190,12 +2190,12 @@
       <c r="B17" s="30" t="s">
         <v>59</v>
       </c>
-      <c r="C17" s="100">
+      <c r="C17" s="102">
         <f>Assumptions!C9</f>
         <v>0.01</v>
       </c>
-      <c r="D17" s="100"/>
-      <c r="E17" s="100"/>
+      <c r="D17" s="102"/>
+      <c r="E17" s="102"/>
       <c r="G17" s="4"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.45">
@@ -2217,36 +2217,36 @@
       <c r="B19" s="30" t="s">
         <v>58</v>
       </c>
-      <c r="C19" s="101">
+      <c r="C19" s="103">
         <f>Assumptions!C10</f>
         <v>1E-3</v>
       </c>
-      <c r="D19" s="101"/>
-      <c r="E19" s="101"/>
+      <c r="D19" s="103"/>
+      <c r="E19" s="103"/>
       <c r="G19" s="4"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B20" s="30" t="s">
         <v>103</v>
       </c>
-      <c r="C20" s="102">
+      <c r="C20" s="104">
         <f>Assumptions!C11</f>
         <v>20000</v>
       </c>
-      <c r="D20" s="102"/>
-      <c r="E20" s="102"/>
+      <c r="D20" s="104"/>
+      <c r="E20" s="104"/>
       <c r="G20" s="4"/>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B21" s="30" t="s">
         <v>104</v>
       </c>
-      <c r="C21" s="102">
+      <c r="C21" s="104">
         <f>Assumptions!C12</f>
         <v>5000</v>
       </c>
-      <c r="D21" s="102"/>
-      <c r="E21" s="102"/>
+      <c r="D21" s="104"/>
+      <c r="E21" s="104"/>
       <c r="G21" s="4"/>
     </row>
     <row r="22" spans="2:7" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -2571,24 +2571,24 @@
       <c r="B52" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="C52" s="98">
+      <c r="C52" s="100">
         <f ca="1">C$38*12</f>
         <v>209208</v>
       </c>
-      <c r="D52" s="98"/>
-      <c r="E52" s="98"/>
+      <c r="D52" s="100"/>
+      <c r="E52" s="100"/>
       <c r="G52" s="4"/>
     </row>
     <row r="53" spans="2:7" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B53" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="C53" s="99">
+      <c r="C53" s="101">
         <f>C$45</f>
         <v>13524000</v>
       </c>
-      <c r="D53" s="99"/>
-      <c r="E53" s="99"/>
+      <c r="D53" s="101"/>
+      <c r="E53" s="101"/>
       <c r="G53" s="4"/>
     </row>
     <row r="54" spans="2:7" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
@@ -2810,12 +2810,12 @@
       <c r="B17" s="59" t="s">
         <v>127</v>
       </c>
-      <c r="C17" s="104">
+      <c r="C17" s="106">
         <f>Assumptions!C9</f>
         <v>0.01</v>
       </c>
-      <c r="D17" s="104"/>
-      <c r="E17" s="104"/>
+      <c r="D17" s="106"/>
+      <c r="E17" s="106"/>
       <c r="G17" s="58"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.5">
@@ -2837,35 +2837,35 @@
       <c r="B19" s="59" t="s">
         <v>129</v>
       </c>
-      <c r="C19" s="105">
+      <c r="C19" s="107">
         <f>Assumptions!C10</f>
         <v>1E-3</v>
       </c>
-      <c r="D19" s="105"/>
-      <c r="E19" s="105"/>
+      <c r="D19" s="107"/>
+      <c r="E19" s="107"/>
       <c r="G19" s="58"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.5">
       <c r="B20" s="59" t="s">
         <v>130</v>
       </c>
-      <c r="C20" s="106">
+      <c r="C20" s="108">
         <f>Assumptions!C11</f>
         <v>20000</v>
       </c>
-      <c r="D20" s="106"/>
-      <c r="E20" s="106"/>
+      <c r="D20" s="108"/>
+      <c r="E20" s="108"/>
       <c r="G20" s="58"/>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.5">
       <c r="B21" s="59" t="s">
         <v>131</v>
       </c>
-      <c r="C21" s="106">
+      <c r="C21" s="108">
         <v>10000</v>
       </c>
-      <c r="D21" s="106"/>
-      <c r="E21" s="106"/>
+      <c r="D21" s="108"/>
+      <c r="E21" s="108"/>
       <c r="G21" s="58" t="s">
         <v>112</v>
       </c>
@@ -3193,24 +3193,24 @@
       <c r="B52" s="59" t="s">
         <v>159</v>
       </c>
-      <c r="C52" s="107">
+      <c r="C52" s="109">
         <f>C$38*12</f>
         <v>521400.00000000023</v>
       </c>
-      <c r="D52" s="107"/>
-      <c r="E52" s="107"/>
+      <c r="D52" s="109"/>
+      <c r="E52" s="109"/>
       <c r="G52" s="58"/>
     </row>
     <row r="53" spans="2:7" ht="15.4" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B53" s="75" t="s">
         <v>151</v>
       </c>
-      <c r="C53" s="103">
+      <c r="C53" s="105">
         <f>C$45</f>
         <v>26000000</v>
       </c>
-      <c r="D53" s="103"/>
-      <c r="E53" s="103"/>
+      <c r="D53" s="105"/>
+      <c r="E53" s="105"/>
       <c r="G53" s="58"/>
     </row>
     <row r="54" spans="2:7" ht="16.149999999999999" thickTop="1" x14ac:dyDescent="0.55000000000000004">
@@ -3403,12 +3403,12 @@
       <c r="B17" s="30" t="s">
         <v>59</v>
       </c>
-      <c r="C17" s="100">
+      <c r="C17" s="102">
         <f>Assumptions!C9</f>
         <v>0.01</v>
       </c>
-      <c r="D17" s="100"/>
-      <c r="E17" s="100"/>
+      <c r="D17" s="102"/>
+      <c r="E17" s="102"/>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B18" s="30" t="s">
@@ -3428,34 +3428,34 @@
       <c r="B19" s="30" t="s">
         <v>58</v>
       </c>
-      <c r="C19" s="101">
+      <c r="C19" s="103">
         <f>Assumptions!C10</f>
         <v>1E-3</v>
       </c>
-      <c r="D19" s="101"/>
-      <c r="E19" s="101"/>
+      <c r="D19" s="103"/>
+      <c r="E19" s="103"/>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B20" s="30" t="s">
         <v>103</v>
       </c>
-      <c r="C20" s="102">
+      <c r="C20" s="104">
         <f>Assumptions!C11</f>
         <v>20000</v>
       </c>
-      <c r="D20" s="102"/>
-      <c r="E20" s="102"/>
+      <c r="D20" s="104"/>
+      <c r="E20" s="104"/>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B21" s="30" t="s">
         <v>104</v>
       </c>
-      <c r="C21" s="102">
+      <c r="C21" s="104">
         <f>Assumptions!C12</f>
         <v>5000</v>
       </c>
-      <c r="D21" s="102"/>
-      <c r="E21" s="102"/>
+      <c r="D21" s="104"/>
+      <c r="E21" s="104"/>
     </row>
     <row r="22" spans="2:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B22" s="32" t="s">
@@ -3729,23 +3729,23 @@
       <c r="B52" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="C52" s="98">
+      <c r="C52" s="100">
         <f ca="1">C$38*12</f>
         <v>185282.125</v>
       </c>
-      <c r="D52" s="98"/>
-      <c r="E52" s="98"/>
+      <c r="D52" s="100"/>
+      <c r="E52" s="100"/>
     </row>
     <row r="53" spans="2:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B53" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="C53" s="99">
+      <c r="C53" s="101">
         <f>C$45</f>
         <v>9772750</v>
       </c>
-      <c r="D53" s="99"/>
-      <c r="E53" s="99"/>
+      <c r="D53" s="101"/>
+      <c r="E53" s="101"/>
     </row>
     <row r="54" spans="2:5" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
       <c r="B54" s="21" t="s">
@@ -3911,13 +3911,13 @@
         <v>125</v>
       </c>
       <c r="C14" s="67" t="s">
-        <v>43</v>
+        <v>161</v>
       </c>
       <c r="D14" s="67" t="s">
-        <v>36</v>
+        <v>162</v>
       </c>
       <c r="E14" s="67" t="s">
-        <v>95</v>
+        <v>163</v>
       </c>
       <c r="G14" s="58"/>
     </row>
@@ -3958,26 +3958,26 @@
       <c r="B17" s="59" t="s">
         <v>127</v>
       </c>
-      <c r="C17" s="104">
+      <c r="C17" s="106">
         <f>Assumptions!C9</f>
         <v>0.01</v>
       </c>
-      <c r="D17" s="104"/>
-      <c r="E17" s="104"/>
+      <c r="D17" s="106"/>
+      <c r="E17" s="106"/>
       <c r="G17" s="58"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.5">
       <c r="B18" s="59" t="s">
         <v>128</v>
       </c>
-      <c r="C18" s="108">
+      <c r="C18" s="98">
         <v>5.5E-2</v>
       </c>
-      <c r="D18" s="108">
+      <c r="D18" s="98">
         <f>C18</f>
         <v>5.5E-2</v>
       </c>
-      <c r="E18" s="108">
+      <c r="E18" s="98">
         <f>D18</f>
         <v>5.5E-2</v>
       </c>
@@ -3987,36 +3987,36 @@
       <c r="B19" s="59" t="s">
         <v>129</v>
       </c>
-      <c r="C19" s="105">
+      <c r="C19" s="107">
         <f>Assumptions!C10</f>
         <v>1E-3</v>
       </c>
-      <c r="D19" s="105"/>
-      <c r="E19" s="105"/>
+      <c r="D19" s="107"/>
+      <c r="E19" s="107"/>
       <c r="G19" s="58"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.5">
       <c r="B20" s="59" t="s">
         <v>130</v>
       </c>
-      <c r="C20" s="106">
+      <c r="C20" s="108">
         <f>Assumptions!C11</f>
         <v>20000</v>
       </c>
-      <c r="D20" s="106"/>
-      <c r="E20" s="106"/>
+      <c r="D20" s="108"/>
+      <c r="E20" s="108"/>
       <c r="G20" s="58"/>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.5">
       <c r="B21" s="59" t="s">
         <v>131</v>
       </c>
-      <c r="C21" s="106">
+      <c r="C21" s="108">
         <f>Assumptions!C12</f>
         <v>5000</v>
       </c>
-      <c r="D21" s="106"/>
-      <c r="E21" s="106"/>
+      <c r="D21" s="108"/>
+      <c r="E21" s="108"/>
       <c r="G21" s="58"/>
     </row>
     <row r="22" spans="2:7" ht="15.4" thickBot="1" x14ac:dyDescent="0.55000000000000004">
@@ -4191,7 +4191,7 @@
       <c r="B37" s="75" t="s">
         <v>143</v>
       </c>
-      <c r="C37" s="109">
+      <c r="C37" s="99">
         <v>0</v>
       </c>
       <c r="D37" s="89">
@@ -4287,15 +4287,15 @@
       </c>
       <c r="C49" s="94" t="str">
         <f>C14</f>
-        <v>Asking Price</v>
+        <v>要價</v>
       </c>
       <c r="D49" s="94" t="str">
         <f>D14</f>
-        <v>Comparable</v>
+        <v>可比售價</v>
       </c>
       <c r="E49" s="94" t="str">
         <f>E14</f>
-        <v>IRR Netural Price</v>
+        <v>IRR中性售價</v>
       </c>
       <c r="G49" s="58"/>
     </row>
@@ -4339,24 +4339,24 @@
       <c r="B52" s="59" t="s">
         <v>159</v>
       </c>
-      <c r="C52" s="107">
+      <c r="C52" s="109">
         <f ca="1">C$38*12</f>
         <v>141840.00000000003</v>
       </c>
-      <c r="D52" s="107"/>
-      <c r="E52" s="107"/>
+      <c r="D52" s="109"/>
+      <c r="E52" s="109"/>
       <c r="G52" s="58"/>
     </row>
     <row r="53" spans="2:7" ht="15.4" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B53" s="75" t="s">
         <v>151</v>
       </c>
-      <c r="C53" s="103">
+      <c r="C53" s="105">
         <f>C$45</f>
         <v>4279905</v>
       </c>
-      <c r="D53" s="103"/>
-      <c r="E53" s="103"/>
+      <c r="D53" s="105"/>
+      <c r="E53" s="105"/>
       <c r="G53" s="58"/>
     </row>
     <row r="54" spans="2:7" ht="16.149999999999999" thickTop="1" x14ac:dyDescent="0.55000000000000004">
